--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF00CA0A-0D61-4C11-A066-4E743671F1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C92B4B-2037-44B7-A541-59D30E3BB2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6866,7 +6866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B27A2E9-3479-41D7-8954-2C95332B0262}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A395AC52-6F77-410E-B691-62E42D941722}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6948,7 +6948,7 @@
         <v>2.9460000000000002</v>
       </c>
       <c r="M11">
-        <v>0.1662904323543602</v>
+        <v>0.16629043199999999</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -6986,7 +6986,7 @@
         <v>0.3765</v>
       </c>
       <c r="M12">
-        <v>0.1660589409575936</v>
+        <v>0.16605894099999999</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -7024,7 +7024,7 @@
         <v>0.86850000000000005</v>
       </c>
       <c r="M13">
-        <v>0.16603687133815981</v>
+        <v>0.166036871</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -7062,7 +7062,7 @@
         <v>2.3174999999999999</v>
       </c>
       <c r="M14">
-        <v>0.16600998761152111</v>
+        <v>0.166009988</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -7100,7 +7100,7 @@
         <v>3.2130000000000001</v>
       </c>
       <c r="M15">
-        <v>0.15791618136540428</v>
+        <v>0.15791618144117647</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -7138,7 +7138,7 @@
         <v>15.913500000000001</v>
       </c>
       <c r="M16">
-        <v>0.1578078168797811</v>
+        <v>0.15780781694895843</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -7176,7 +7176,7 @@
         <v>0.30449999999999999</v>
       </c>
       <c r="M17">
-        <v>0.15763049594795012</v>
+        <v>0.1576304955862069</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -7214,7 +7214,7 @@
         <v>19.1175</v>
       </c>
       <c r="M18">
-        <v>0.15708286511247102</v>
+        <v>0.15708286501294624</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -7252,7 +7252,7 @@
         <v>17.7135</v>
       </c>
       <c r="M19">
-        <v>0.1559119009051162</v>
+        <v>0.15591190081776607</v>
       </c>
       <c r="N19">
         <v>3</v>
@@ -7290,7 +7290,7 @@
         <v>55.235250000000001</v>
       </c>
       <c r="M20">
-        <v>0.15242640936734639</v>
+        <v>0.15242640939611934</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -7328,7 +7328,7 @@
         <v>35.448749999999997</v>
       </c>
       <c r="M21">
-        <v>0.14922923885275707</v>
+        <v>0.1492292388035967</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -7366,7 +7366,7 @@
         <v>48.84675</v>
       </c>
       <c r="M22">
-        <v>0.14900018618577154</v>
+        <v>0.14900018618331312</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -7404,7 +7404,7 @@
         <v>37.276499999999999</v>
       </c>
       <c r="M23">
-        <v>0.14696908603529971</v>
+        <v>0.14696908609122369</v>
       </c>
       <c r="N23">
         <v>3</v>
@@ -7442,7 +7442,7 @@
         <v>30.28725</v>
       </c>
       <c r="M24">
-        <v>0.14640461999321244</v>
+        <v>0.1464046198908204</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -7480,7 +7480,7 @@
         <v>101.51625</v>
       </c>
       <c r="M25">
-        <v>0.14266988441536055</v>
+        <v>0.14266988444631526</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -7518,7 +7518,7 @@
         <v>103.524</v>
       </c>
       <c r="M26">
-        <v>0.13860597249684553</v>
+        <v>0.13860597241461403</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -7556,7 +7556,7 @@
         <v>97.376999999999995</v>
       </c>
       <c r="M27">
-        <v>0.1379235172174148</v>
+        <v>0.13792351711269604</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -7594,7 +7594,7 @@
         <v>103.755</v>
       </c>
       <c r="M28">
-        <v>0.13713528865346272</v>
+        <v>0.13713528867831432</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -7632,7 +7632,7 @@
         <v>88.663499999999999</v>
       </c>
       <c r="M29">
-        <v>0.13654150960518857</v>
+        <v>0.13654150962306927</v>
       </c>
       <c r="N29">
         <v>3</v>
@@ -7670,7 +7670,7 @@
         <v>83.819249999999997</v>
       </c>
       <c r="M30">
-        <v>0.13376983623565916</v>
+        <v>0.13376983621610786</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -7708,7 +7708,7 @@
         <v>63.249749999999999</v>
       </c>
       <c r="M31">
-        <v>0.13372190917245153</v>
+        <v>0.13372190909688969</v>
       </c>
       <c r="N31">
         <v>2</v>
@@ -7746,7 +7746,7 @@
         <v>65.268749999999997</v>
       </c>
       <c r="M32">
-        <v>0.13341965150528012</v>
+        <v>0.13341965170718761</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -7784,7 +7784,7 @@
         <v>72.006</v>
       </c>
       <c r="M33">
-        <v>0.13329939427311402</v>
+        <v>0.13329939427113366</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -7822,7 +7822,7 @@
         <v>71.385750000000002</v>
       </c>
       <c r="M34">
-        <v>0.1320486454572623</v>
+        <v>0.13204864563094526</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -7834,7 +7834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD55BEA1-A5FD-4BBF-BC5E-C750043F35F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF049B48-9CC0-4CFE-ACF4-F9B56B3B83FD}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14736,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC28E8ED-F7EA-4C0C-A5C6-3D0400455E26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01BBBAD1-33A4-4F25-940E-E70C475CA750}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C92B4B-2037-44B7-A541-59D30E3BB2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FA510EB-8813-4E97-B341-700E6B724BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6866,7 +6866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A395AC52-6F77-410E-B691-62E42D941722}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E73A424-89F8-4FD5-B2FE-7E7D623DF9BF}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6948,7 +6948,7 @@
         <v>2.9460000000000002</v>
       </c>
       <c r="M11">
-        <v>0.16629043199999999</v>
+        <v>0.1662904323543602</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -6986,7 +6986,7 @@
         <v>0.3765</v>
       </c>
       <c r="M12">
-        <v>0.16605894099999999</v>
+        <v>0.1660589409575936</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -7024,7 +7024,7 @@
         <v>0.86850000000000005</v>
       </c>
       <c r="M13">
-        <v>0.166036871</v>
+        <v>0.16603687133815981</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -7062,7 +7062,7 @@
         <v>2.3174999999999999</v>
       </c>
       <c r="M14">
-        <v>0.166009988</v>
+        <v>0.16600998761152111</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -7100,7 +7100,7 @@
         <v>3.2130000000000001</v>
       </c>
       <c r="M15">
-        <v>0.15791618144117647</v>
+        <v>0.15791618136540428</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -7138,7 +7138,7 @@
         <v>15.913500000000001</v>
       </c>
       <c r="M16">
-        <v>0.15780781694895843</v>
+        <v>0.1578078168797811</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -7176,7 +7176,7 @@
         <v>0.30449999999999999</v>
       </c>
       <c r="M17">
-        <v>0.1576304955862069</v>
+        <v>0.15763049594795012</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -7214,7 +7214,7 @@
         <v>19.1175</v>
       </c>
       <c r="M18">
-        <v>0.15708286501294624</v>
+        <v>0.15708286511247102</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -7252,7 +7252,7 @@
         <v>17.7135</v>
       </c>
       <c r="M19">
-        <v>0.15591190081776607</v>
+        <v>0.1559119009051162</v>
       </c>
       <c r="N19">
         <v>3</v>
@@ -7290,7 +7290,7 @@
         <v>55.235250000000001</v>
       </c>
       <c r="M20">
-        <v>0.15242640939611934</v>
+        <v>0.15242640936734639</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -7328,7 +7328,7 @@
         <v>35.448749999999997</v>
       </c>
       <c r="M21">
-        <v>0.1492292388035967</v>
+        <v>0.14922923885275707</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -7366,7 +7366,7 @@
         <v>48.84675</v>
       </c>
       <c r="M22">
-        <v>0.14900018618331312</v>
+        <v>0.14900018618577154</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -7404,7 +7404,7 @@
         <v>37.276499999999999</v>
       </c>
       <c r="M23">
-        <v>0.14696908609122369</v>
+        <v>0.14696908603529971</v>
       </c>
       <c r="N23">
         <v>3</v>
@@ -7442,7 +7442,7 @@
         <v>30.28725</v>
       </c>
       <c r="M24">
-        <v>0.1464046198908204</v>
+        <v>0.14640461999321244</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -7480,7 +7480,7 @@
         <v>101.51625</v>
       </c>
       <c r="M25">
-        <v>0.14266988444631526</v>
+        <v>0.14266988441536055</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -7518,7 +7518,7 @@
         <v>103.524</v>
       </c>
       <c r="M26">
-        <v>0.13860597241461403</v>
+        <v>0.13860597249684553</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -7556,7 +7556,7 @@
         <v>97.376999999999995</v>
       </c>
       <c r="M27">
-        <v>0.13792351711269604</v>
+        <v>0.1379235172174148</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -7594,7 +7594,7 @@
         <v>103.755</v>
       </c>
       <c r="M28">
-        <v>0.13713528867831432</v>
+        <v>0.13713528865346272</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -7632,7 +7632,7 @@
         <v>88.663499999999999</v>
       </c>
       <c r="M29">
-        <v>0.13654150962306927</v>
+        <v>0.13654150960518857</v>
       </c>
       <c r="N29">
         <v>3</v>
@@ -7670,7 +7670,7 @@
         <v>83.819249999999997</v>
       </c>
       <c r="M30">
-        <v>0.13376983621610786</v>
+        <v>0.13376983623565916</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -7708,7 +7708,7 @@
         <v>63.249749999999999</v>
       </c>
       <c r="M31">
-        <v>0.13372190909688969</v>
+        <v>0.13372190917245153</v>
       </c>
       <c r="N31">
         <v>2</v>
@@ -7746,7 +7746,7 @@
         <v>65.268749999999997</v>
       </c>
       <c r="M32">
-        <v>0.13341965170718761</v>
+        <v>0.13341965150528012</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -7784,7 +7784,7 @@
         <v>72.006</v>
       </c>
       <c r="M33">
-        <v>0.13329939427113366</v>
+        <v>0.13329939427311402</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -7822,7 +7822,7 @@
         <v>71.385750000000002</v>
       </c>
       <c r="M34">
-        <v>0.13204864563094526</v>
+        <v>0.1320486454572623</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -7834,7 +7834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF049B48-9CC0-4CFE-ACF4-F9B56B3B83FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A1F8B1-67F0-41A0-8C6F-CA296B34EB0B}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14736,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01BBBAD1-33A4-4F25-940E-E70C475CA750}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B572E010-8CB7-41C2-A01D-25F1B3C3D8C0}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FA510EB-8813-4E97-B341-700E6B724BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{513285AF-95D5-470D-B081-ED8E3464B589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="599">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -679,10 +679,10 @@
     <t>ele</t>
   </si>
   <si>
-    <t>e_spv-DEU_17_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_17 -- cost class 1</t>
+    <t>e_spv-DEU_13_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_13 -- cost class 1</t>
   </si>
   <si>
     <t>annual</t>
@@ -691,120 +691,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>e_spv-DEU_17_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_17 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_17_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_17 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_17_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_17 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_16_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_16 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_16_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_16 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_16_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_16 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_16_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_16 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_16_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_16 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_15_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_15 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_15_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_15 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_15_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_15 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_15_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_15 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_15_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_15 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_14_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_14 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_14_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_14 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_14_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_14 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_14_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_14 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_14_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_14 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_13_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_13 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-DEU_13_c2</t>
   </si>
   <si>
@@ -817,16 +703,76 @@
     <t>solar resource -- CF class spv-DEU_13 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-DEU_13_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_13 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-DEU_13_c5</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-DEU_13 -- cost class 5</t>
   </si>
   <si>
-    <t>e_spv-DEU_13_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_13 -- cost class 4</t>
+    <t>e_spv-DEU_12_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_12 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_12_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_12 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_12_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_12 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_12_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_12 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_12_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_12 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_11_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_11 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_11_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_11 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_11_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_11 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_11_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_11 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_11_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_11 -- cost class 5</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -844,76 +790,10 @@
     <t>elc_spv-DEU</t>
   </si>
   <si>
-    <t>e_won-DEU_61_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_61 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_58_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_58 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_57_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_57 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_57_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_57 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_56_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_56_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_56_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_56_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_54_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_54 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_51_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_51 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_51_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_51 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_51_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_51 -- cost class 3</t>
+    <t>e_won-DEU_52_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_52 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-DEU_50_c1</t>
@@ -922,28 +802,22 @@
     <t>onshore wind resource -- CF class won-DEU_50 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_48_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_48 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_47_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_47 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_47_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_47 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_46_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_46 -- cost class 2</t>
+    <t>e_won-DEU_49_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_49 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_49_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_49 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_49_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_49 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_46_c1</t>
@@ -958,12 +832,30 @@
     <t>onshore wind resource -- CF class won-DEU_45 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-DEU_45_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_45 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-DEU_45_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_45 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_45_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_45 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_44_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_44 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-DEU_43_c1</t>
   </si>
   <si>
@@ -976,22 +868,82 @@
     <t>onshore wind resource -- CF class won-DEU_43 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_43_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_43 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_43_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_43 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_43_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_43 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-DEU_42_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_42 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-DEU_42_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_42 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_42_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_42 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_42_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_42 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_41_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_41 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_41_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_41 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-DEU_41_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_41 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_41_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_41 -- cost class 1</t>
+    <t>e_won-DEU_40_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_40_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_40_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_40_c3</t>
@@ -1000,30 +952,60 @@
     <t>onshore wind resource -- CF class won-DEU_40 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_40_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_40_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-DEU_39_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_39 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-DEU_39_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_39_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_39_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_39_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-DEU_38_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_38 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-DEU_38_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_38 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_38_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_38 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_38_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_38 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-DEU_37_c1</t>
   </si>
   <si>
@@ -1036,22 +1018,52 @@
     <t>onshore wind resource -- CF class won-DEU_37 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_37_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_37 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_37_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_37 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_37_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_37 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_36_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_36_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-DEU_36_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_36 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_36_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_36_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 1</t>
+    <t>e_won-DEU_35_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_35_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_35_c2</t>
@@ -1060,28 +1072,28 @@
     <t>onshore wind resource -- CF class won-DEU_35 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_35_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-DEU_35_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_35 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_35_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_35_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_35_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 1</t>
+    <t>e_won-DEU_34_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_34_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-DEU_34_c3</t>
@@ -1090,16 +1102,10 @@
     <t>onshore wind resource -- CF class won-DEU_34 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_34_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_34_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 2</t>
+    <t>e_won-DEU_34_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_34_c4</t>
@@ -1108,10 +1114,16 @@
     <t>onshore wind resource -- CF class won-DEU_34 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_34_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 5</t>
+    <t>e_won-DEU_33_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_33_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_33_c3</t>
@@ -1126,22 +1138,22 @@
     <t>onshore wind resource -- CF class won-DEU_33 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_33_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-DEU_33_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_33 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_33_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 1</t>
+    <t>e_won-DEU_32_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_32_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-DEU_32_c3</t>
@@ -1150,16 +1162,10 @@
     <t>onshore wind resource -- CF class won-DEU_32 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_32_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_32_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 1</t>
+    <t>e_won-DEU_32_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_32_c5</t>
@@ -1168,10 +1174,16 @@
     <t>onshore wind resource -- CF class won-DEU_32 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_32_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 4</t>
+    <t>e_won-DEU_31_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_31_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_31_c3</t>
@@ -1180,16 +1192,10 @@
     <t>onshore wind resource -- CF class won-DEU_31 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_31_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_31_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 1</t>
+    <t>e_won-DEU_31_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_31_c5</t>
@@ -1198,10 +1204,16 @@
     <t>onshore wind resource -- CF class won-DEU_31 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_31_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 4</t>
+    <t>e_won-DEU_30_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_30_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_30_c1</t>
@@ -1210,16 +1222,10 @@
     <t>onshore wind resource -- CF class won-DEU_30 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_30_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_30_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 2</t>
+    <t>e_won-DEU_30_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_30_c5</t>
@@ -1228,10 +1234,16 @@
     <t>onshore wind resource -- CF class won-DEU_30 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_30_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 4</t>
+    <t>e_won-DEU_29_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_29_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_29_c3</t>
@@ -1240,16 +1252,10 @@
     <t>onshore wind resource -- CF class won-DEU_29 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_29_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_29_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 1</t>
+    <t>e_won-DEU_29_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_29_c5</t>
@@ -1258,10 +1264,10 @@
     <t>onshore wind resource -- CF class won-DEU_29 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_29_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 4</t>
+    <t>e_won-DEU_28_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_28_c1</t>
@@ -1276,10 +1282,10 @@
     <t>onshore wind resource -- CF class won-DEU_28 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_28_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 3</t>
+    <t>e_won-DEU_28_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_28_c4</t>
@@ -1288,10 +1294,28 @@
     <t>onshore wind resource -- CF class won-DEU_28 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_28_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 5</t>
+    <t>e_won-DEU_27_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_27_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_27_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_27_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_27_c4</t>
@@ -1300,48 +1324,24 @@
     <t>onshore wind resource -- CF class won-DEU_27 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_27_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_27_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_27_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_27_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-DEU_26_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_26 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-DEU_26_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_26 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-DEU_26_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_26 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_26_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_26 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-DEU_26_c3</t>
   </si>
   <si>
@@ -1354,34 +1354,40 @@
     <t>onshore wind resource -- CF class won-DEU_26 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-DEU_25_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_25_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_25_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_25_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-DEU_25_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_25 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_25_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_25_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_25_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_25_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 4</t>
+    <t>e_won-DEU_24_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_24_c1</t>
@@ -1390,10 +1396,34 @@
     <t>onshore wind resource -- CF class won-DEU_24 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_23_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 5</t>
+    <t>e_won-DEU_24_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_24_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_24_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_23_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_23_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_23_c2</t>
@@ -1402,22 +1432,22 @@
     <t>onshore wind resource -- CF class won-DEU_23 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_23_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_23_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_23 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_23_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 1</t>
+    <t>e_won-DEU_22_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_22_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_22_c3</t>
@@ -1432,18 +1462,6 @@
     <t>onshore wind resource -- CF class won-DEU_22 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_22_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_22_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-DEU_22_c5</t>
   </si>
   <si>
@@ -1462,34 +1480,46 @@
     <t>onshore wind resource -- CF class won-DEU_21 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_21_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_21 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-DEU_21_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_21 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_21_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_21 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-DEU_21_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_21 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-DEU_20_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_20_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-DEU_20_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_20 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_20_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 2</t>
+    <t>e_won-DEU_20_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_20_c5</t>
@@ -1498,18 +1528,6 @@
     <t>onshore wind resource -- CF class won-DEU_20 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_20_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_20_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-DEU_19_c2</t>
   </si>
   <si>
@@ -1534,30 +1552,30 @@
     <t>onshore wind resource -- CF class won-DEU_19 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-DEU_18_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_18_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_18_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-DEU_18_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_18 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_18_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_18_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_18_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-DEU_18_c4</t>
   </si>
   <si>
@@ -1576,34 +1594,22 @@
     <t>onshore wind resource -- CF class won-DEU_17 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_17_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_17 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_17_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_17 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_16_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_16 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_15_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_15 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_15_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_15 -- cost class 3</t>
+    <t>e_won-DEU_16_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_16 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_16_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_16 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_15_c2</t>
@@ -1616,96 +1622,6 @@
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_15 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_14_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_14 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_13_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_13 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_12_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_12 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_11_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_11 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_11_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_11 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_10_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_10 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_9_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_9 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_9_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_9 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_7_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_7 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_5_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_5 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_5_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_5 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_3_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_3 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_3_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_3 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_2_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_2 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_2_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_2 -- cost class 1</t>
   </si>
   <si>
     <t>elc_won-DEU</t>
@@ -6866,8 +6782,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E73A424-89F8-4FD5-B2FE-7E7D623DF9BF}">
-  <dimension ref="B9:N34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BADF93B6-A5AB-4D92-B818-FEA08B7983DE}">
+  <dimension ref="B9:N25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:14">
@@ -6904,16 +6820,16 @@
         <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="L10" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="M10" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="N10" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -6942,13 +6858,13 @@
         <v>183</v>
       </c>
       <c r="K11" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L11">
-        <v>2.9460000000000002</v>
+        <v>12.791782386791809</v>
       </c>
       <c r="M11">
-        <v>0.1662904323543602</v>
+        <v>0.12902814577730443</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -6980,16 +6896,16 @@
         <v>187</v>
       </c>
       <c r="K12" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L12">
-        <v>0.3765</v>
+        <v>11.702903699571227</v>
       </c>
       <c r="M12">
-        <v>0.1660589409575936</v>
+        <v>0.1275874621992075</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -7018,16 +6934,16 @@
         <v>189</v>
       </c>
       <c r="K13" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L13">
-        <v>0.86850000000000005</v>
+        <v>19.844602556083714</v>
       </c>
       <c r="M13">
-        <v>0.16603687133815981</v>
+        <v>0.12645222884017382</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -7056,16 +6972,16 @@
         <v>191</v>
       </c>
       <c r="K14" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L14">
-        <v>2.3174999999999999</v>
+        <v>16.35015221521143</v>
       </c>
       <c r="M14">
-        <v>0.16600998761152111</v>
+        <v>0.1252207615863512</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -7094,16 +7010,16 @@
         <v>193</v>
       </c>
       <c r="K15" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L15">
-        <v>3.2130000000000001</v>
+        <v>10.526058360717219</v>
       </c>
       <c r="M15">
-        <v>0.15791618136540428</v>
+        <v>0.125</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -7132,16 +7048,16 @@
         <v>195</v>
       </c>
       <c r="K16" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L16">
-        <v>15.913500000000001</v>
+        <v>65.153241509933423</v>
       </c>
       <c r="M16">
-        <v>0.1578078168797811</v>
+        <v>0.12288031961134829</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7170,16 +7086,16 @@
         <v>197</v>
       </c>
       <c r="K17" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L17">
-        <v>0.30449999999999999</v>
+        <v>52.401759920563556</v>
       </c>
       <c r="M17">
-        <v>0.15763049594795012</v>
+        <v>0.1192081285175584</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7208,16 +7124,16 @@
         <v>199</v>
       </c>
       <c r="K18" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L18">
-        <v>19.1175</v>
+        <v>54.02475928388197</v>
       </c>
       <c r="M18">
-        <v>0.15708286511247102</v>
+        <v>0.11711793039977518</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7246,16 +7162,16 @@
         <v>201</v>
       </c>
       <c r="K19" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L19">
-        <v>17.7135</v>
+        <v>43.685343348396096</v>
       </c>
       <c r="M19">
-        <v>0.1559119009051162</v>
+        <v>0.11589950344468616</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7284,16 +7200,16 @@
         <v>203</v>
       </c>
       <c r="K20" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L20">
-        <v>55.235250000000001</v>
+        <v>48.822480329285014</v>
       </c>
       <c r="M20">
-        <v>0.15242640936734639</v>
+        <v>0.11503306689481993</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7322,16 +7238,16 @@
         <v>205</v>
       </c>
       <c r="K21" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L21">
-        <v>35.448749999999997</v>
+        <v>39.308023057963723</v>
       </c>
       <c r="M21">
-        <v>0.14922923885275707</v>
+        <v>0.11374801486475515</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7360,13 +7276,13 @@
         <v>207</v>
       </c>
       <c r="K22" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L22">
-        <v>48.84675</v>
+        <v>42.484800815089351</v>
       </c>
       <c r="M22">
-        <v>0.14900018618577154</v>
+        <v>0.11279660370308546</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -7398,13 +7314,13 @@
         <v>209</v>
       </c>
       <c r="K23" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L23">
-        <v>37.276499999999999</v>
+        <v>39.836754523943725</v>
       </c>
       <c r="M23">
-        <v>0.14696908603529971</v>
+        <v>0.1116845138712432</v>
       </c>
       <c r="N23">
         <v>3</v>
@@ -7436,16 +7352,16 @@
         <v>211</v>
       </c>
       <c r="K24" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L24">
-        <v>30.28725</v>
+        <v>31.620646602849003</v>
       </c>
       <c r="M24">
-        <v>0.14640461999321244</v>
+        <v>0.1106221621197848</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -7474,358 +7390,16 @@
         <v>213</v>
       </c>
       <c r="K25" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="L25">
-        <v>101.51625</v>
+        <v>40.168147484835643</v>
       </c>
       <c r="M25">
-        <v>0.14266988441536055</v>
+        <v>0.10949475767165157</v>
       </c>
       <c r="N25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14">
-      <c r="B26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" t="s">
-        <v>215</v>
-      </c>
-      <c r="D26" t="s">
-        <v>216</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>185</v>
-      </c>
-      <c r="H26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J26" t="s">
-        <v>215</v>
-      </c>
-      <c r="K26" t="s">
-        <v>237</v>
-      </c>
-      <c r="L26">
-        <v>103.524</v>
-      </c>
-      <c r="M26">
-        <v>0.13860597249684553</v>
-      </c>
-      <c r="N26">
         <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="B27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" t="s">
-        <v>217</v>
-      </c>
-      <c r="D27" t="s">
-        <v>218</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>185</v>
-      </c>
-      <c r="H27" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" t="s">
-        <v>217</v>
-      </c>
-      <c r="K27" t="s">
-        <v>237</v>
-      </c>
-      <c r="L27">
-        <v>97.376999999999995</v>
-      </c>
-      <c r="M27">
-        <v>0.1379235172174148</v>
-      </c>
-      <c r="N27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="B28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" t="s">
-        <v>220</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" t="s">
-        <v>186</v>
-      </c>
-      <c r="J28" t="s">
-        <v>219</v>
-      </c>
-      <c r="K28" t="s">
-        <v>237</v>
-      </c>
-      <c r="L28">
-        <v>103.755</v>
-      </c>
-      <c r="M28">
-        <v>0.13713528865346272</v>
-      </c>
-      <c r="N28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" t="s">
-        <v>221</v>
-      </c>
-      <c r="D29" t="s">
-        <v>222</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H29" t="s">
-        <v>186</v>
-      </c>
-      <c r="J29" t="s">
-        <v>221</v>
-      </c>
-      <c r="K29" t="s">
-        <v>237</v>
-      </c>
-      <c r="L29">
-        <v>88.663499999999999</v>
-      </c>
-      <c r="M29">
-        <v>0.13654150960518857</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14">
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" t="s">
-        <v>186</v>
-      </c>
-      <c r="J30" t="s">
-        <v>223</v>
-      </c>
-      <c r="K30" t="s">
-        <v>237</v>
-      </c>
-      <c r="L30">
-        <v>83.819249999999997</v>
-      </c>
-      <c r="M30">
-        <v>0.13376983623565916</v>
-      </c>
-      <c r="N30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="B31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" t="s">
-        <v>225</v>
-      </c>
-      <c r="D31" t="s">
-        <v>226</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" t="s">
-        <v>225</v>
-      </c>
-      <c r="K31" t="s">
-        <v>237</v>
-      </c>
-      <c r="L31">
-        <v>63.249749999999999</v>
-      </c>
-      <c r="M31">
-        <v>0.13372190917245153</v>
-      </c>
-      <c r="N31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14">
-      <c r="B32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" t="s">
-        <v>227</v>
-      </c>
-      <c r="D32" t="s">
-        <v>228</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>185</v>
-      </c>
-      <c r="H32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J32" t="s">
-        <v>227</v>
-      </c>
-      <c r="K32" t="s">
-        <v>237</v>
-      </c>
-      <c r="L32">
-        <v>65.268749999999997</v>
-      </c>
-      <c r="M32">
-        <v>0.13341965150528012</v>
-      </c>
-      <c r="N32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14">
-      <c r="B33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C33" t="s">
-        <v>229</v>
-      </c>
-      <c r="D33" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" t="s">
-        <v>186</v>
-      </c>
-      <c r="J33" t="s">
-        <v>229</v>
-      </c>
-      <c r="K33" t="s">
-        <v>237</v>
-      </c>
-      <c r="L33">
-        <v>72.006</v>
-      </c>
-      <c r="M33">
-        <v>0.13329939427311402</v>
-      </c>
-      <c r="N33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14">
-      <c r="B34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" t="s">
-        <v>231</v>
-      </c>
-      <c r="D34" t="s">
-        <v>232</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" t="s">
-        <v>186</v>
-      </c>
-      <c r="J34" t="s">
-        <v>231</v>
-      </c>
-      <c r="K34" t="s">
-        <v>237</v>
-      </c>
-      <c r="L34">
-        <v>71.385750000000002</v>
-      </c>
-      <c r="M34">
-        <v>0.1320486454572623</v>
-      </c>
-      <c r="N34">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7834,8 +7408,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4A1F8B1-67F0-41A0-8C6F-CA296B34EB0B}">
-  <dimension ref="B9:AB154"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAC2B83-F673-473A-BB02-02FB8C573C8F}">
+  <dimension ref="B9:AB149"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:28">
@@ -7878,16 +7452,16 @@
         <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="L10" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="M10" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="N10" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="P10" t="s">
         <v>178</v>
@@ -7914,16 +7488,16 @@
         <v>164</v>
       </c>
       <c r="Y10" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="Z10" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="AA10" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="AB10" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="2:28">
@@ -7931,10 +7505,10 @@
         <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D11" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7949,16 +7523,16 @@
         <v>186</v>
       </c>
       <c r="J11" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="K11" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L11">
-        <v>1.125E-2</v>
+        <v>7.6602564102564094E-3</v>
       </c>
       <c r="M11">
-        <v>0.60547369604706214</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -7967,10 +7541,10 @@
         <v>182</v>
       </c>
       <c r="Q11" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="R11" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="S11" t="s">
         <v>10</v>
@@ -7985,10 +7559,10 @@
         <v>186</v>
       </c>
       <c r="X11" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="Y11" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z11">
         <v>13.8675</v>
@@ -8005,10 +7579,10 @@
         <v>182</v>
       </c>
       <c r="C12" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -8023,16 +7597,16 @@
         <v>186</v>
       </c>
       <c r="J12" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="K12" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L12">
-        <v>0.13200000000000001</v>
+        <v>8.8807957153787295E-2</v>
       </c>
       <c r="M12">
-        <v>0.57960586454463925</v>
+        <v>0.501</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -8041,10 +7615,10 @@
         <v>182</v>
       </c>
       <c r="Q12" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="R12" t="s">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="S12" t="s">
         <v>10</v>
@@ -8059,10 +7633,10 @@
         <v>186</v>
       </c>
       <c r="X12" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="Y12" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z12">
         <v>11.755000000000001</v>
@@ -8079,10 +7653,10 @@
         <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D13" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -8097,28 +7671,28 @@
         <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="K13" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L13">
-        <v>0.21375</v>
+        <v>0.62654719309068485</v>
       </c>
       <c r="M13">
-        <v>0.57320959241145331</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" t="s">
         <v>182</v>
       </c>
       <c r="Q13" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="R13" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="S13" t="s">
         <v>10</v>
@@ -8133,10 +7707,10 @@
         <v>186</v>
       </c>
       <c r="X13" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="Y13" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z13">
         <v>13.8675</v>
@@ -8153,10 +7727,10 @@
         <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -8171,28 +7745,28 @@
         <v>186</v>
       </c>
       <c r="J14" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="K14" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L14">
-        <v>0.94199999999999995</v>
+        <v>0.1374704812888238</v>
       </c>
       <c r="M14">
-        <v>0.57299534979618882</v>
+        <v>0.49</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P14" t="s">
         <v>182</v>
       </c>
       <c r="Q14" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="R14" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="S14" t="s">
         <v>10</v>
@@ -8207,10 +7781,10 @@
         <v>186</v>
       </c>
       <c r="X14" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="Y14" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z14">
         <v>13.8675</v>
@@ -8227,10 +7801,10 @@
         <v>182</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D15" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -8245,28 +7819,28 @@
         <v>186</v>
       </c>
       <c r="J15" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="K15" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L15">
-        <v>0.222</v>
+        <v>0.14665964293128506</v>
       </c>
       <c r="M15">
-        <v>0.56455391735389493</v>
+        <v>0.48899999999999993</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="s">
         <v>182</v>
       </c>
       <c r="Q15" t="s">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="R15" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="S15" t="s">
         <v>10</v>
@@ -8281,10 +7855,10 @@
         <v>186</v>
       </c>
       <c r="X15" t="s">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="Y15" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z15">
         <v>13.8675</v>
@@ -8301,10 +7875,10 @@
         <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -8319,28 +7893,28 @@
         <v>186</v>
       </c>
       <c r="J16" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="K16" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L16">
-        <v>0.20549999999999999</v>
+        <v>0.30943732119635886</v>
       </c>
       <c r="M16">
-        <v>0.55646086641743908</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" t="s">
         <v>182</v>
       </c>
       <c r="Q16" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="R16" t="s">
-        <v>538</v>
+        <v>510</v>
       </c>
       <c r="S16" t="s">
         <v>10</v>
@@ -8355,10 +7929,10 @@
         <v>186</v>
       </c>
       <c r="X16" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="Y16" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z16">
         <v>13.8675</v>
@@ -8375,10 +7949,10 @@
         <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="D17" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -8393,28 +7967,28 @@
         <v>186</v>
       </c>
       <c r="J17" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="K17" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L17">
-        <v>0.48149999999999998</v>
+        <v>2.8129591489571522</v>
       </c>
       <c r="M17">
-        <v>0.55571876678834353</v>
+        <v>0.45</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P17" t="s">
         <v>182</v>
       </c>
       <c r="Q17" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="R17" t="s">
-        <v>540</v>
+        <v>512</v>
       </c>
       <c r="S17" t="s">
         <v>10</v>
@@ -8429,10 +8003,10 @@
         <v>186</v>
       </c>
       <c r="X17" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="Y17" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z17">
         <v>27.734999999999999</v>
@@ -8449,10 +8023,10 @@
         <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D18" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -8467,16 +8041,16 @@
         <v>186</v>
       </c>
       <c r="J18" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="K18" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L18">
-        <v>2.23875</v>
+        <v>0.58742454465550076</v>
       </c>
       <c r="M18">
-        <v>0.55538842146607259</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -8485,10 +8059,10 @@
         <v>182</v>
       </c>
       <c r="Q18" t="s">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="R18" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="S18" t="s">
         <v>10</v>
@@ -8503,10 +8077,10 @@
         <v>186</v>
       </c>
       <c r="X18" t="s">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="Y18" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z18">
         <v>14.02875</v>
@@ -8523,10 +8097,10 @@
         <v>182</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -8541,28 +8115,28 @@
         <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="K19" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L19">
-        <v>0.90525</v>
+        <v>0.1551219562401488</v>
       </c>
       <c r="M19">
-        <v>0.54362148490056739</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" t="s">
         <v>182</v>
       </c>
       <c r="Q19" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="R19" t="s">
-        <v>544</v>
+        <v>516</v>
       </c>
       <c r="S19" t="s">
         <v>10</v>
@@ -8577,10 +8151,10 @@
         <v>186</v>
       </c>
       <c r="X19" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="Y19" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z19">
         <v>13.8675</v>
@@ -8597,10 +8171,10 @@
         <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="D20" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -8615,28 +8189,28 @@
         <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="K20" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L20">
         <v>1.4212499999999999</v>
       </c>
       <c r="M20">
-        <v>0.51172011645728255</v>
+        <v>0.44499999999999995</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P20" t="s">
         <v>182</v>
       </c>
       <c r="Q20" t="s">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="R20" t="s">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="S20" t="s">
         <v>10</v>
@@ -8651,10 +8225,10 @@
         <v>186</v>
       </c>
       <c r="X20" t="s">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="Y20" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z20">
         <v>14.02875</v>
@@ -8671,10 +8245,10 @@
         <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -8689,28 +8263,28 @@
         <v>186</v>
       </c>
       <c r="J21" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="K21" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L21">
-        <v>2.1030000000000002</v>
+        <v>1.5770138627625505</v>
       </c>
       <c r="M21">
-        <v>0.50785221851711282</v>
+        <v>0.44400000000000006</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="s">
         <v>182</v>
       </c>
       <c r="Q21" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="R21" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="S21" t="s">
         <v>10</v>
@@ -8725,10 +8299,10 @@
         <v>186</v>
       </c>
       <c r="X21" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="Y21" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z21">
         <v>13.827500000000001</v>
@@ -8745,10 +8319,10 @@
         <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -8763,28 +8337,28 @@
         <v>186</v>
       </c>
       <c r="J22" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="K22" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L22">
-        <v>1.4744999999999999</v>
+        <v>4.4932775647884773</v>
       </c>
       <c r="M22">
-        <v>0.50527134774735971</v>
+        <v>0.43336492005138938</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P22" t="s">
         <v>182</v>
       </c>
       <c r="Q22" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="R22" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="S22" t="s">
         <v>10</v>
@@ -8799,10 +8373,10 @@
         <v>186</v>
       </c>
       <c r="X22" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="Y22" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z22">
         <v>13.92625</v>
@@ -8819,10 +8393,10 @@
         <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="D23" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -8837,28 +8411,28 @@
         <v>186</v>
       </c>
       <c r="J23" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="K23" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L23">
-        <v>0.83250000000000002</v>
+        <v>4.5376647457138732</v>
       </c>
       <c r="M23">
-        <v>0.5000100636922703</v>
+        <v>0.43</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" t="s">
         <v>182</v>
       </c>
       <c r="Q23" t="s">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="R23" t="s">
-        <v>552</v>
+        <v>524</v>
       </c>
       <c r="S23" t="s">
         <v>10</v>
@@ -8873,10 +8447,10 @@
         <v>186</v>
       </c>
       <c r="X23" t="s">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="Y23" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z23">
         <v>13.23875</v>
@@ -8893,10 +8467,10 @@
         <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D24" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -8911,29 +8485,29 @@
         <v>186</v>
       </c>
       <c r="J24" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="K24" t="s">
+        <v>498</v>
+      </c>
+      <c r="L24">
+        <v>4.8667662261345104</v>
+      </c>
+      <c r="M24">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="P24" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>525</v>
+      </c>
+      <c r="R24" t="s">
         <v>526</v>
       </c>
-      <c r="L24">
-        <v>1.476</v>
-      </c>
-      <c r="M24">
-        <v>0.47927323018315537</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="P24" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>553</v>
-      </c>
-      <c r="R24" t="s">
-        <v>554</v>
-      </c>
       <c r="S24" t="s">
         <v>10</v>
       </c>
@@ -8947,10 +8521,10 @@
         <v>186</v>
       </c>
       <c r="X24" t="s">
-        <v>553</v>
+        <v>525</v>
       </c>
       <c r="Y24" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z24">
         <v>4.5162500000000003</v>
@@ -8967,10 +8541,10 @@
         <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D25" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -8985,28 +8559,28 @@
         <v>186</v>
       </c>
       <c r="J25" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="K25" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L25">
-        <v>5.4210000000000003</v>
+        <v>4.0798187691058461</v>
       </c>
       <c r="M25">
-        <v>0.47395544719054766</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P25" t="s">
         <v>182</v>
       </c>
       <c r="Q25" t="s">
-        <v>555</v>
+        <v>527</v>
       </c>
       <c r="R25" t="s">
-        <v>556</v>
+        <v>528</v>
       </c>
       <c r="S25" t="s">
         <v>10</v>
@@ -9021,10 +8595,10 @@
         <v>186</v>
       </c>
       <c r="X25" t="s">
-        <v>555</v>
+        <v>527</v>
       </c>
       <c r="Y25" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z25">
         <v>13.8675</v>
@@ -9041,10 +8615,10 @@
         <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D26" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -9059,28 +8633,28 @@
         <v>186</v>
       </c>
       <c r="J26" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="K26" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L26">
-        <v>4.1527500000000002</v>
+        <v>2.409816641133665</v>
       </c>
       <c r="M26">
-        <v>0.4679272704745196</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P26" t="s">
         <v>182</v>
       </c>
       <c r="Q26" t="s">
-        <v>557</v>
+        <v>529</v>
       </c>
       <c r="R26" t="s">
-        <v>558</v>
+        <v>530</v>
       </c>
       <c r="S26" t="s">
         <v>10</v>
@@ -9095,10 +8669,10 @@
         <v>186</v>
       </c>
       <c r="X26" t="s">
-        <v>557</v>
+        <v>529</v>
       </c>
       <c r="Y26" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z26">
         <v>8.1549999999999994</v>
@@ -9115,10 +8689,10 @@
         <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="D27" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -9133,28 +8707,28 @@
         <v>186</v>
       </c>
       <c r="J27" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="K27" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L27">
-        <v>1.5667500000000001</v>
+        <v>3.4628263818732856</v>
       </c>
       <c r="M27">
-        <v>0.4617910666503538</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P27" t="s">
         <v>182</v>
       </c>
       <c r="Q27" t="s">
-        <v>559</v>
+        <v>531</v>
       </c>
       <c r="R27" t="s">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="S27" t="s">
         <v>10</v>
@@ -9169,10 +8743,10 @@
         <v>186</v>
       </c>
       <c r="X27" t="s">
-        <v>559</v>
+        <v>531</v>
       </c>
       <c r="Y27" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z27">
         <v>11.2575</v>
@@ -9189,10 +8763,10 @@
         <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="D28" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -9207,28 +8781,28 @@
         <v>186</v>
       </c>
       <c r="J28" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="K28" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L28">
-        <v>5.5514999999999999</v>
+        <v>1.3176292984869329</v>
       </c>
       <c r="M28">
-        <v>0.45911415041508091</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28" t="s">
         <v>182</v>
       </c>
       <c r="Q28" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="R28" t="s">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="S28" t="s">
         <v>10</v>
@@ -9243,10 +8817,10 @@
         <v>186</v>
       </c>
       <c r="X28" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="Y28" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z28">
         <v>9.06</v>
@@ -9263,10 +8837,10 @@
         <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -9281,28 +8855,28 @@
         <v>186</v>
       </c>
       <c r="J29" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="K29" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L29">
-        <v>5.4794999999999998</v>
+        <v>0.52875913363466021</v>
       </c>
       <c r="M29">
-        <v>0.45349251926597589</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P29" t="s">
         <v>182</v>
       </c>
       <c r="Q29" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="R29" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="S29" t="s">
         <v>10</v>
@@ -9317,10 +8891,10 @@
         <v>186</v>
       </c>
       <c r="X29" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="Y29" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z29">
         <v>10.8575</v>
@@ -9337,10 +8911,10 @@
         <v>182</v>
       </c>
       <c r="C30" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -9355,28 +8929,28 @@
         <v>186</v>
       </c>
       <c r="J30" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="K30" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L30">
-        <v>7.0282499999999999</v>
+        <v>1.3855212742120202</v>
       </c>
       <c r="M30">
-        <v>0.44728008221576948</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P30" t="s">
         <v>182</v>
       </c>
       <c r="Q30" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="R30" t="s">
-        <v>566</v>
+        <v>538</v>
       </c>
       <c r="S30" t="s">
         <v>10</v>
@@ -9391,10 +8965,10 @@
         <v>186</v>
       </c>
       <c r="X30" t="s">
-        <v>565</v>
+        <v>537</v>
       </c>
       <c r="Y30" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z30">
         <v>6.6375000000000002</v>
@@ -9411,10 +8985,10 @@
         <v>182</v>
       </c>
       <c r="C31" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -9429,16 +9003,16 @@
         <v>186</v>
       </c>
       <c r="J31" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="K31" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L31">
-        <v>4.3147500000000001</v>
+        <v>0.94391071885781108</v>
       </c>
       <c r="M31">
-        <v>0.43447773296025288</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -9447,10 +9021,10 @@
         <v>182</v>
       </c>
       <c r="Q31" t="s">
-        <v>567</v>
+        <v>539</v>
       </c>
       <c r="R31" t="s">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="S31" t="s">
         <v>10</v>
@@ -9465,10 +9039,10 @@
         <v>186</v>
       </c>
       <c r="X31" t="s">
-        <v>567</v>
+        <v>539</v>
       </c>
       <c r="Y31" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z31">
         <v>12.063750000000001</v>
@@ -9485,10 +9059,10 @@
         <v>182</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -9503,28 +9077,28 @@
         <v>186</v>
       </c>
       <c r="J32" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="K32" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L32">
-        <v>6.3097500000000002</v>
+        <v>3.9527508633093529</v>
       </c>
       <c r="M32">
-        <v>0.43159159220331572</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P32" t="s">
         <v>182</v>
       </c>
       <c r="Q32" t="s">
-        <v>569</v>
+        <v>541</v>
       </c>
       <c r="R32" t="s">
-        <v>570</v>
+        <v>542</v>
       </c>
       <c r="S32" t="s">
         <v>10</v>
@@ -9539,10 +9113,10 @@
         <v>186</v>
       </c>
       <c r="X32" t="s">
-        <v>569</v>
+        <v>541</v>
       </c>
       <c r="Y32" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z32">
         <v>2.8424999999999998</v>
@@ -9559,10 +9133,10 @@
         <v>182</v>
       </c>
       <c r="C33" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D33" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -9577,28 +9151,28 @@
         <v>186</v>
       </c>
       <c r="J33" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="K33" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L33">
-        <v>6.2902500000000003</v>
+        <v>5.0086472477064214</v>
       </c>
       <c r="M33">
-        <v>0.41804908680458552</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" t="s">
         <v>182</v>
       </c>
       <c r="Q33" t="s">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="R33" t="s">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="S33" t="s">
         <v>10</v>
@@ -9613,10 +9187,10 @@
         <v>186</v>
       </c>
       <c r="X33" t="s">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="Y33" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z33">
         <v>0.11874999999999999</v>
@@ -9633,10 +9207,10 @@
         <v>182</v>
       </c>
       <c r="C34" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -9651,46 +9225,46 @@
         <v>186</v>
       </c>
       <c r="J34" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="K34" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L34">
-        <v>7.9312500000000004</v>
+        <v>4.4937013078329349</v>
       </c>
       <c r="M34">
-        <v>0.41321055018703212</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34" t="s">
         <v>182</v>
       </c>
       <c r="Q34" t="s">
+        <v>545</v>
+      </c>
+      <c r="R34" t="s">
+        <v>546</v>
+      </c>
+      <c r="S34" t="s">
+        <v>10</v>
+      </c>
+      <c r="T34" t="s">
+        <v>21</v>
+      </c>
+      <c r="U34" t="s">
+        <v>185</v>
+      </c>
+      <c r="V34" t="s">
+        <v>186</v>
+      </c>
+      <c r="X34" t="s">
+        <v>545</v>
+      </c>
+      <c r="Y34" t="s">
         <v>573</v>
-      </c>
-      <c r="R34" t="s">
-        <v>574</v>
-      </c>
-      <c r="S34" t="s">
-        <v>10</v>
-      </c>
-      <c r="T34" t="s">
-        <v>21</v>
-      </c>
-      <c r="U34" t="s">
-        <v>185</v>
-      </c>
-      <c r="V34" t="s">
-        <v>186</v>
-      </c>
-      <c r="X34" t="s">
-        <v>573</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>601</v>
       </c>
       <c r="Z34">
         <v>10.682499999999999</v>
@@ -9707,10 +9281,10 @@
         <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D35" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -9725,28 +9299,28 @@
         <v>186</v>
       </c>
       <c r="J35" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="K35" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L35">
-        <v>7.54575</v>
+        <v>5.0095686646967783</v>
       </c>
       <c r="M35">
-        <v>0.41233198565551887</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" t="s">
         <v>182</v>
       </c>
       <c r="Q35" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="R35" t="s">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="S35" t="s">
         <v>10</v>
@@ -9761,10 +9335,10 @@
         <v>186</v>
       </c>
       <c r="X35" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="Y35" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z35">
         <v>5.9212499999999997</v>
@@ -9781,10 +9355,10 @@
         <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -9799,28 +9373,28 @@
         <v>186</v>
       </c>
       <c r="J36" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="K36" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L36">
-        <v>6.3307500000000001</v>
+        <v>3.416737782360558</v>
       </c>
       <c r="M36">
-        <v>0.40294995999097311</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P36" t="s">
         <v>182</v>
       </c>
       <c r="Q36" t="s">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="R36" t="s">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="S36" t="s">
         <v>10</v>
@@ -9835,10 +9409,10 @@
         <v>186</v>
       </c>
       <c r="X36" t="s">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="Y36" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z36">
         <v>2.61375</v>
@@ -9855,10 +9429,10 @@
         <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="D37" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -9873,28 +9447,28 @@
         <v>186</v>
       </c>
       <c r="J37" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="K37" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L37">
-        <v>3.75</v>
+        <v>4.8593444496597042</v>
       </c>
       <c r="M37">
-        <v>0.39697151968295202</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P37" t="s">
         <v>182</v>
       </c>
       <c r="Q37" t="s">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="R37" t="s">
-        <v>580</v>
+        <v>552</v>
       </c>
       <c r="S37" t="s">
         <v>10</v>
@@ -9909,10 +9483,10 @@
         <v>186</v>
       </c>
       <c r="X37" t="s">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="Y37" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z37">
         <v>3.9175</v>
@@ -9929,10 +9503,10 @@
         <v>182</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="D38" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -9947,28 +9521,28 @@
         <v>186</v>
       </c>
       <c r="J38" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="K38" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L38">
-        <v>6.7619999999999996</v>
+        <v>10.368566720583351</v>
       </c>
       <c r="M38">
-        <v>0.39521220594388218</v>
+        <v>0.38900588095273092</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38" t="s">
         <v>182</v>
       </c>
       <c r="Q38" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="R38" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
       <c r="S38" t="s">
         <v>10</v>
@@ -9983,10 +9557,10 @@
         <v>186</v>
       </c>
       <c r="X38" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="Y38" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z38">
         <v>1.0075000000000001</v>
@@ -10003,10 +9577,10 @@
         <v>182</v>
       </c>
       <c r="C39" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="D39" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -10021,28 +9595,28 @@
         <v>186</v>
       </c>
       <c r="J39" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="K39" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L39">
-        <v>2.4224999999999999</v>
+        <v>4.884892809638619</v>
       </c>
       <c r="M39">
-        <v>0.39414986229971999</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P39" t="s">
         <v>182</v>
       </c>
       <c r="Q39" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="R39" t="s">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="S39" t="s">
         <v>10</v>
@@ -10057,10 +9631,10 @@
         <v>186</v>
       </c>
       <c r="X39" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="Y39" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z39">
         <v>0.58250000000000002</v>
@@ -10077,10 +9651,10 @@
         <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D40" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -10095,28 +9669,28 @@
         <v>186</v>
       </c>
       <c r="J40" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="K40" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L40">
-        <v>7.7835000000000001</v>
+        <v>2.5383421781044189</v>
       </c>
       <c r="M40">
-        <v>0.38201746921684659</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P40" t="s">
         <v>182</v>
       </c>
       <c r="Q40" t="s">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="R40" t="s">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="S40" t="s">
         <v>10</v>
@@ -10131,10 +9705,10 @@
         <v>186</v>
       </c>
       <c r="X40" t="s">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="Y40" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z40">
         <v>3.7499999999999999E-3</v>
@@ -10151,10 +9725,10 @@
         <v>182</v>
       </c>
       <c r="C41" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -10169,28 +9743,28 @@
         <v>186</v>
       </c>
       <c r="J41" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="K41" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L41">
-        <v>7.9904999999999999</v>
+        <v>4.2242993630573249</v>
       </c>
       <c r="M41">
-        <v>0.37434168064361761</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P41" t="s">
         <v>182</v>
       </c>
       <c r="Q41" t="s">
-        <v>587</v>
+        <v>559</v>
       </c>
       <c r="R41" t="s">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="S41" t="s">
         <v>10</v>
@@ -10205,10 +9779,10 @@
         <v>186</v>
       </c>
       <c r="X41" t="s">
-        <v>587</v>
+        <v>559</v>
       </c>
       <c r="Y41" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z41">
         <v>0.57625000000000004</v>
@@ -10225,10 +9799,10 @@
         <v>182</v>
       </c>
       <c r="C42" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -10243,28 +9817,28 @@
         <v>186</v>
       </c>
       <c r="J42" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="K42" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L42">
-        <v>7.8585000000000003</v>
+        <v>4.8352011138905935</v>
       </c>
       <c r="M42">
-        <v>0.36917162151179039</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P42" t="s">
         <v>182</v>
       </c>
       <c r="Q42" t="s">
-        <v>589</v>
+        <v>561</v>
       </c>
       <c r="R42" t="s">
-        <v>590</v>
+        <v>562</v>
       </c>
       <c r="S42" t="s">
         <v>10</v>
@@ -10279,10 +9853,10 @@
         <v>186</v>
       </c>
       <c r="X42" t="s">
-        <v>589</v>
+        <v>561</v>
       </c>
       <c r="Y42" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z42">
         <v>2.75E-2</v>
@@ -10299,10 +9873,10 @@
         <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -10317,28 +9891,28 @@
         <v>186</v>
       </c>
       <c r="J43" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="K43" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L43">
-        <v>8.3204999999999991</v>
+        <v>4.7590365600332367</v>
       </c>
       <c r="M43">
-        <v>0.36453803340134289</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="N43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P43" t="s">
         <v>182</v>
       </c>
       <c r="Q43" t="s">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="R43" t="s">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="S43" t="s">
         <v>10</v>
@@ -10353,10 +9927,10 @@
         <v>186</v>
       </c>
       <c r="X43" t="s">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="Y43" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z43">
         <v>0.21625</v>
@@ -10373,10 +9947,10 @@
         <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -10391,16 +9965,16 @@
         <v>186</v>
       </c>
       <c r="J44" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="K44" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L44">
-        <v>8.3302499999999995</v>
+        <v>4.864937090544406</v>
       </c>
       <c r="M44">
-        <v>0.36281825576124332</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="N44">
         <v>2</v>
@@ -10409,10 +9983,10 @@
         <v>182</v>
       </c>
       <c r="Q44" t="s">
-        <v>593</v>
+        <v>565</v>
       </c>
       <c r="R44" t="s">
-        <v>594</v>
+        <v>566</v>
       </c>
       <c r="S44" t="s">
         <v>10</v>
@@ -10427,10 +10001,10 @@
         <v>186</v>
       </c>
       <c r="X44" t="s">
-        <v>593</v>
+        <v>565</v>
       </c>
       <c r="Y44" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z44">
         <v>1.7500000000000002E-2</v>
@@ -10447,10 +10021,10 @@
         <v>182</v>
       </c>
       <c r="C45" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -10465,28 +10039,28 @@
         <v>186</v>
       </c>
       <c r="J45" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="K45" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L45">
-        <v>7.11</v>
+        <v>4.994320411537756</v>
       </c>
       <c r="M45">
-        <v>0.36076949931521968</v>
+        <v>0.376</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P45" t="s">
         <v>182</v>
       </c>
       <c r="Q45" t="s">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="R45" t="s">
-        <v>596</v>
+        <v>568</v>
       </c>
       <c r="S45" t="s">
         <v>10</v>
@@ -10501,10 +10075,10 @@
         <v>186</v>
       </c>
       <c r="X45" t="s">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="Y45" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z45">
         <v>5.0000000000000001E-3</v>
@@ -10521,10 +10095,10 @@
         <v>182</v>
       </c>
       <c r="C46" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -10539,28 +10113,28 @@
         <v>186</v>
       </c>
       <c r="J46" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="K46" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L46">
-        <v>7.9522500000000003</v>
+        <v>5.0295832058946193</v>
       </c>
       <c r="M46">
-        <v>0.3503211333347076</v>
+        <v>0.375</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P46" t="s">
         <v>182</v>
       </c>
       <c r="Q46" t="s">
-        <v>597</v>
+        <v>569</v>
       </c>
       <c r="R46" t="s">
-        <v>598</v>
+        <v>570</v>
       </c>
       <c r="S46" t="s">
         <v>10</v>
@@ -10575,10 +10149,10 @@
         <v>186</v>
       </c>
       <c r="X46" t="s">
-        <v>597</v>
+        <v>569</v>
       </c>
       <c r="Y46" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z46">
         <v>0.33500000000000002</v>
@@ -10595,10 +10169,10 @@
         <v>182</v>
       </c>
       <c r="C47" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -10613,28 +10187,28 @@
         <v>186</v>
       </c>
       <c r="J47" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="K47" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L47">
-        <v>8.2560000000000002</v>
+        <v>10.262704387859074</v>
       </c>
       <c r="M47">
-        <v>0.34982996232856922</v>
+        <v>0.37051326021922154</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P47" t="s">
         <v>182</v>
       </c>
       <c r="Q47" t="s">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="R47" t="s">
-        <v>600</v>
+        <v>572</v>
       </c>
       <c r="S47" t="s">
         <v>10</v>
@@ -10649,10 +10223,10 @@
         <v>186</v>
       </c>
       <c r="X47" t="s">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="Y47" t="s">
-        <v>601</v>
+        <v>573</v>
       </c>
       <c r="Z47">
         <v>1.125E-2</v>
@@ -10669,10 +10243,10 @@
         <v>182</v>
       </c>
       <c r="C48" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="D48" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -10687,19 +10261,19 @@
         <v>186</v>
       </c>
       <c r="J48" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="K48" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L48">
-        <v>6.9974999999999996</v>
+        <v>3.8112316593784894</v>
       </c>
       <c r="M48">
-        <v>0.3472447936452937</v>
+        <v>0.37</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="2:14">
@@ -10707,10 +10281,10 @@
         <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="D49" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -10725,19 +10299,19 @@
         <v>186</v>
       </c>
       <c r="J49" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="K49" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L49">
-        <v>8.2560000000000002</v>
+        <v>4.9665134770262096</v>
       </c>
       <c r="M49">
-        <v>0.3460630650440007</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:14">
@@ -10745,10 +10319,10 @@
         <v>182</v>
       </c>
       <c r="C50" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -10763,19 +10337,19 @@
         <v>186</v>
       </c>
       <c r="J50" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="K50" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L50">
-        <v>7.6604999999999999</v>
+        <v>5.1121834784511249</v>
       </c>
       <c r="M50">
-        <v>0.34578516432535861</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="2:14">
@@ -10783,10 +10357,10 @@
         <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -10801,19 +10375,19 @@
         <v>186</v>
       </c>
       <c r="J51" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="K51" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L51">
-        <v>15.265499999999999</v>
+        <v>5.0653150350969742</v>
       </c>
       <c r="M51">
-        <v>0.34285342473994845</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="2:14">
@@ -10821,10 +10395,10 @@
         <v>182</v>
       </c>
       <c r="C52" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="D52" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -10839,16 +10413,16 @@
         <v>186</v>
       </c>
       <c r="J52" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="K52" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L52">
-        <v>16.202249999999999</v>
+        <v>4.2794182124410511</v>
       </c>
       <c r="M52">
-        <v>0.34279298051743229</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -10859,10 +10433,10 @@
         <v>182</v>
       </c>
       <c r="C53" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="D53" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -10877,16 +10451,16 @@
         <v>186</v>
       </c>
       <c r="J53" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="K53" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L53">
-        <v>16.576499999999999</v>
+        <v>4.9670647324483372</v>
       </c>
       <c r="M53">
-        <v>0.34157478585116785</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="N53">
         <v>2</v>
@@ -10897,10 +10471,10 @@
         <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="D54" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
@@ -10915,19 +10489,19 @@
         <v>186</v>
       </c>
       <c r="J54" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="K54" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L54">
-        <v>8.3204999999999991</v>
+        <v>5.0659056138954517</v>
       </c>
       <c r="M54">
-        <v>0.3380798122756935</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="2:14">
@@ -10935,10 +10509,10 @@
         <v>182</v>
       </c>
       <c r="C55" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="D55" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
@@ -10953,19 +10527,19 @@
         <v>186</v>
       </c>
       <c r="J55" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="K55" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L55">
-        <v>8.2560000000000002</v>
+        <v>4.851944576116682</v>
       </c>
       <c r="M55">
-        <v>0.33565465890466423</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="N55">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:14">
@@ -10973,10 +10547,10 @@
         <v>182</v>
       </c>
       <c r="C56" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="D56" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -10991,16 +10565,16 @@
         <v>186</v>
       </c>
       <c r="J56" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="K56" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L56">
-        <v>16.443750000000001</v>
+        <v>4.9779003558185355</v>
       </c>
       <c r="M56">
-        <v>0.33229672875683269</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="N56">
         <v>3</v>
@@ -11011,10 +10585,10 @@
         <v>182</v>
       </c>
       <c r="C57" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="D57" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -11029,19 +10603,19 @@
         <v>186</v>
       </c>
       <c r="J57" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="K57" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L57">
-        <v>15.8925</v>
+        <v>4.9455560929732627</v>
       </c>
       <c r="M57">
-        <v>0.33167178517132029</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="N57">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="2:14">
@@ -11049,10 +10623,10 @@
         <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D58" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -11067,19 +10641,19 @@
         <v>186</v>
       </c>
       <c r="J58" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="K58" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L58">
-        <v>16.356000000000002</v>
+        <v>0.93356002702813012</v>
       </c>
       <c r="M58">
-        <v>0.33102079357943931</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="2:14">
@@ -11087,10 +10661,10 @@
         <v>182</v>
       </c>
       <c r="C59" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="D59" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -11105,16 +10679,16 @@
         <v>186</v>
       </c>
       <c r="J59" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="K59" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L59">
-        <v>16.608000000000001</v>
+        <v>4.8624568965517234</v>
       </c>
       <c r="M59">
-        <v>0.33073003868744016</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="N59">
         <v>4</v>
@@ -11125,10 +10699,10 @@
         <v>182</v>
       </c>
       <c r="C60" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="D60" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -11143,19 +10717,19 @@
         <v>186</v>
       </c>
       <c r="J60" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="K60" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L60">
-        <v>16.440000000000001</v>
+        <v>4.9143760952594917</v>
       </c>
       <c r="M60">
-        <v>0.32928205462055127</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -11163,10 +10737,10 @@
         <v>182</v>
       </c>
       <c r="C61" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="D61" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -11181,19 +10755,19 @@
         <v>186</v>
       </c>
       <c r="J61" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="K61" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L61">
-        <v>8.4172499999999992</v>
+        <v>4.7878806570483601</v>
       </c>
       <c r="M61">
-        <v>0.3248909103796751</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -11201,10 +10775,10 @@
         <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="D62" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -11219,19 +10793,19 @@
         <v>186</v>
       </c>
       <c r="J62" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="K62" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L62">
-        <v>8.3204999999999991</v>
+        <v>4.8613650595423934</v>
       </c>
       <c r="M62">
-        <v>0.32233893827024601</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -11239,10 +10813,10 @@
         <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="D63" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -11257,19 +10831,19 @@
         <v>186</v>
       </c>
       <c r="J63" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="K63" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L63">
-        <v>16.494</v>
+        <v>4.0865774761939289</v>
       </c>
       <c r="M63">
-        <v>0.322297171768758</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -11277,10 +10851,10 @@
         <v>182</v>
       </c>
       <c r="C64" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="D64" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -11295,19 +10869,19 @@
         <v>186</v>
       </c>
       <c r="J64" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="K64" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L64">
-        <v>8.3940000000000001</v>
+        <v>4.9213123608204397</v>
       </c>
       <c r="M64">
-        <v>0.32000561918811909</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="2:14">
@@ -11315,10 +10889,10 @@
         <v>182</v>
       </c>
       <c r="C65" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="D65" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -11333,19 +10907,19 @@
         <v>186</v>
       </c>
       <c r="J65" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="K65" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L65">
-        <v>8.2822499999999994</v>
+        <v>4.9542152822842311</v>
       </c>
       <c r="M65">
-        <v>0.31646037881333522</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="2:14">
@@ -11353,10 +10927,10 @@
         <v>182</v>
       </c>
       <c r="C66" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="D66" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -11371,19 +10945,19 @@
         <v>186</v>
       </c>
       <c r="J66" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="K66" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L66">
-        <v>7.9522500000000003</v>
+        <v>4.8438766478279671</v>
       </c>
       <c r="M66">
-        <v>0.3136383423020469</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="2:14">
@@ -11391,10 +10965,10 @@
         <v>182</v>
       </c>
       <c r="C67" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="D67" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -11409,19 +10983,19 @@
         <v>186</v>
       </c>
       <c r="J67" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="K67" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L67">
-        <v>16.361249999999998</v>
+        <v>4.8096304762365536</v>
       </c>
       <c r="M67">
-        <v>0.31030291584078723</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="2:14">
@@ -11429,10 +11003,10 @@
         <v>182</v>
       </c>
       <c r="C68" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D68" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -11447,19 +11021,19 @@
         <v>186</v>
       </c>
       <c r="J68" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="K68" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L68">
-        <v>16.737749999999998</v>
+        <v>5.3252175859598845</v>
       </c>
       <c r="M68">
-        <v>0.30928380343691669</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="2:14">
@@ -11467,10 +11041,10 @@
         <v>182</v>
       </c>
       <c r="C69" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D69" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -11485,19 +11059,19 @@
         <v>186</v>
       </c>
       <c r="J69" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="K69" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L69">
-        <v>8.2702500000000008</v>
+        <v>4.8907163236881939</v>
       </c>
       <c r="M69">
-        <v>0.30647247396222338</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="2:14">
@@ -11505,10 +11079,10 @@
         <v>182</v>
       </c>
       <c r="C70" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="D70" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -11523,19 +11097,19 @@
         <v>186</v>
       </c>
       <c r="J70" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="K70" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L70">
-        <v>8.2560000000000002</v>
+        <v>10.947911509682086</v>
       </c>
       <c r="M70">
-        <v>0.30527266685973509</v>
+        <v>0.32357558385042384</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="2:14">
@@ -11543,10 +11117,10 @@
         <v>182</v>
       </c>
       <c r="C71" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="D71" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
@@ -11561,16 +11135,16 @@
         <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="K71" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L71">
-        <v>16.704000000000001</v>
+        <v>15.156868040079724</v>
       </c>
       <c r="M71">
-        <v>0.30271532050989003</v>
+        <v>0.3226777076281595</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -11581,10 +11155,10 @@
         <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D72" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -11599,16 +11173,16 @@
         <v>186</v>
       </c>
       <c r="J72" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="K72" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L72">
-        <v>15.920249999999999</v>
+        <v>9.3788751439971421</v>
       </c>
       <c r="M72">
-        <v>0.30221899176191497</v>
+        <v>0.32000171858046994</v>
       </c>
       <c r="N72">
         <v>3</v>
@@ -11619,10 +11193,10 @@
         <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="D73" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -11637,19 +11211,19 @@
         <v>186</v>
       </c>
       <c r="J73" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="K73" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L73">
-        <v>16.427250000000001</v>
+        <v>9.379403694701411</v>
       </c>
       <c r="M73">
-        <v>0.30209248954799067</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="2:14">
@@ -11657,10 +11231,10 @@
         <v>182</v>
       </c>
       <c r="C74" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D74" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
@@ -11675,16 +11249,16 @@
         <v>186</v>
       </c>
       <c r="J74" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="K74" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L74">
-        <v>8.3977500000000003</v>
+        <v>11.036952771537861</v>
       </c>
       <c r="M74">
-        <v>0.30123828002817632</v>
+        <v>0.31650975182315566</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -11695,10 +11269,10 @@
         <v>182</v>
       </c>
       <c r="C75" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="D75" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -11713,19 +11287,19 @@
         <v>186</v>
       </c>
       <c r="J75" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K75" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L75">
-        <v>8.0084999999999997</v>
+        <v>9.2537084879455112</v>
       </c>
       <c r="M75">
-        <v>0.2956005552279718</v>
+        <v>0.31301609570896388</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="2:14">
@@ -11733,10 +11307,10 @@
         <v>182</v>
       </c>
       <c r="C76" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D76" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
@@ -11751,19 +11325,19 @@
         <v>186</v>
       </c>
       <c r="J76" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="K76" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L76">
-        <v>15.19425</v>
+        <v>10.57589864275476</v>
       </c>
       <c r="M76">
-        <v>0.2921506139120435</v>
+        <v>0.31244556074751012</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="2:14">
@@ -11771,10 +11345,10 @@
         <v>182</v>
       </c>
       <c r="C77" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="D77" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -11789,19 +11363,19 @@
         <v>186</v>
       </c>
       <c r="J77" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="K77" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L77">
-        <v>16.007999999999999</v>
+        <v>4.5845280146163221</v>
       </c>
       <c r="M77">
-        <v>0.29125451946762304</v>
+        <v>0.308</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="2:14">
@@ -11809,10 +11383,10 @@
         <v>182</v>
       </c>
       <c r="C78" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D78" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -11827,19 +11401,19 @@
         <v>186</v>
       </c>
       <c r="J78" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="K78" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L78">
-        <v>16.265999999999998</v>
+        <v>4.6545121707814463</v>
       </c>
       <c r="M78">
-        <v>0.29059087096714503</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="N78">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="2:14">
@@ -11847,10 +11421,10 @@
         <v>182</v>
       </c>
       <c r="C79" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="D79" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -11865,16 +11439,16 @@
         <v>186</v>
       </c>
       <c r="J79" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="K79" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L79">
-        <v>8.2560000000000002</v>
+        <v>4.0542812473136758</v>
       </c>
       <c r="M79">
-        <v>0.28641433365004793</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -11885,10 +11459,10 @@
         <v>182</v>
       </c>
       <c r="C80" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="D80" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -11903,19 +11477,19 @@
         <v>186</v>
       </c>
       <c r="J80" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="K80" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L80">
-        <v>8.2560000000000002</v>
+        <v>5.1889235567804528</v>
       </c>
       <c r="M80">
-        <v>0.28531699904219149</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="2:14">
@@ -11923,10 +11497,10 @@
         <v>182</v>
       </c>
       <c r="C81" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="D81" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -11941,19 +11515,19 @@
         <v>186</v>
       </c>
       <c r="J81" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="K81" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L81">
-        <v>24.786000000000001</v>
+        <v>8.883595826171728</v>
       </c>
       <c r="M81">
-        <v>0.28197110055070385</v>
+        <v>0.30152164728516667</v>
       </c>
       <c r="N81">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="2:14">
@@ -11961,10 +11535,10 @@
         <v>182</v>
       </c>
       <c r="C82" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D82" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -11979,19 +11553,19 @@
         <v>186</v>
       </c>
       <c r="J82" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="K82" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L82">
-        <v>16.512</v>
+        <v>9.1462487058296862</v>
       </c>
       <c r="M82">
-        <v>0.28085097369955403</v>
+        <v>0.3004950473117774</v>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="2:14">
@@ -11999,10 +11573,10 @@
         <v>182</v>
       </c>
       <c r="C83" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="D83" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -12017,19 +11591,19 @@
         <v>186</v>
       </c>
       <c r="J83" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="K83" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L83">
-        <v>15.9975</v>
+        <v>5.2813291256599371</v>
       </c>
       <c r="M83">
-        <v>0.28005162341503592</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="N83">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="2:14">
@@ -12037,10 +11611,10 @@
         <v>182</v>
       </c>
       <c r="C84" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D84" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -12055,19 +11629,19 @@
         <v>186</v>
       </c>
       <c r="J84" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="K84" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L84">
-        <v>16.191749999999999</v>
+        <v>5.9115072899602676</v>
       </c>
       <c r="M84">
-        <v>0.27959436616938216</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="N84">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="2:14">
@@ -12075,10 +11649,10 @@
         <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="D85" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -12093,19 +11667,19 @@
         <v>186</v>
       </c>
       <c r="J85" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="K85" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L85">
-        <v>16.22325</v>
+        <v>8.7820183107080148</v>
       </c>
       <c r="M85">
-        <v>0.27902728741545046</v>
+        <v>0.2919819966082256</v>
       </c>
       <c r="N85">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="2:14">
@@ -12113,10 +11687,10 @@
         <v>182</v>
       </c>
       <c r="C86" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D86" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -12131,19 +11705,19 @@
         <v>186</v>
       </c>
       <c r="J86" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="K86" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L86">
-        <v>15.27825</v>
+        <v>8.7472121213954797</v>
       </c>
       <c r="M86">
-        <v>0.27320894570623816</v>
+        <v>0.29148660942592647</v>
       </c>
       <c r="N86">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="2:14">
@@ -12151,10 +11725,10 @@
         <v>182</v>
       </c>
       <c r="C87" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D87" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -12169,19 +11743,19 @@
         <v>186</v>
       </c>
       <c r="J87" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="K87" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L87">
-        <v>16.188749999999999</v>
+        <v>8.8559922267903239</v>
       </c>
       <c r="M87">
-        <v>0.27139263711887346</v>
+        <v>0.2891569021304003</v>
       </c>
       <c r="N87">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="2:14">
@@ -12189,10 +11763,10 @@
         <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="D88" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -12207,19 +11781,19 @@
         <v>186</v>
       </c>
       <c r="J88" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K88" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L88">
-        <v>24.497250000000001</v>
+        <v>5.4957336161516137</v>
       </c>
       <c r="M88">
-        <v>0.27001044045013539</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="N88">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="2:14">
@@ -12227,10 +11801,10 @@
         <v>182</v>
       </c>
       <c r="C89" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="D89" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -12245,19 +11819,19 @@
         <v>186</v>
       </c>
       <c r="J89" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="K89" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L89">
-        <v>24.4725</v>
+        <v>4.5381100825646259</v>
       </c>
       <c r="M89">
-        <v>0.26832787025108823</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="2:14">
@@ -12265,10 +11839,10 @@
         <v>182</v>
       </c>
       <c r="C90" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="D90" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -12283,16 +11857,16 @@
         <v>186</v>
       </c>
       <c r="J90" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="K90" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L90">
-        <v>24.669750000000001</v>
+        <v>6.8389936670565934</v>
       </c>
       <c r="M90">
-        <v>0.26785881678952761</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="N90">
         <v>3</v>
@@ -12303,10 +11877,10 @@
         <v>182</v>
       </c>
       <c r="C91" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="D91" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -12321,16 +11895,16 @@
         <v>186</v>
       </c>
       <c r="J91" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="K91" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L91">
-        <v>16.286999999999999</v>
+        <v>8.5542689256619457</v>
       </c>
       <c r="M91">
-        <v>0.26358218830149871</v>
+        <v>0.28349734078055322</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -12341,10 +11915,10 @@
         <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="D92" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -12359,19 +11933,19 @@
         <v>186</v>
       </c>
       <c r="J92" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="K92" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L92">
-        <v>7.9237500000000001</v>
+        <v>8.8196363168443597</v>
       </c>
       <c r="M92">
-        <v>0.26353984242186729</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="N92">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="2:14">
@@ -12379,10 +11953,10 @@
         <v>182</v>
       </c>
       <c r="C93" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D93" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -12397,19 +11971,19 @@
         <v>186</v>
       </c>
       <c r="J93" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="K93" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L93">
-        <v>16.806000000000001</v>
+        <v>7.2570352571720447</v>
       </c>
       <c r="M93">
-        <v>0.26103897642935076</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="2:14">
@@ -12417,10 +11991,10 @@
         <v>182</v>
       </c>
       <c r="C94" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="D94" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -12435,19 +12009,19 @@
         <v>186</v>
       </c>
       <c r="J94" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="K94" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L94">
-        <v>8.3122500000000006</v>
+        <v>4.8405906082909169</v>
       </c>
       <c r="M94">
-        <v>0.26017150954454588</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="N94">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="2:14">
@@ -12455,10 +12029,10 @@
         <v>182</v>
       </c>
       <c r="C95" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="D95" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -12473,19 +12047,19 @@
         <v>186</v>
       </c>
       <c r="J95" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="K95" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L95">
-        <v>8.2447499999999998</v>
+        <v>9.3287996709345613</v>
       </c>
       <c r="M95">
-        <v>0.25624716754528271</v>
+        <v>0.27199999999999996</v>
       </c>
       <c r="N95">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="2:14">
@@ -12493,10 +12067,10 @@
         <v>182</v>
       </c>
       <c r="C96" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="D96" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -12511,19 +12085,19 @@
         <v>186</v>
       </c>
       <c r="J96" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="K96" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L96">
-        <v>8.3190000000000008</v>
+        <v>11.210608005261635</v>
       </c>
       <c r="M96">
-        <v>0.25437685697328188</v>
+        <v>0.27169029267377787</v>
       </c>
       <c r="N96">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="2:14">
@@ -12531,10 +12105,10 @@
         <v>182</v>
       </c>
       <c r="C97" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="D97" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -12549,19 +12123,19 @@
         <v>186</v>
       </c>
       <c r="J97" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="K97" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L97">
-        <v>8.3520000000000003</v>
+        <v>10.243936168565069</v>
       </c>
       <c r="M97">
-        <v>0.25033910336926979</v>
+        <v>0.26963893884660473</v>
       </c>
       <c r="N97">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="2:14">
@@ -12569,10 +12143,10 @@
         <v>182</v>
       </c>
       <c r="C98" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="D98" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -12587,19 +12161,19 @@
         <v>186</v>
       </c>
       <c r="J98" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="K98" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L98">
-        <v>16.623750000000001</v>
+        <v>5.8285641113784807</v>
       </c>
       <c r="M98">
-        <v>0.25016385744889219</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="2:14">
@@ -12607,10 +12181,10 @@
         <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="D99" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -12625,19 +12199,19 @@
         <v>186</v>
       </c>
       <c r="J99" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="K99" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L99">
-        <v>16.6035</v>
+        <v>11.80572716941902</v>
       </c>
       <c r="M99">
-        <v>0.24992012655828535</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="2:14">
@@ -12645,10 +12219,10 @@
         <v>182</v>
       </c>
       <c r="C100" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="D100" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -12663,19 +12237,19 @@
         <v>186</v>
       </c>
       <c r="J100" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="K100" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L100">
-        <v>8.1412499999999994</v>
+        <v>10.300282496826917</v>
       </c>
       <c r="M100">
-        <v>0.24866879062703021</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="N100">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:14">
@@ -12683,10 +12257,10 @@
         <v>182</v>
       </c>
       <c r="C101" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="D101" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -12701,19 +12275,19 @@
         <v>186</v>
       </c>
       <c r="J101" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="K101" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L101">
-        <v>8.2334999999999994</v>
+        <v>13.116020331258497</v>
       </c>
       <c r="M101">
-        <v>0.24453800228933559</v>
+        <v>0.26160113955177522</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="2:14">
@@ -12721,10 +12295,10 @@
         <v>182</v>
       </c>
       <c r="C102" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D102" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -12739,19 +12313,19 @@
         <v>186</v>
       </c>
       <c r="J102" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="K102" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L102">
-        <v>8.4120000000000008</v>
+        <v>11.241985870961329</v>
       </c>
       <c r="M102">
-        <v>0.23431152599072719</v>
+        <v>0.2613580906125238</v>
       </c>
       <c r="N102">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="2:14">
@@ -12759,10 +12333,10 @@
         <v>182</v>
       </c>
       <c r="C103" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="D103" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -12777,19 +12351,19 @@
         <v>186</v>
       </c>
       <c r="J103" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="K103" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L103">
-        <v>16.50675</v>
+        <v>11.075096855096069</v>
       </c>
       <c r="M103">
-        <v>0.2332613701270935</v>
+        <v>0.25970490363192827</v>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="2:14">
@@ -12797,10 +12371,10 @@
         <v>182</v>
       </c>
       <c r="C104" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D104" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -12815,19 +12389,19 @@
         <v>186</v>
       </c>
       <c r="J104" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="K104" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L104">
-        <v>16.8</v>
+        <v>5.6165998996393229</v>
       </c>
       <c r="M104">
-        <v>0.2314743086100115</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="N104">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="2:14">
@@ -12835,10 +12409,10 @@
         <v>182</v>
       </c>
       <c r="C105" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="D105" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -12853,19 +12427,19 @@
         <v>186</v>
       </c>
       <c r="J105" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="K105" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L105">
-        <v>16.560749999999999</v>
+        <v>4.5110170134884706</v>
       </c>
       <c r="M105">
-        <v>0.22753233900315215</v>
+        <v>0.254</v>
       </c>
       <c r="N105">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="2:14">
@@ -12873,10 +12447,10 @@
         <v>182</v>
       </c>
       <c r="C106" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="D106" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -12891,19 +12465,19 @@
         <v>186</v>
       </c>
       <c r="J106" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="K106" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L106">
-        <v>16.834499999999998</v>
+        <v>5.7764433098643861</v>
       </c>
       <c r="M106">
-        <v>0.22595625908105055</v>
+        <v>0.252</v>
       </c>
       <c r="N106">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="2:14">
@@ -12911,10 +12485,10 @@
         <v>182</v>
       </c>
       <c r="C107" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="D107" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -12929,19 +12503,19 @@
         <v>186</v>
       </c>
       <c r="J107" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="K107" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L107">
-        <v>16.22475</v>
+        <v>5.5177612223893595</v>
       </c>
       <c r="M107">
-        <v>0.22244751832298354</v>
+        <v>0.252</v>
       </c>
       <c r="N107">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="2:14">
@@ -12949,10 +12523,10 @@
         <v>182</v>
       </c>
       <c r="C108" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="D108" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
@@ -12967,19 +12541,19 @@
         <v>186</v>
       </c>
       <c r="J108" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="K108" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L108">
-        <v>8.2784999999999993</v>
+        <v>6.4809362742382701</v>
       </c>
       <c r="M108">
-        <v>0.2213539932129876</v>
+        <v>0.251</v>
       </c>
       <c r="N108">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="2:14">
@@ -12987,10 +12561,10 @@
         <v>182</v>
       </c>
       <c r="C109" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="D109" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -13005,19 +12579,19 @@
         <v>186</v>
       </c>
       <c r="J109" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="K109" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L109">
-        <v>16.131</v>
+        <v>4.9162836926193423</v>
       </c>
       <c r="M109">
-        <v>0.21900587927997026</v>
+        <v>0.245</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="2:14">
@@ -13025,10 +12599,10 @@
         <v>182</v>
       </c>
       <c r="C110" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="D110" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
@@ -13043,16 +12617,16 @@
         <v>186</v>
       </c>
       <c r="J110" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="K110" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L110">
-        <v>16.48875</v>
+        <v>12.461581781258454</v>
       </c>
       <c r="M110">
-        <v>0.21846639115997579</v>
+        <v>0.24166985856757878</v>
       </c>
       <c r="N110">
         <v>2</v>
@@ -13063,10 +12637,10 @@
         <v>182</v>
       </c>
       <c r="C111" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="D111" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -13081,19 +12655,19 @@
         <v>186</v>
       </c>
       <c r="J111" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="K111" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L111">
-        <v>8.4172499999999992</v>
+        <v>8.5476117597164016</v>
       </c>
       <c r="M111">
-        <v>0.217092880817122</v>
+        <v>0.23946785129309572</v>
       </c>
       <c r="N111">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="2:14">
@@ -13101,10 +12675,10 @@
         <v>182</v>
       </c>
       <c r="C112" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D112" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
@@ -13119,19 +12693,19 @@
         <v>186</v>
       </c>
       <c r="J112" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="K112" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L112">
-        <v>16.253250000000001</v>
+        <v>11.836128067739212</v>
       </c>
       <c r="M112">
-        <v>0.21300171263089362</v>
+        <v>0.23551027631933105</v>
       </c>
       <c r="N112">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="2:14">
@@ -13139,10 +12713,10 @@
         <v>182</v>
       </c>
       <c r="C113" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="D113" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -13157,19 +12731,19 @@
         <v>186</v>
       </c>
       <c r="J113" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="K113" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L113">
-        <v>8.1487499999999997</v>
+        <v>10.829302216902397</v>
       </c>
       <c r="M113">
-        <v>0.21070878780867561</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="2:14">
@@ -13177,10 +12751,10 @@
         <v>182</v>
       </c>
       <c r="C114" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="D114" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -13195,19 +12769,19 @@
         <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="K114" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L114">
-        <v>8.3684999999999992</v>
+        <v>6.1020172586244481</v>
       </c>
       <c r="M114">
-        <v>0.2085778275618437</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="N114">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="2:14">
@@ -13215,10 +12789,10 @@
         <v>182</v>
       </c>
       <c r="C115" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D115" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -13233,19 +12807,19 @@
         <v>186</v>
       </c>
       <c r="J115" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="K115" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L115">
-        <v>7.7519999999999998</v>
+        <v>5.5224316416039274</v>
       </c>
       <c r="M115">
-        <v>0.20722419775208159</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="N115">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="2:14">
@@ -13253,10 +12827,10 @@
         <v>182</v>
       </c>
       <c r="C116" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="D116" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -13271,19 +12845,19 @@
         <v>186</v>
       </c>
       <c r="J116" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="K116" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L116">
-        <v>8.1517499999999998</v>
+        <v>6.7762483094915744</v>
       </c>
       <c r="M116">
-        <v>0.2069558113847936</v>
+        <v>0.22900000000000004</v>
       </c>
       <c r="N116">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="2:14">
@@ -13291,10 +12865,10 @@
         <v>182</v>
       </c>
       <c r="C117" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="D117" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -13309,19 +12883,19 @@
         <v>186</v>
       </c>
       <c r="J117" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="K117" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L117">
-        <v>8.4112500000000008</v>
+        <v>4.5677412696440225</v>
       </c>
       <c r="M117">
-        <v>0.20417104587625901</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="2:14">
@@ -13329,10 +12903,10 @@
         <v>182</v>
       </c>
       <c r="C118" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="D118" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
@@ -13347,19 +12921,19 @@
         <v>186</v>
       </c>
       <c r="J118" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="K118" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L118">
-        <v>8.3520000000000003</v>
+        <v>4.8943617948361116</v>
       </c>
       <c r="M118">
-        <v>0.20381315305750669</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="2:14">
@@ -13367,10 +12941,10 @@
         <v>182</v>
       </c>
       <c r="C119" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="D119" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
@@ -13385,19 +12959,19 @@
         <v>186</v>
       </c>
       <c r="J119" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="K119" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L119">
-        <v>8.1329999999999991</v>
+        <v>14.484013970800403</v>
       </c>
       <c r="M119">
-        <v>0.19960804861015211</v>
+        <v>0.22285259743445196</v>
       </c>
       <c r="N119">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="2:14">
@@ -13405,10 +12979,10 @@
         <v>182</v>
       </c>
       <c r="C120" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="D120" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
@@ -13423,19 +12997,19 @@
         <v>186</v>
       </c>
       <c r="J120" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="K120" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L120">
-        <v>8.3467500000000001</v>
+        <v>15.306904509089872</v>
       </c>
       <c r="M120">
-        <v>0.1987438354835861</v>
+        <v>0.22105977893047932</v>
       </c>
       <c r="N120">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="2:14">
@@ -13443,10 +13017,10 @@
         <v>182</v>
       </c>
       <c r="C121" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D121" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
@@ -13461,19 +13035,19 @@
         <v>186</v>
       </c>
       <c r="J121" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="K121" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L121">
-        <v>8.1577500000000001</v>
+        <v>14.694629142996705</v>
       </c>
       <c r="M121">
-        <v>0.1954346092831527</v>
+        <v>0.22081668756048034</v>
       </c>
       <c r="N121">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="2:14">
@@ -13481,10 +13055,10 @@
         <v>182</v>
       </c>
       <c r="C122" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="D122" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
@@ -13499,19 +13073,19 @@
         <v>186</v>
       </c>
       <c r="J122" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="K122" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L122">
-        <v>8.4172499999999992</v>
+        <v>14.711329700109928</v>
       </c>
       <c r="M122">
-        <v>0.19307640154597469</v>
+        <v>0.21828144412580569</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="2:14">
@@ -13519,10 +13093,10 @@
         <v>182</v>
       </c>
       <c r="C123" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="D123" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
@@ -13537,19 +13111,19 @@
         <v>186</v>
       </c>
       <c r="J123" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="K123" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L123">
-        <v>8.2530000000000001</v>
+        <v>11.318997585164663</v>
       </c>
       <c r="M123">
-        <v>0.1920373552511174</v>
+        <v>0.21648357291892867</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="2:14">
@@ -13557,10 +13131,10 @@
         <v>182</v>
       </c>
       <c r="C124" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="D124" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
@@ -13575,16 +13149,16 @@
         <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="K124" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L124">
-        <v>8.0145</v>
+        <v>7.2158185827770955</v>
       </c>
       <c r="M124">
-        <v>0.1910895850265463</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -13595,10 +13169,10 @@
         <v>182</v>
       </c>
       <c r="C125" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="D125" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="E125" t="s">
         <v>10</v>
@@ -13613,19 +13187,19 @@
         <v>186</v>
       </c>
       <c r="J125" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="K125" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L125">
-        <v>8.4172499999999992</v>
+        <v>5.2729080193969784</v>
       </c>
       <c r="M125">
-        <v>0.18934356175103029</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="N125">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="2:14">
@@ -13633,10 +13207,10 @@
         <v>182</v>
       </c>
       <c r="C126" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="D126" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
@@ -13651,16 +13225,16 @@
         <v>186</v>
       </c>
       <c r="J126" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="K126" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L126">
-        <v>8.1959999999999997</v>
+        <v>5.1872871755483212</v>
       </c>
       <c r="M126">
-        <v>0.18492326876860271</v>
+        <v>0.21</v>
       </c>
       <c r="N126">
         <v>3</v>
@@ -13671,10 +13245,10 @@
         <v>182</v>
       </c>
       <c r="C127" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="D127" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
@@ -13689,19 +13263,19 @@
         <v>186</v>
       </c>
       <c r="J127" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="K127" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L127">
-        <v>16.204499999999999</v>
+        <v>3.9739696310223738</v>
       </c>
       <c r="M127">
-        <v>0.18328507151636589</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="2:14">
@@ -13709,10 +13283,10 @@
         <v>182</v>
       </c>
       <c r="C128" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="D128" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -13727,19 +13301,19 @@
         <v>186</v>
       </c>
       <c r="J128" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="K128" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L128">
-        <v>16.234500000000001</v>
+        <v>5.7512927167383499</v>
       </c>
       <c r="M128">
-        <v>0.18299240011642368</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="N128">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="2:14">
@@ -13747,10 +13321,10 @@
         <v>182</v>
       </c>
       <c r="C129" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="D129" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
@@ -13765,19 +13339,19 @@
         <v>186</v>
       </c>
       <c r="J129" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="K129" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L129">
-        <v>8.0932499999999994</v>
+        <v>12.232944913795405</v>
       </c>
       <c r="M129">
-        <v>0.1800625315270642</v>
+        <v>0.20254661476397157</v>
       </c>
       <c r="N129">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="2:14">
@@ -13785,10 +13359,10 @@
         <v>182</v>
       </c>
       <c r="C130" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="D130" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
@@ -13803,19 +13377,19 @@
         <v>186</v>
       </c>
       <c r="J130" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="K130" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L130">
-        <v>8.1262500000000006</v>
+        <v>12.427735791628271</v>
       </c>
       <c r="M130">
-        <v>0.17649544137809611</v>
+        <v>0.20130471055462157</v>
       </c>
       <c r="N130">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="2:14">
@@ -13823,10 +13397,10 @@
         <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="D131" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
@@ -13841,19 +13415,19 @@
         <v>186</v>
       </c>
       <c r="J131" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="K131" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L131">
-        <v>8.0954999999999995</v>
+        <v>9.1623368293883836</v>
       </c>
       <c r="M131">
-        <v>0.17322038910379561</v>
+        <v>0.19927632397200792</v>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="2:14">
@@ -13861,10 +13435,10 @@
         <v>182</v>
       </c>
       <c r="C132" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D132" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
@@ -13879,19 +13453,19 @@
         <v>186</v>
       </c>
       <c r="J132" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="K132" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L132">
-        <v>8.0662500000000001</v>
+        <v>9.0572714220328798</v>
       </c>
       <c r="M132">
-        <v>0.17119241346264749</v>
+        <v>0.19644414840968813</v>
       </c>
       <c r="N132">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="2:14">
@@ -13899,10 +13473,10 @@
         <v>182</v>
       </c>
       <c r="C133" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="D133" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -13917,19 +13491,19 @@
         <v>186</v>
       </c>
       <c r="J133" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="K133" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L133">
-        <v>8.3992500000000003</v>
+        <v>8.9663246965978445</v>
       </c>
       <c r="M133">
-        <v>0.1680996609254681</v>
+        <v>0.19554285725274165</v>
       </c>
       <c r="N133">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="2:14">
@@ -13937,10 +13511,10 @@
         <v>182</v>
       </c>
       <c r="C134" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="D134" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -13955,19 +13529,19 @@
         <v>186</v>
       </c>
       <c r="J134" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="K134" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L134">
-        <v>7.8179999999999996</v>
+        <v>6.0178716042520675</v>
       </c>
       <c r="M134">
-        <v>0.16530815223310119</v>
+        <v>0.19</v>
       </c>
       <c r="N134">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="2:14">
@@ -13975,10 +13549,10 @@
         <v>182</v>
       </c>
       <c r="C135" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D135" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -13993,19 +13567,19 @@
         <v>186</v>
       </c>
       <c r="J135" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="K135" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L135">
-        <v>8.2117500000000003</v>
+        <v>4.2950214952425814</v>
       </c>
       <c r="M135">
-        <v>0.1648640031148178</v>
+        <v>0.19</v>
       </c>
       <c r="N135">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="2:14">
@@ -14013,10 +13587,10 @@
         <v>182</v>
       </c>
       <c r="C136" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="D136" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -14031,19 +13605,19 @@
         <v>186</v>
       </c>
       <c r="J136" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="K136" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L136">
-        <v>8.2560000000000002</v>
+        <v>4.5224792372855314</v>
       </c>
       <c r="M136">
-        <v>0.1520135729443049</v>
+        <v>0.189</v>
       </c>
       <c r="N136">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="2:14">
@@ -14051,10 +13625,10 @@
         <v>182</v>
       </c>
       <c r="C137" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="D137" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -14069,19 +13643,19 @@
         <v>186</v>
       </c>
       <c r="J137" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="K137" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L137">
-        <v>8.1442499999999995</v>
+        <v>6.5715455615362517</v>
       </c>
       <c r="M137">
-        <v>0.151708166751155</v>
+        <v>0.185</v>
       </c>
       <c r="N137">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="2:14">
@@ -14089,10 +13663,10 @@
         <v>182</v>
       </c>
       <c r="C138" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D138" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -14107,19 +13681,19 @@
         <v>186</v>
       </c>
       <c r="J138" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="K138" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L138">
-        <v>8.3294999999999995</v>
+        <v>7.252914863655616</v>
       </c>
       <c r="M138">
-        <v>0.15002509122581789</v>
+        <v>0.18351752774567745</v>
       </c>
       <c r="N138">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="2:14">
@@ -14127,10 +13701,10 @@
         <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="D139" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -14145,19 +13719,19 @@
         <v>186</v>
       </c>
       <c r="J139" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="K139" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L139">
-        <v>8.4172499999999992</v>
+        <v>9.8740077247180409</v>
       </c>
       <c r="M139">
-        <v>0.1486604569627136</v>
+        <v>0.18216976514368449</v>
       </c>
       <c r="N139">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="2:14">
@@ -14165,10 +13739,10 @@
         <v>182</v>
       </c>
       <c r="C140" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="D140" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -14183,19 +13757,19 @@
         <v>186</v>
       </c>
       <c r="J140" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="K140" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L140">
-        <v>7.7272499999999997</v>
+        <v>0.82040396789140502</v>
       </c>
       <c r="M140">
-        <v>0.14069336661847689</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="N140">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="2:14">
@@ -14203,37 +13777,37 @@
         <v>182</v>
       </c>
       <c r="C141" t="s">
+        <v>480</v>
+      </c>
+      <c r="D141" t="s">
+        <v>481</v>
+      </c>
+      <c r="E141" t="s">
+        <v>10</v>
+      </c>
+      <c r="F141" t="s">
+        <v>21</v>
+      </c>
+      <c r="G141" t="s">
+        <v>185</v>
+      </c>
+      <c r="H141" t="s">
+        <v>186</v>
+      </c>
+      <c r="J141" t="s">
+        <v>480</v>
+      </c>
+      <c r="K141" t="s">
         <v>498</v>
       </c>
-      <c r="D141" t="s">
-        <v>499</v>
-      </c>
-      <c r="E141" t="s">
-        <v>10</v>
-      </c>
-      <c r="F141" t="s">
-        <v>21</v>
-      </c>
-      <c r="G141" t="s">
-        <v>185</v>
-      </c>
-      <c r="H141" t="s">
-        <v>186</v>
-      </c>
-      <c r="J141" t="s">
-        <v>498</v>
-      </c>
-      <c r="K141" t="s">
-        <v>526</v>
-      </c>
       <c r="L141">
-        <v>8.2177500000000006</v>
+        <v>8.6591881426587864</v>
       </c>
       <c r="M141">
-        <v>0.1335690204311058</v>
+        <v>0.17755584851005002</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="2:14">
@@ -14241,10 +13815,10 @@
         <v>182</v>
       </c>
       <c r="C142" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="D142" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -14259,19 +13833,19 @@
         <v>186</v>
       </c>
       <c r="J142" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="K142" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L142">
-        <v>7.1909999999999998</v>
+        <v>2.2385167735403306</v>
       </c>
       <c r="M142">
-        <v>0.118271462242377</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="N142">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="2:14">
@@ -14279,10 +13853,10 @@
         <v>182</v>
       </c>
       <c r="C143" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="D143" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -14297,19 +13871,19 @@
         <v>186</v>
       </c>
       <c r="J143" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="K143" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L143">
-        <v>7.3612500000000001</v>
+        <v>5.4261482771080383</v>
       </c>
       <c r="M143">
-        <v>0.113610085547156</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="N143">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="2:14">
@@ -14317,10 +13891,10 @@
         <v>182</v>
       </c>
       <c r="C144" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="D144" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -14335,19 +13909,19 @@
         <v>186</v>
       </c>
       <c r="J144" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="K144" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L144">
-        <v>8.2837499999999995</v>
+        <v>1.4790050900062073</v>
       </c>
       <c r="M144">
-        <v>0.1106928942651814</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="N144">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145" spans="2:14">
@@ -14355,10 +13929,10 @@
         <v>182</v>
       </c>
       <c r="C145" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="D145" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -14373,16 +13947,16 @@
         <v>186</v>
       </c>
       <c r="J145" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="K145" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L145">
-        <v>7.8937499999999998</v>
+        <v>1.3949784753138748</v>
       </c>
       <c r="M145">
-        <v>0.1038043665341269</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="N145">
         <v>1</v>
@@ -14393,10 +13967,10 @@
         <v>182</v>
       </c>
       <c r="C146" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="D146" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -14411,19 +13985,19 @@
         <v>186</v>
       </c>
       <c r="J146" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="K146" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L146">
-        <v>6.9930000000000003</v>
+        <v>5.4637182537171771</v>
       </c>
       <c r="M146">
-        <v>9.3457654798712805E-2</v>
+        <v>0.159</v>
       </c>
       <c r="N146">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="2:14">
@@ -14431,10 +14005,10 @@
         <v>182</v>
       </c>
       <c r="C147" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="D147" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -14449,19 +14023,19 @@
         <v>186</v>
       </c>
       <c r="J147" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="K147" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L147">
-        <v>7.7370000000000001</v>
+        <v>4.8709592243217905</v>
       </c>
       <c r="M147">
-        <v>8.6101260740745103E-2</v>
+        <v>0.155</v>
       </c>
       <c r="N147">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="2:14">
@@ -14469,10 +14043,10 @@
         <v>182</v>
       </c>
       <c r="C148" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="D148" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -14487,19 +14061,19 @@
         <v>186</v>
       </c>
       <c r="J148" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="K148" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L148">
-        <v>7.6942500000000003</v>
+        <v>0.82815675434685676</v>
       </c>
       <c r="M148">
-        <v>7.03514394781561E-2</v>
+        <v>0.151</v>
       </c>
       <c r="N148">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="2:14">
@@ -14507,10 +14081,10 @@
         <v>182</v>
       </c>
       <c r="C149" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="D149" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -14525,208 +14099,18 @@
         <v>186</v>
       </c>
       <c r="J149" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="K149" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="L149">
-        <v>4.5172499999999998</v>
+        <v>4.930205144235063</v>
       </c>
       <c r="M149">
-        <v>5.1050580434309399E-2</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="N149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="2:14">
-      <c r="B150" t="s">
-        <v>182</v>
-      </c>
-      <c r="C150" t="s">
-        <v>516</v>
-      </c>
-      <c r="D150" t="s">
-        <v>517</v>
-      </c>
-      <c r="E150" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150" t="s">
-        <v>21</v>
-      </c>
-      <c r="G150" t="s">
-        <v>185</v>
-      </c>
-      <c r="H150" t="s">
-        <v>186</v>
-      </c>
-      <c r="J150" t="s">
-        <v>516</v>
-      </c>
-      <c r="K150" t="s">
-        <v>526</v>
-      </c>
-      <c r="L150">
-        <v>5.0430000000000001</v>
-      </c>
-      <c r="M150">
-        <v>5.0246123962461697E-2</v>
-      </c>
-      <c r="N150">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="2:14">
-      <c r="B151" t="s">
-        <v>182</v>
-      </c>
-      <c r="C151" t="s">
-        <v>518</v>
-      </c>
-      <c r="D151" t="s">
-        <v>519</v>
-      </c>
-      <c r="E151" t="s">
-        <v>10</v>
-      </c>
-      <c r="F151" t="s">
-        <v>21</v>
-      </c>
-      <c r="G151" t="s">
-        <v>185</v>
-      </c>
-      <c r="H151" t="s">
-        <v>186</v>
-      </c>
-      <c r="J151" t="s">
-        <v>518</v>
-      </c>
-      <c r="K151" t="s">
-        <v>526</v>
-      </c>
-      <c r="L151">
-        <v>2.0242499999999999</v>
-      </c>
-      <c r="M151">
-        <v>2.8461322395155499E-2</v>
-      </c>
-      <c r="N151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="2:14">
-      <c r="B152" t="s">
-        <v>182</v>
-      </c>
-      <c r="C152" t="s">
-        <v>520</v>
-      </c>
-      <c r="D152" t="s">
-        <v>521</v>
-      </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152" t="s">
-        <v>21</v>
-      </c>
-      <c r="G152" t="s">
-        <v>185</v>
-      </c>
-      <c r="H152" t="s">
-        <v>186</v>
-      </c>
-      <c r="J152" t="s">
-        <v>520</v>
-      </c>
-      <c r="K152" t="s">
-        <v>526</v>
-      </c>
-      <c r="L152">
-        <v>2.8544999999999998</v>
-      </c>
-      <c r="M152">
-        <v>2.8014890642676895E-2</v>
-      </c>
-      <c r="N152">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153" spans="2:14">
-      <c r="B153" t="s">
-        <v>182</v>
-      </c>
-      <c r="C153" t="s">
-        <v>522</v>
-      </c>
-      <c r="D153" t="s">
-        <v>523</v>
-      </c>
-      <c r="E153" t="s">
-        <v>10</v>
-      </c>
-      <c r="F153" t="s">
-        <v>21</v>
-      </c>
-      <c r="G153" t="s">
-        <v>185</v>
-      </c>
-      <c r="H153" t="s">
-        <v>186</v>
-      </c>
-      <c r="J153" t="s">
-        <v>522</v>
-      </c>
-      <c r="K153" t="s">
-        <v>526</v>
-      </c>
-      <c r="L153">
-        <v>1.0740000000000001</v>
-      </c>
-      <c r="M153">
-        <v>2.1418931566030801E-2</v>
-      </c>
-      <c r="N153">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="2:14">
-      <c r="B154" t="s">
-        <v>182</v>
-      </c>
-      <c r="C154" t="s">
-        <v>524</v>
-      </c>
-      <c r="D154" t="s">
-        <v>525</v>
-      </c>
-      <c r="E154" t="s">
-        <v>10</v>
-      </c>
-      <c r="F154" t="s">
-        <v>21</v>
-      </c>
-      <c r="G154" t="s">
-        <v>185</v>
-      </c>
-      <c r="H154" t="s">
-        <v>186</v>
-      </c>
-      <c r="J154" t="s">
-        <v>524</v>
-      </c>
-      <c r="K154" t="s">
-        <v>526</v>
-      </c>
-      <c r="L154">
-        <v>1.1220000000000001</v>
-      </c>
-      <c r="M154">
-        <v>2.02272857010726E-2</v>
-      </c>
-      <c r="N154">
         <v>1</v>
       </c>
     </row>
@@ -14736,7 +14120,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B572E010-8CB7-41C2-A01D-25F1B3C3D8C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EB3E35-2298-4C79-92A0-BCF2FBC49252}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14753,10 +14137,10 @@
         <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>602</v>
+        <v>574</v>
       </c>
       <c r="D10" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -14794,7 +14178,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -14818,7 +14202,7 @@
         <v>182</v>
       </c>
       <c r="K11" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -14827,15 +14211,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P11" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -14853,13 +14237,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
       <c r="J12" t="s">
         <v>182</v>
       </c>
       <c r="K12" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -14868,15 +14252,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P12" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -14894,13 +14278,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
       <c r="J13" t="s">
         <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -14909,15 +14293,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P13" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -14935,13 +14319,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="J14" t="s">
         <v>182</v>
       </c>
       <c r="K14" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -14950,15 +14334,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P14" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>603</v>
+        <v>575</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -14976,13 +14360,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
       <c r="J15" t="s">
         <v>182</v>
       </c>
       <c r="K15" t="s">
-        <v>611</v>
+        <v>583</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -14991,15 +14375,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P15" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -15023,7 +14407,7 @@
         <v>182</v>
       </c>
       <c r="K16" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -15032,15 +14416,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P16" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -15058,13 +14442,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
       <c r="J17" t="s">
         <v>182</v>
       </c>
       <c r="K17" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -15073,15 +14457,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P17" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -15099,13 +14483,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
       <c r="J18" t="s">
         <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -15114,15 +14498,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P18" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -15140,13 +14524,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="J19" t="s">
         <v>182</v>
       </c>
       <c r="K19" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -15155,15 +14539,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P19" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -15181,13 +14565,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
       <c r="J20" t="s">
         <v>182</v>
       </c>
       <c r="K20" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -15196,15 +14580,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P20" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -15228,7 +14612,7 @@
         <v>182</v>
       </c>
       <c r="K21" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -15237,15 +14621,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P21" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -15263,13 +14647,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
       <c r="J22" t="s">
         <v>182</v>
       </c>
       <c r="K22" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -15278,15 +14662,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P22" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -15304,13 +14688,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="J23" t="s">
         <v>182</v>
       </c>
       <c r="K23" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -15319,15 +14703,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P23" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -15351,7 +14735,7 @@
         <v>182</v>
       </c>
       <c r="K24" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -15360,15 +14744,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P24" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -15386,13 +14770,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
       <c r="J25" t="s">
         <v>182</v>
       </c>
       <c r="K25" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -15401,15 +14785,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P25" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -15427,13 +14811,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="J26" t="s">
         <v>182</v>
       </c>
       <c r="K26" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -15442,15 +14826,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P26" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>611</v>
+        <v>583</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -15474,7 +14858,7 @@
         <v>182</v>
       </c>
       <c r="K27" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -15483,15 +14867,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="P27" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>611</v>
+        <v>583</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -15509,12 +14893,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>611</v>
+        <v>583</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -15532,12 +14916,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -15560,7 +14944,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -15578,12 +14962,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -15601,12 +14985,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -15629,7 +15013,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -15647,12 +15031,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -15670,12 +15054,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -15693,12 +15077,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -15716,12 +15100,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -15744,7 +15128,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -15762,12 +15146,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>614</v>
+        <v>586</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -15785,12 +15169,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -15813,7 +15197,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -15831,12 +15215,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -15854,12 +15238,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -15882,7 +15266,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -15900,12 +15284,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -15923,12 +15307,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -15951,7 +15335,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -15969,12 +15353,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -15992,12 +15376,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -16020,7 +15404,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -16038,12 +15422,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -16061,12 +15445,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -16084,12 +15468,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -16107,12 +15491,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -16135,7 +15519,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -16153,12 +15537,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -16176,12 +15560,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -16204,7 +15588,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -16222,12 +15606,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -16245,12 +15629,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -16273,7 +15657,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -16291,12 +15675,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -16314,15 +15698,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="C64" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -16342,10 +15726,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="C65" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -16360,15 +15744,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="C66" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -16383,15 +15767,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="C67" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -16406,15 +15790,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="C68" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -16429,15 +15813,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="C69" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -16457,10 +15841,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="C70" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -16475,15 +15859,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>604</v>
+        <v>576</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="C71" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -16498,15 +15882,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>605</v>
+        <v>577</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="C72" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -16521,15 +15905,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="C73" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -16544,7 +15928,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>607</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{513285AF-95D5-470D-B081-ED8E3464B589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52486C56-C2AD-48C8-BC68-06B5C5DFFE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="627">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -679,18 +679,132 @@
     <t>ele</t>
   </si>
   <si>
+    <t>e_spv-DEU_17_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_17 -- cost class 1</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_17_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_17 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_17_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_17 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_17_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_17 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_16_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_16 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_16_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_16 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_16_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_16 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_16_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_16 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_16_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_16 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_15_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_15 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_15_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_15 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_15_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_15 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_15_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_15 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_15_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_15 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_14_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_14 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_14_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_14 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_14_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_14 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_14_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_14 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_spv-DEU_14_c3</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_14 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_spv-DEU_13_c1</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-DEU_13 -- cost class 1</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>e_spv-DEU_13_c2</t>
   </si>
   <si>
@@ -703,78 +817,18 @@
     <t>solar resource -- CF class spv-DEU_13 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-DEU_13_c5</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-DEU_13 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_spv-DEU_13_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-DEU_13 -- cost class 4</t>
   </si>
   <si>
-    <t>e_spv-DEU_13_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_13 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_12_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_12 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_12_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_12 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_12_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_12 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_12_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_12 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_12_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_12 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_11_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_11 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_11_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_11 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_11_c3</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_11 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_11_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_11 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_spv-DEU_11_c5</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-DEU_11 -- cost class 5</t>
-  </si>
-  <si>
     <t>comm-out</t>
   </si>
   <si>
@@ -790,10 +844,76 @@
     <t>elc_spv-DEU</t>
   </si>
   <si>
-    <t>e_won-DEU_52_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_52 -- cost class 1</t>
+    <t>e_won-DEU_61_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_61 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_58_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_58 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_57_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_57 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_57_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_57 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_56_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_56_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_56_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_56_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_56 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_54_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_54 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_51_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_51 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_51_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_51 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_51_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_51 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_50_c1</t>
@@ -802,22 +922,28 @@
     <t>onshore wind resource -- CF class won-DEU_50 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_49_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_49 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_49_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_49 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_49_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_49 -- cost class 2</t>
+    <t>e_won-DEU_48_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_48 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_47_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_47 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_47_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_47 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_46_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_46 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_46_c1</t>
@@ -832,30 +958,12 @@
     <t>onshore wind resource -- CF class won-DEU_45 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_45_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_45 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_45_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_45 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_45_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_45 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_44_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_44 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-DEU_43_c1</t>
   </si>
   <si>
@@ -868,46 +976,16 @@
     <t>onshore wind resource -- CF class won-DEU_43 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_43_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_43 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_43_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_43 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_43_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_43 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-DEU_42_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_42 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_42_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_42 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_42_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_42 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_42_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_42 -- cost class 4</t>
+    <t>e_won-DEU_41_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_41 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_41_c1</t>
@@ -916,16 +994,10 @@
     <t>onshore wind resource -- CF class won-DEU_41 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_41_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_41 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_41_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_41 -- cost class 2</t>
+    <t>e_won-DEU_40_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_40_c1</t>
@@ -940,72 +1012,18 @@
     <t>onshore wind resource -- CF class won-DEU_40 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_40_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_40_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_40 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-DEU_39_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_39 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_39_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_39_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_39_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_39_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_39 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-DEU_38_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_38 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_38_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_38 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_38_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_38 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_38_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_38 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_37_c1</t>
   </si>
   <si>
@@ -1018,22 +1036,16 @@
     <t>onshore wind resource -- CF class won-DEU_37 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_37_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_37 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_37_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_37 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_37_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_37 -- cost class 4</t>
+    <t>e_won-DEU_36_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_36_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_36_c1</t>
@@ -1042,16 +1054,28 @@
     <t>onshore wind resource -- CF class won-DEU_36 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_36_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_36_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_36 -- cost class 3</t>
+    <t>e_won-DEU_35_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_35_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_35_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_35_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_35_c1</t>
@@ -1060,28 +1084,16 @@
     <t>onshore wind resource -- CF class won-DEU_35 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_35_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_35_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_35_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_35_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_35 -- cost class 4</t>
+    <t>e_won-DEU_34_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_34_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-DEU_34_c2</t>
@@ -1090,16 +1102,10 @@
     <t>onshore wind resource -- CF class won-DEU_34 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_34_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_34_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 3</t>
+    <t>e_won-DEU_34_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_34_c5</t>
@@ -1108,10 +1114,28 @@
     <t>onshore wind resource -- CF class won-DEU_34 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_34_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_34 -- cost class 4</t>
+    <t>e_won-DEU_33_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_33_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_33_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_33_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_33_c1</t>
@@ -1120,28 +1144,10 @@
     <t>onshore wind resource -- CF class won-DEU_33 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_33_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_33_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_33_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_33_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_33 -- cost class 4</t>
+    <t>e_won-DEU_32_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_32_c2</t>
@@ -1156,10 +1162,10 @@
     <t>onshore wind resource -- CF class won-DEU_32 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_32_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 3</t>
+    <t>e_won-DEU_32_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_32_c4</t>
@@ -1168,10 +1174,16 @@
     <t>onshore wind resource -- CF class won-DEU_32 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_32_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_32 -- cost class 5</t>
+    <t>e_won-DEU_31_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_31_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_31_c1</t>
@@ -1180,16 +1192,10 @@
     <t>onshore wind resource -- CF class won-DEU_31 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_31_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_31_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 3</t>
+    <t>e_won-DEU_31_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_31_c4</t>
@@ -1198,10 +1204,10 @@
     <t>onshore wind resource -- CF class won-DEU_31 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_31_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_31 -- cost class 5</t>
+    <t>e_won-DEU_30_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-DEU_30_c3</t>
@@ -1216,10 +1222,10 @@
     <t>onshore wind resource -- CF class won-DEU_30 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_30_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 1</t>
+    <t>e_won-DEU_30_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_30_c4</t>
@@ -1228,10 +1234,16 @@
     <t>onshore wind resource -- CF class won-DEU_30 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_30_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_30 -- cost class 5</t>
+    <t>e_won-DEU_29_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_29_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_29_c1</t>
@@ -1240,16 +1252,10 @@
     <t>onshore wind resource -- CF class won-DEU_29 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_29_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_29_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 3</t>
+    <t>e_won-DEU_29_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 5</t>
   </si>
   <si>
     <t>e_won-DEU_29_c4</t>
@@ -1258,10 +1264,16 @@
     <t>onshore wind resource -- CF class won-DEU_29 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_29_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_29 -- cost class 5</t>
+    <t>e_won-DEU_28_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_28_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_28_c3</t>
@@ -1270,16 +1282,10 @@
     <t>onshore wind resource -- CF class won-DEU_28 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_28_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-DEU_28_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 2</t>
+    <t>e_won-DEU_28_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_28_c5</t>
@@ -1288,10 +1294,22 @@
     <t>onshore wind resource -- CF class won-DEU_28 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_28_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_28 -- cost class 4</t>
+    <t>e_won-DEU_27_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_27_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_27_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-DEU_27_c1</t>
@@ -1306,42 +1324,24 @@
     <t>onshore wind resource -- CF class won-DEU_27 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_27_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_27_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_27_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_27 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_26_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_26 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-DEU_26_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_26 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-DEU_26_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_26 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_26_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_26 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_26_c3</t>
   </si>
   <si>
@@ -1354,6 +1354,24 @@
     <t>onshore wind resource -- CF class won-DEU_26 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-DEU_25_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_25_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_25_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-DEU_25_c1</t>
   </si>
   <si>
@@ -1366,52 +1384,34 @@
     <t>onshore wind resource -- CF class won-DEU_25 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-DEU_25_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_25_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_25_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_25 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-DEU_24_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-DEU_24_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_24 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_24_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_24_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_24_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_24 -- cost class 5</t>
+    <t>e_won-DEU_23_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_23_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_23_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_23_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_23_c1</t>
@@ -1420,22 +1420,16 @@
     <t>onshore wind resource -- CF class won-DEU_23 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_23_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_23_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_23_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_23 -- cost class 3</t>
+    <t>e_won-DEU_22_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_22_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 4</t>
   </si>
   <si>
     <t>e_won-DEU_22_c1</t>
@@ -1450,18 +1444,6 @@
     <t>onshore wind resource -- CF class won-DEU_22 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-DEU_22_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_22_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_22 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_22_c5</t>
   </si>
   <si>
@@ -1480,54 +1462,54 @@
     <t>onshore wind resource -- CF class won-DEU_21 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_21_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_21 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-DEU_21_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_21 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-DEU_21_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_21 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-DEU_21_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_21 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-DEU_20_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-DEU_20_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_20 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_20_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 5</t>
+  </si>
+  <si>
+    <t>e_won-DEU_20_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-DEU_20_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_20 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_20_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 3</t>
-  </si>
-  <si>
-    <t>e_won-DEU_20_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-DEU_20_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_20 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-DEU_19_c2</t>
   </si>
   <si>
@@ -1552,30 +1534,30 @@
     <t>onshore wind resource -- CF class won-DEU_19 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-DEU_18_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_18_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-DEU_18_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_18 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_18_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-DEU_18_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_18 -- cost class 5</t>
   </si>
   <si>
-    <t>e_won-DEU_18_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_18 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-DEU_18_c4</t>
   </si>
   <si>
@@ -1594,22 +1576,34 @@
     <t>onshore wind resource -- CF class won-DEU_17 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-DEU_17_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_17 -- cost class 3</t>
+  </si>
+  <si>
+    <t>e_won-DEU_17_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_17 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-DEU_16_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_16 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-DEU_16_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_16 -- cost class 2</t>
-  </si>
-  <si>
-    <t>e_won-DEU_16_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-DEU_16 -- cost class 3</t>
+    <t>e_won-DEU_15_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_15 -- cost class 4</t>
+  </si>
+  <si>
+    <t>e_won-DEU_15_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_15 -- cost class 3</t>
   </si>
   <si>
     <t>e_won-DEU_15_c2</t>
@@ -1622,6 +1616,96 @@
   </si>
   <si>
     <t>onshore wind resource -- CF class won-DEU_15 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_14_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_14 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_13_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_13 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_12_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_12 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_11_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_11 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_11_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_11 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_10_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_10 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_9_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_9 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_9_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_9 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_7_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_7 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_5_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_5 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_5_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_5 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_3_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_3 -- cost class 1</t>
+  </si>
+  <si>
+    <t>e_won-DEU_3_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_3 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_2_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_2 -- cost class 2</t>
+  </si>
+  <si>
+    <t>e_won-DEU_2_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-DEU_2 -- cost class 1</t>
   </si>
   <si>
     <t>elc_won-DEU</t>
@@ -6782,8 +6866,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BADF93B6-A5AB-4D92-B818-FEA08B7983DE}">
-  <dimension ref="B9:N25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7314F02B-E03D-4979-8E2B-EE9344C32764}">
+  <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:14">
@@ -6820,16 +6904,16 @@
         <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="L10" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="M10" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="N10" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -6858,13 +6942,13 @@
         <v>183</v>
       </c>
       <c r="K11" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L11">
-        <v>12.791782386791809</v>
+        <v>1.7147665359668733</v>
       </c>
       <c r="M11">
-        <v>0.12902814577730443</v>
+        <v>0.1662904323543602</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -6896,16 +6980,16 @@
         <v>187</v>
       </c>
       <c r="K12" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L12">
-        <v>11.702903699571227</v>
+        <v>0.24486767721801161</v>
       </c>
       <c r="M12">
-        <v>0.1275874621992075</v>
+        <v>0.1660589409575936</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -6934,16 +7018,16 @@
         <v>189</v>
       </c>
       <c r="K13" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L13">
-        <v>19.844602556083714</v>
+        <v>0.5445065016374494</v>
       </c>
       <c r="M13">
-        <v>0.12645222884017382</v>
+        <v>0.16603687133815981</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -6972,16 +7056,16 @@
         <v>191</v>
       </c>
       <c r="K14" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L14">
-        <v>16.35015221521143</v>
+        <v>1.4593439237490069</v>
       </c>
       <c r="M14">
-        <v>0.1252207615863512</v>
+        <v>0.16600998761152111</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -7010,16 +7094,16 @@
         <v>193</v>
       </c>
       <c r="K15" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L15">
-        <v>10.526058360717219</v>
+        <v>1.327347186749162</v>
       </c>
       <c r="M15">
-        <v>0.125</v>
+        <v>0.15836819459097992</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -7048,16 +7132,16 @@
         <v>195</v>
       </c>
       <c r="K16" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L16">
-        <v>65.153241509933423</v>
+        <v>9.5414224166697288</v>
       </c>
       <c r="M16">
-        <v>0.12288031961134829</v>
+        <v>0.15792490416383353</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7086,16 +7170,16 @@
         <v>197</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L17">
-        <v>52.401759920563556</v>
+        <v>0.10493364400542535</v>
       </c>
       <c r="M17">
-        <v>0.1192081285175584</v>
+        <v>0.15773407945444637</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7124,16 +7208,16 @@
         <v>199</v>
       </c>
       <c r="K18" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L18">
-        <v>54.02475928388197</v>
+        <v>11.077015850824937</v>
       </c>
       <c r="M18">
-        <v>0.11711793039977518</v>
+        <v>0.15716936869560441</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7162,16 +7246,16 @@
         <v>201</v>
       </c>
       <c r="K19" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L19">
-        <v>43.685343348396096</v>
+        <v>10.448746425420433</v>
       </c>
       <c r="M19">
-        <v>0.11589950344468616</v>
+        <v>0.15591228601011772</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7200,16 +7284,16 @@
         <v>203</v>
       </c>
       <c r="K20" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L20">
-        <v>48.822480329285014</v>
+        <v>31.76985587454876</v>
       </c>
       <c r="M20">
-        <v>0.11503306689481993</v>
+        <v>0.15245170977190434</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7238,16 +7322,16 @@
         <v>205</v>
       </c>
       <c r="K21" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L21">
-        <v>39.308023057963723</v>
+        <v>13.933870333541359</v>
       </c>
       <c r="M21">
-        <v>0.11374801486475515</v>
+        <v>0.14925526007034357</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7276,13 +7360,13 @@
         <v>207</v>
       </c>
       <c r="K22" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L22">
-        <v>42.484800815089351</v>
+        <v>28.023821917968824</v>
       </c>
       <c r="M22">
-        <v>0.11279660370308546</v>
+        <v>0.14904174881428328</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -7314,13 +7398,13 @@
         <v>209</v>
       </c>
       <c r="K23" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L23">
-        <v>39.836754523943725</v>
+        <v>19.800101686635433</v>
       </c>
       <c r="M23">
-        <v>0.1116845138712432</v>
+        <v>0.14692238543364075</v>
       </c>
       <c r="N23">
         <v>3</v>
@@ -7352,16 +7436,16 @@
         <v>211</v>
       </c>
       <c r="K24" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L24">
-        <v>31.620646602849003</v>
+        <v>11.345704435831776</v>
       </c>
       <c r="M24">
-        <v>0.1106221621197848</v>
+        <v>0.14643457270381485</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -7390,16 +7474,358 @@
         <v>213</v>
       </c>
       <c r="K25" t="s">
+        <v>237</v>
+      </c>
+      <c r="L25">
+        <v>54.52843912661929</v>
+      </c>
+      <c r="M25">
+        <v>0.14268997177598666</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26" t="s">
+        <v>215</v>
+      </c>
+      <c r="K26" t="s">
+        <v>237</v>
+      </c>
+      <c r="L26">
+        <v>40.021838922783786</v>
+      </c>
+      <c r="M26">
+        <v>0.13854439301816671</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" t="s">
+        <v>186</v>
+      </c>
+      <c r="J27" t="s">
+        <v>217</v>
+      </c>
+      <c r="K27" t="s">
+        <v>237</v>
+      </c>
+      <c r="L27">
+        <v>48.571657115533917</v>
+      </c>
+      <c r="M27">
+        <v>0.13802198772305829</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C28" t="s">
         <v>219</v>
       </c>
-      <c r="L25">
-        <v>40.168147484835643</v>
-      </c>
-      <c r="M25">
-        <v>0.10949475767165157</v>
-      </c>
-      <c r="N25">
+      <c r="D28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" t="s">
+        <v>219</v>
+      </c>
+      <c r="K28" t="s">
+        <v>237</v>
+      </c>
+      <c r="L28">
+        <v>45.353475554365239</v>
+      </c>
+      <c r="M28">
+        <v>0.13702217040516357</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>185</v>
+      </c>
+      <c r="H29" t="s">
+        <v>186</v>
+      </c>
+      <c r="J29" t="s">
+        <v>221</v>
+      </c>
+      <c r="K29" t="s">
+        <v>237</v>
+      </c>
+      <c r="L29">
+        <v>42.660399724001145</v>
+      </c>
+      <c r="M29">
+        <v>0.13647845492057911</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" t="s">
+        <v>186</v>
+      </c>
+      <c r="J30" t="s">
+        <v>223</v>
+      </c>
+      <c r="K30" t="s">
+        <v>237</v>
+      </c>
+      <c r="L30">
+        <v>39.024506669608691</v>
+      </c>
+      <c r="M30">
+        <v>0.13376619369545326</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" t="s">
+        <v>226</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" t="s">
+        <v>186</v>
+      </c>
+      <c r="J31" t="s">
+        <v>225</v>
+      </c>
+      <c r="K31" t="s">
+        <v>237</v>
+      </c>
+      <c r="L31">
+        <v>29.528794352284979</v>
+      </c>
+      <c r="M31">
+        <v>0.13374577894500153</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" t="s">
+        <v>227</v>
+      </c>
+      <c r="D32" t="s">
+        <v>228</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>185</v>
+      </c>
+      <c r="H32" t="s">
+        <v>186</v>
+      </c>
+      <c r="J32" t="s">
+        <v>227</v>
+      </c>
+      <c r="K32" t="s">
+        <v>237</v>
+      </c>
+      <c r="L32">
+        <v>28.180219467472426</v>
+      </c>
+      <c r="M32">
+        <v>0.13338367781240143</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" t="s">
+        <v>186</v>
+      </c>
+      <c r="J33" t="s">
+        <v>229</v>
+      </c>
+      <c r="K33" t="s">
+        <v>237</v>
+      </c>
+      <c r="L33">
+        <v>29.346448011117623</v>
+      </c>
+      <c r="M33">
+        <v>0.13329991902745508</v>
+      </c>
+      <c r="N33">
         <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" t="s">
+        <v>231</v>
+      </c>
+      <c r="D34" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H34" t="s">
+        <v>186</v>
+      </c>
+      <c r="J34" t="s">
+        <v>231</v>
+      </c>
+      <c r="K34" t="s">
+        <v>237</v>
+      </c>
+      <c r="L34">
+        <v>30.169372740562626</v>
+      </c>
+      <c r="M34">
+        <v>0.13201841902575226</v>
+      </c>
+      <c r="N34">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7408,8 +7834,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAC2B83-F673-473A-BB02-02FB8C573C8F}">
-  <dimension ref="B9:AB149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E74485-4207-4546-BC54-D0DEAA9D4472}">
+  <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:28">
@@ -7452,16 +7878,16 @@
         <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="L10" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="M10" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="N10" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="P10" t="s">
         <v>178</v>
@@ -7488,16 +7914,16 @@
         <v>164</v>
       </c>
       <c r="Y10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="Z10" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="AA10" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="AB10" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="2:28">
@@ -7505,10 +7931,10 @@
         <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7523,16 +7949,16 @@
         <v>186</v>
       </c>
       <c r="J11" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="K11" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L11">
         <v>7.6602564102564094E-3</v>
       </c>
       <c r="M11">
-        <v>0.51500000000000001</v>
+        <v>0.60547369604706214</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -7541,10 +7967,10 @@
         <v>182</v>
       </c>
       <c r="Q11" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="R11" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="S11" t="s">
         <v>10</v>
@@ -7559,10 +7985,10 @@
         <v>186</v>
       </c>
       <c r="X11" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="Y11" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z11">
         <v>13.8675</v>
@@ -7579,10 +8005,10 @@
         <v>182</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -7597,16 +8023,16 @@
         <v>186</v>
       </c>
       <c r="J12" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="K12" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L12">
         <v>8.8807957153787295E-2</v>
       </c>
       <c r="M12">
-        <v>0.501</v>
+        <v>0.57960586454463925</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -7615,10 +8041,10 @@
         <v>182</v>
       </c>
       <c r="Q12" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="R12" t="s">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="S12" t="s">
         <v>10</v>
@@ -7633,10 +8059,10 @@
         <v>186</v>
       </c>
       <c r="X12" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="Y12" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z12">
         <v>11.755000000000001</v>
@@ -7653,10 +8079,10 @@
         <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -7671,28 +8097,28 @@
         <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="K13" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L13">
-        <v>0.62654719309068485</v>
+        <v>0.1551219562401488</v>
       </c>
       <c r="M13">
-        <v>0.49299999999999999</v>
+        <v>0.57320959241145331</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" t="s">
         <v>182</v>
       </c>
       <c r="Q13" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="R13" t="s">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="S13" t="s">
         <v>10</v>
@@ -7707,10 +8133,10 @@
         <v>186</v>
       </c>
       <c r="X13" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="Y13" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z13">
         <v>13.8675</v>
@@ -7727,10 +8153,10 @@
         <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -7745,28 +8171,28 @@
         <v>186</v>
       </c>
       <c r="J14" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="K14" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L14">
-        <v>0.1374704812888238</v>
+        <v>0.62654719309068485</v>
       </c>
       <c r="M14">
-        <v>0.49</v>
+        <v>0.57299534979618882</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P14" t="s">
         <v>182</v>
       </c>
       <c r="Q14" t="s">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="R14" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="S14" t="s">
         <v>10</v>
@@ -7781,10 +8207,10 @@
         <v>186</v>
       </c>
       <c r="X14" t="s">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="Y14" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z14">
         <v>13.8675</v>
@@ -7801,10 +8227,10 @@
         <v>182</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -7819,28 +8245,28 @@
         <v>186</v>
       </c>
       <c r="J15" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="K15" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L15">
         <v>0.14665964293128506</v>
       </c>
       <c r="M15">
-        <v>0.48899999999999993</v>
+        <v>0.56455391735389493</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" t="s">
         <v>182</v>
       </c>
       <c r="Q15" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="R15" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="S15" t="s">
         <v>10</v>
@@ -7855,10 +8281,10 @@
         <v>186</v>
       </c>
       <c r="X15" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="Y15" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z15">
         <v>13.8675</v>
@@ -7875,10 +8301,10 @@
         <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -7893,28 +8319,28 @@
         <v>186</v>
       </c>
       <c r="J16" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="K16" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L16">
-        <v>0.30943732119635886</v>
+        <v>0.1374704812888238</v>
       </c>
       <c r="M16">
-        <v>0.46300000000000002</v>
+        <v>0.55646086641743908</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" t="s">
         <v>182</v>
       </c>
       <c r="Q16" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="R16" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="S16" t="s">
         <v>10</v>
@@ -7929,10 +8355,10 @@
         <v>186</v>
       </c>
       <c r="X16" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="Y16" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z16">
         <v>13.8675</v>
@@ -7949,10 +8375,10 @@
         <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7967,28 +8393,28 @@
         <v>186</v>
       </c>
       <c r="J17" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="K17" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L17">
-        <v>2.8129591489571522</v>
+        <v>0.30943732119635886</v>
       </c>
       <c r="M17">
-        <v>0.45</v>
+        <v>0.55571876678834353</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P17" t="s">
         <v>182</v>
       </c>
       <c r="Q17" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="R17" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="S17" t="s">
         <v>10</v>
@@ -8003,10 +8429,10 @@
         <v>186</v>
       </c>
       <c r="X17" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="Y17" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z17">
         <v>27.734999999999999</v>
@@ -8023,10 +8449,10 @@
         <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -8041,16 +8467,16 @@
         <v>186</v>
       </c>
       <c r="J18" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="K18" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L18">
-        <v>0.58742454465550076</v>
+        <v>1.3855212742120202</v>
       </c>
       <c r="M18">
-        <v>0.44600000000000001</v>
+        <v>0.55538842146607259</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -8059,10 +8485,10 @@
         <v>182</v>
       </c>
       <c r="Q18" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="R18" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="S18" t="s">
         <v>10</v>
@@ -8077,10 +8503,10 @@
         <v>186</v>
       </c>
       <c r="X18" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="Y18" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z18">
         <v>14.02875</v>
@@ -8097,10 +8523,10 @@
         <v>182</v>
       </c>
       <c r="C19" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -8115,28 +8541,28 @@
         <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="K19" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L19">
-        <v>0.1551219562401488</v>
+        <v>0.58742454465550076</v>
       </c>
       <c r="M19">
-        <v>0.44500000000000001</v>
+        <v>0.54362148490056739</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" t="s">
         <v>182</v>
       </c>
       <c r="Q19" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="R19" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="S19" t="s">
         <v>10</v>
@@ -8151,10 +8577,10 @@
         <v>186</v>
       </c>
       <c r="X19" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="Y19" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z19">
         <v>13.8675</v>
@@ -8171,10 +8597,10 @@
         <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -8189,28 +8615,28 @@
         <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="K20" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L20">
         <v>1.4212499999999999</v>
       </c>
       <c r="M20">
-        <v>0.44499999999999995</v>
+        <v>0.51172011645728255</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P20" t="s">
         <v>182</v>
       </c>
       <c r="Q20" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="R20" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="S20" t="s">
         <v>10</v>
@@ -8225,10 +8651,10 @@
         <v>186</v>
       </c>
       <c r="X20" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="Y20" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z20">
         <v>14.02875</v>
@@ -8245,10 +8671,10 @@
         <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -8263,28 +8689,28 @@
         <v>186</v>
       </c>
       <c r="J21" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="K21" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L21">
-        <v>1.5770138627625505</v>
+        <v>1.3176292984869329</v>
       </c>
       <c r="M21">
-        <v>0.44400000000000006</v>
+        <v>0.50785221851711282</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" t="s">
         <v>182</v>
       </c>
       <c r="Q21" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="R21" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="S21" t="s">
         <v>10</v>
@@ -8299,10 +8725,10 @@
         <v>186</v>
       </c>
       <c r="X21" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="Y21" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z21">
         <v>13.827500000000001</v>
@@ -8319,10 +8745,10 @@
         <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D22" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -8337,28 +8763,28 @@
         <v>186</v>
       </c>
       <c r="J22" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="K22" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L22">
-        <v>4.4932775647884773</v>
+        <v>0.94391071885781108</v>
       </c>
       <c r="M22">
-        <v>0.43336492005138938</v>
+        <v>0.50527134774735971</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P22" t="s">
         <v>182</v>
       </c>
       <c r="Q22" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="R22" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="S22" t="s">
         <v>10</v>
@@ -8373,10 +8799,10 @@
         <v>186</v>
       </c>
       <c r="X22" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="Y22" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z22">
         <v>13.92625</v>
@@ -8393,10 +8819,10 @@
         <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -8411,28 +8837,28 @@
         <v>186</v>
       </c>
       <c r="J23" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="K23" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L23">
-        <v>4.5376647457138732</v>
+        <v>0.52875913363466021</v>
       </c>
       <c r="M23">
-        <v>0.43</v>
+        <v>0.5000100636922703</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" t="s">
         <v>182</v>
       </c>
       <c r="Q23" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="R23" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="S23" t="s">
         <v>10</v>
@@ -8447,10 +8873,10 @@
         <v>186</v>
       </c>
       <c r="X23" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="Y23" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z23">
         <v>13.23875</v>
@@ -8467,10 +8893,10 @@
         <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -8485,28 +8911,28 @@
         <v>186</v>
       </c>
       <c r="J24" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="K24" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L24">
-        <v>4.8667662261345104</v>
+        <v>0.95119682831310748</v>
       </c>
       <c r="M24">
-        <v>0.42799999999999999</v>
+        <v>0.47927323018315537</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P24" t="s">
         <v>182</v>
       </c>
       <c r="Q24" t="s">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="R24" t="s">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="S24" t="s">
         <v>10</v>
@@ -8521,10 +8947,10 @@
         <v>186</v>
       </c>
       <c r="X24" t="s">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="Y24" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z24">
         <v>4.5162500000000003</v>
@@ -8541,10 +8967,10 @@
         <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -8559,28 +8985,28 @@
         <v>186</v>
       </c>
       <c r="J25" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="K25" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L25">
-        <v>4.0798187691058461</v>
+        <v>3.4628263818732856</v>
       </c>
       <c r="M25">
-        <v>0.42799999999999999</v>
+        <v>0.47395544719054761</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P25" t="s">
         <v>182</v>
       </c>
       <c r="Q25" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="R25" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="S25" t="s">
         <v>10</v>
@@ -8595,10 +9021,10 @@
         <v>186</v>
       </c>
       <c r="X25" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="Y25" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z25">
         <v>13.8675</v>
@@ -8615,10 +9041,10 @@
         <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D26" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -8633,28 +9059,28 @@
         <v>186</v>
       </c>
       <c r="J26" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="K26" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L26">
-        <v>2.409816641133665</v>
+        <v>2.5383421781044189</v>
       </c>
       <c r="M26">
-        <v>0.42499999999999999</v>
+        <v>0.4679272704745196</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P26" t="s">
         <v>182</v>
       </c>
       <c r="Q26" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="R26" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="S26" t="s">
         <v>10</v>
@@ -8669,10 +9095,10 @@
         <v>186</v>
       </c>
       <c r="X26" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="Y26" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z26">
         <v>8.1549999999999994</v>
@@ -8689,10 +9115,10 @@
         <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -8707,28 +9133,28 @@
         <v>186</v>
       </c>
       <c r="J27" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="K27" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L27">
-        <v>3.4628263818732856</v>
+        <v>0.93356002702813012</v>
       </c>
       <c r="M27">
-        <v>0.42199999999999999</v>
+        <v>0.4617910666503538</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" t="s">
         <v>182</v>
       </c>
       <c r="Q27" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="R27" t="s">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="S27" t="s">
         <v>10</v>
@@ -8743,10 +9169,10 @@
         <v>186</v>
       </c>
       <c r="X27" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="Y27" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z27">
         <v>11.2575</v>
@@ -8763,10 +9189,10 @@
         <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -8781,28 +9207,28 @@
         <v>186</v>
       </c>
       <c r="J28" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="K28" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L28">
-        <v>1.3176292984869329</v>
+        <v>3.416737782360558</v>
       </c>
       <c r="M28">
-        <v>0.41799999999999998</v>
+        <v>0.45911415041508086</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28" t="s">
         <v>182</v>
       </c>
       <c r="Q28" t="s">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="R28" t="s">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="S28" t="s">
         <v>10</v>
@@ -8817,10 +9243,10 @@
         <v>186</v>
       </c>
       <c r="X28" t="s">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="Y28" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z28">
         <v>9.06</v>
@@ -8837,10 +9263,10 @@
         <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D29" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -8855,28 +9281,28 @@
         <v>186</v>
       </c>
       <c r="J29" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="K29" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L29">
-        <v>0.52875913363466021</v>
+        <v>3.5420807364753699</v>
       </c>
       <c r="M29">
-        <v>0.41599999999999998</v>
+        <v>0.45349251926597589</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P29" t="s">
         <v>182</v>
       </c>
       <c r="Q29" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="R29" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="S29" t="s">
         <v>10</v>
@@ -8891,10 +9317,10 @@
         <v>186</v>
       </c>
       <c r="X29" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="Y29" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z29">
         <v>10.8575</v>
@@ -8911,10 +9337,10 @@
         <v>182</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D30" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -8929,28 +9355,28 @@
         <v>186</v>
       </c>
       <c r="J30" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="K30" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L30">
-        <v>1.3855212742120202</v>
+        <v>4.5376647457138732</v>
       </c>
       <c r="M30">
-        <v>0.41499999999999998</v>
+        <v>0.44728008221576948</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P30" t="s">
         <v>182</v>
       </c>
       <c r="Q30" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="R30" t="s">
-        <v>538</v>
+        <v>566</v>
       </c>
       <c r="S30" t="s">
         <v>10</v>
@@ -8965,10 +9391,10 @@
         <v>186</v>
       </c>
       <c r="X30" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="Y30" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z30">
         <v>6.6375000000000002</v>
@@ -8985,10 +9411,10 @@
         <v>182</v>
       </c>
       <c r="C31" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D31" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -9003,16 +9429,16 @@
         <v>186</v>
       </c>
       <c r="J31" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="K31" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L31">
-        <v>0.94391071885781108</v>
+        <v>2.8129591489571522</v>
       </c>
       <c r="M31">
-        <v>0.41299999999999998</v>
+        <v>0.43447773296025288</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -9021,10 +9447,10 @@
         <v>182</v>
       </c>
       <c r="Q31" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="R31" t="s">
-        <v>540</v>
+        <v>568</v>
       </c>
       <c r="S31" t="s">
         <v>10</v>
@@ -9039,10 +9465,10 @@
         <v>186</v>
       </c>
       <c r="X31" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="Y31" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z31">
         <v>12.063750000000001</v>
@@ -9059,10 +9485,10 @@
         <v>182</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D32" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -9077,28 +9503,28 @@
         <v>186</v>
       </c>
       <c r="J32" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="K32" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L32">
-        <v>3.9527508633093529</v>
+        <v>4.0798187691058461</v>
       </c>
       <c r="M32">
-        <v>0.40799999999999997</v>
+        <v>0.43159159220331572</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P32" t="s">
         <v>182</v>
       </c>
       <c r="Q32" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="R32" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="S32" t="s">
         <v>10</v>
@@ -9113,10 +9539,10 @@
         <v>186</v>
       </c>
       <c r="X32" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="Y32" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z32">
         <v>2.8424999999999998</v>
@@ -9133,10 +9559,10 @@
         <v>182</v>
       </c>
       <c r="C33" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="D33" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -9151,28 +9577,28 @@
         <v>186</v>
       </c>
       <c r="J33" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="K33" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L33">
-        <v>5.0086472477064214</v>
+        <v>3.9527508633093529</v>
       </c>
       <c r="M33">
-        <v>0.40799999999999997</v>
+        <v>0.41804908680458558</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33" t="s">
         <v>182</v>
       </c>
       <c r="Q33" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="R33" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="S33" t="s">
         <v>10</v>
@@ -9187,10 +9613,10 @@
         <v>186</v>
       </c>
       <c r="X33" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="Y33" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z33">
         <v>0.11874999999999999</v>
@@ -9207,10 +9633,10 @@
         <v>182</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -9225,28 +9651,28 @@
         <v>186</v>
       </c>
       <c r="J34" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="K34" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L34">
-        <v>4.4937013078329349</v>
+        <v>4.884892809638619</v>
       </c>
       <c r="M34">
-        <v>0.40300000000000002</v>
+        <v>0.41321055018703212</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" t="s">
         <v>182</v>
       </c>
       <c r="Q34" t="s">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="R34" t="s">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="S34" t="s">
         <v>10</v>
@@ -9261,10 +9687,10 @@
         <v>186</v>
       </c>
       <c r="X34" t="s">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="Y34" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z34">
         <v>10.682499999999999</v>
@@ -9281,10 +9707,10 @@
         <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -9299,28 +9725,28 @@
         <v>186</v>
       </c>
       <c r="J35" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="K35" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L35">
-        <v>5.0095686646967783</v>
+        <v>4.8667662261345104</v>
       </c>
       <c r="M35">
-        <v>0.39700000000000002</v>
+        <v>0.41233198565551887</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35" t="s">
         <v>182</v>
       </c>
       <c r="Q35" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="R35" t="s">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="S35" t="s">
         <v>10</v>
@@ -9335,10 +9761,10 @@
         <v>186</v>
       </c>
       <c r="X35" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="Y35" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z35">
         <v>5.9212499999999997</v>
@@ -9355,10 +9781,10 @@
         <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D36" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -9373,28 +9799,28 @@
         <v>186</v>
       </c>
       <c r="J36" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="K36" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L36">
-        <v>3.416737782360558</v>
+        <v>3.8112316593784894</v>
       </c>
       <c r="M36">
-        <v>0.39500000000000002</v>
+        <v>0.40294995999097311</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P36" t="s">
         <v>182</v>
       </c>
       <c r="Q36" t="s">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="R36" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="S36" t="s">
         <v>10</v>
@@ -9409,10 +9835,10 @@
         <v>186</v>
       </c>
       <c r="X36" t="s">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="Y36" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z36">
         <v>2.61375</v>
@@ -9429,10 +9855,10 @@
         <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -9447,28 +9873,28 @@
         <v>186</v>
       </c>
       <c r="J37" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="K37" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L37">
-        <v>4.8593444496597042</v>
+        <v>2.409816641133665</v>
       </c>
       <c r="M37">
-        <v>0.39500000000000002</v>
+        <v>0.39697151968295202</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P37" t="s">
         <v>182</v>
       </c>
       <c r="Q37" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="R37" t="s">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="S37" t="s">
         <v>10</v>
@@ -9483,10 +9909,10 @@
         <v>186</v>
       </c>
       <c r="X37" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="Y37" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z37">
         <v>3.9175</v>
@@ -9503,10 +9929,10 @@
         <v>182</v>
       </c>
       <c r="C38" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D38" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -9521,28 +9947,28 @@
         <v>186</v>
       </c>
       <c r="J38" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="K38" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L38">
-        <v>10.368566720583351</v>
+        <v>4.2242993630573249</v>
       </c>
       <c r="M38">
-        <v>0.38900588095273092</v>
+        <v>0.39521220594388218</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="s">
         <v>182</v>
       </c>
       <c r="Q38" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="R38" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="S38" t="s">
         <v>10</v>
@@ -9557,10 +9983,10 @@
         <v>186</v>
       </c>
       <c r="X38" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="Y38" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z38">
         <v>1.0075000000000001</v>
@@ -9577,10 +10003,10 @@
         <v>182</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D39" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -9595,28 +10021,28 @@
         <v>186</v>
       </c>
       <c r="J39" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="K39" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L39">
-        <v>4.884892809638619</v>
+        <v>1.5770138627625505</v>
       </c>
       <c r="M39">
-        <v>0.38900000000000001</v>
+        <v>0.39414986229971999</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" t="s">
         <v>182</v>
       </c>
       <c r="Q39" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="R39" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="S39" t="s">
         <v>10</v>
@@ -9631,10 +10057,10 @@
         <v>186</v>
       </c>
       <c r="X39" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="Y39" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z39">
         <v>0.58250000000000002</v>
@@ -9651,10 +10077,10 @@
         <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D40" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -9669,28 +10095,28 @@
         <v>186</v>
       </c>
       <c r="J40" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="K40" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L40">
-        <v>2.5383421781044189</v>
+        <v>4.8593444496597042</v>
       </c>
       <c r="M40">
-        <v>0.38800000000000001</v>
+        <v>0.38201746921684659</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P40" t="s">
         <v>182</v>
       </c>
       <c r="Q40" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="R40" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="S40" t="s">
         <v>10</v>
@@ -9705,10 +10131,10 @@
         <v>186</v>
       </c>
       <c r="X40" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="Y40" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z40">
         <v>3.7499999999999999E-3</v>
@@ -9725,10 +10151,10 @@
         <v>182</v>
       </c>
       <c r="C41" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D41" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -9743,28 +10169,28 @@
         <v>186</v>
       </c>
       <c r="J41" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="K41" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L41">
-        <v>4.2242993630573249</v>
+        <v>5.0095686646967783</v>
       </c>
       <c r="M41">
-        <v>0.38800000000000001</v>
+        <v>0.37434168064361761</v>
       </c>
       <c r="N41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P41" t="s">
         <v>182</v>
       </c>
       <c r="Q41" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="R41" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="S41" t="s">
         <v>10</v>
@@ -9779,10 +10205,10 @@
         <v>186</v>
       </c>
       <c r="X41" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="Y41" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z41">
         <v>0.57625000000000004</v>
@@ -9799,10 +10225,10 @@
         <v>182</v>
       </c>
       <c r="C42" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="D42" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -9817,28 +10243,28 @@
         <v>186</v>
       </c>
       <c r="J42" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="K42" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L42">
         <v>4.8352011138905935</v>
       </c>
       <c r="M42">
-        <v>0.38700000000000001</v>
+        <v>0.36917162151179039</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P42" t="s">
         <v>182</v>
       </c>
       <c r="Q42" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="R42" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="S42" t="s">
         <v>10</v>
@@ -9853,10 +10279,10 @@
         <v>186</v>
       </c>
       <c r="X42" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="Y42" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z42">
         <v>2.75E-2</v>
@@ -9873,10 +10299,10 @@
         <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D43" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -9891,28 +10317,28 @@
         <v>186</v>
       </c>
       <c r="J43" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="K43" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L43">
-        <v>4.7590365600332367</v>
+        <v>5.0859902905998453</v>
       </c>
       <c r="M43">
-        <v>0.38400000000000001</v>
+        <v>0.36453803340134289</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P43" t="s">
         <v>182</v>
       </c>
       <c r="Q43" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="R43" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="S43" t="s">
         <v>10</v>
@@ -9927,10 +10353,10 @@
         <v>186</v>
       </c>
       <c r="X43" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="Y43" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z43">
         <v>0.21625</v>
@@ -9947,10 +10373,10 @@
         <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D44" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -9965,16 +10391,16 @@
         <v>186</v>
       </c>
       <c r="J44" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="K44" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L44">
-        <v>4.864937090544406</v>
+        <v>5.2147718856773482</v>
       </c>
       <c r="M44">
-        <v>0.38300000000000001</v>
+        <v>0.36281825576124332</v>
       </c>
       <c r="N44">
         <v>2</v>
@@ -9983,10 +10409,10 @@
         <v>182</v>
       </c>
       <c r="Q44" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="R44" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="S44" t="s">
         <v>10</v>
@@ -10001,10 +10427,10 @@
         <v>186</v>
       </c>
       <c r="X44" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="Y44" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z44">
         <v>1.7500000000000002E-2</v>
@@ -10021,10 +10447,10 @@
         <v>182</v>
       </c>
       <c r="C45" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="D45" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -10039,28 +10465,28 @@
         <v>186</v>
       </c>
       <c r="J45" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="K45" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L45">
-        <v>4.994320411537756</v>
+        <v>4.4937013078329349</v>
       </c>
       <c r="M45">
-        <v>0.376</v>
+        <v>0.36076949931521968</v>
       </c>
       <c r="N45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P45" t="s">
         <v>182</v>
       </c>
       <c r="Q45" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="R45" t="s">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="S45" t="s">
         <v>10</v>
@@ -10075,10 +10501,10 @@
         <v>186</v>
       </c>
       <c r="X45" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="Y45" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z45">
         <v>5.0000000000000001E-3</v>
@@ -10095,10 +10521,10 @@
         <v>182</v>
       </c>
       <c r="C46" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="D46" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -10113,28 +10539,28 @@
         <v>186</v>
       </c>
       <c r="J46" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="K46" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L46">
-        <v>5.0295832058946193</v>
+        <v>4.864937090544406</v>
       </c>
       <c r="M46">
-        <v>0.375</v>
+        <v>0.3503211333347076</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P46" t="s">
         <v>182</v>
       </c>
       <c r="Q46" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="R46" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="S46" t="s">
         <v>10</v>
@@ -10149,10 +10575,10 @@
         <v>186</v>
       </c>
       <c r="X46" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="Y46" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z46">
         <v>0.33500000000000002</v>
@@ -10169,10 +10595,10 @@
         <v>182</v>
       </c>
       <c r="C47" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="D47" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -10187,28 +10613,28 @@
         <v>186</v>
       </c>
       <c r="J47" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="K47" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L47">
-        <v>10.262704387859074</v>
+        <v>4.9670647324483372</v>
       </c>
       <c r="M47">
-        <v>0.37051326021922154</v>
+        <v>0.34982996232856922</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P47" t="s">
         <v>182</v>
       </c>
       <c r="Q47" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="R47" t="s">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="S47" t="s">
         <v>10</v>
@@ -10223,10 +10649,10 @@
         <v>186</v>
       </c>
       <c r="X47" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="Y47" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="Z47">
         <v>1.125E-2</v>
@@ -10243,10 +10669,10 @@
         <v>182</v>
       </c>
       <c r="C48" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="D48" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -10261,19 +10687,19 @@
         <v>186</v>
       </c>
       <c r="J48" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="K48" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L48">
-        <v>3.8112316593784894</v>
+        <v>4.0865774761939289</v>
       </c>
       <c r="M48">
-        <v>0.37</v>
+        <v>0.3472447936452937</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:14">
@@ -10281,10 +10707,10 @@
         <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="D49" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -10299,19 +10725,19 @@
         <v>186</v>
       </c>
       <c r="J49" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="K49" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L49">
-        <v>4.9665134770262096</v>
+        <v>5.0295832058946193</v>
       </c>
       <c r="M49">
-        <v>0.36799999999999999</v>
+        <v>0.3460630650440007</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="2:14">
@@ -10319,10 +10745,10 @@
         <v>182</v>
       </c>
       <c r="C50" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D50" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -10337,19 +10763,19 @@
         <v>186</v>
       </c>
       <c r="J50" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="K50" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L50">
-        <v>5.1121834784511249</v>
+        <v>4.7590365600332367</v>
       </c>
       <c r="M50">
-        <v>0.36699999999999999</v>
+        <v>0.34578516432535861</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:14">
@@ -10357,10 +10783,10 @@
         <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="D51" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -10375,19 +10801,19 @@
         <v>186</v>
       </c>
       <c r="J51" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="K51" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L51">
-        <v>5.0653150350969742</v>
+        <v>9.2249743054143138</v>
       </c>
       <c r="M51">
-        <v>0.36699999999999999</v>
+        <v>0.34285785438460714</v>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="2:14">
@@ -10395,10 +10821,10 @@
         <v>182</v>
       </c>
       <c r="C52" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="D52" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -10413,16 +10839,16 @@
         <v>186</v>
       </c>
       <c r="J52" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="K52" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L52">
-        <v>4.2794182124410511</v>
+        <v>10.162442082612424</v>
       </c>
       <c r="M52">
-        <v>0.36399999999999999</v>
+        <v>0.34279793123163405</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -10433,10 +10859,10 @@
         <v>182</v>
       </c>
       <c r="C53" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="D53" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -10451,16 +10877,16 @@
         <v>186</v>
       </c>
       <c r="J53" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="K53" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L53">
-        <v>4.9670647324483372</v>
+        <v>10.078696955477335</v>
       </c>
       <c r="M53">
-        <v>0.36099999999999999</v>
+        <v>0.34158625076062854</v>
       </c>
       <c r="N53">
         <v>2</v>
@@ -10471,10 +10897,10 @@
         <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D54" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
@@ -10489,19 +10915,19 @@
         <v>186</v>
       </c>
       <c r="J54" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="K54" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L54">
-        <v>5.0659056138954517</v>
+        <v>4.9779003558185355</v>
       </c>
       <c r="M54">
-        <v>0.35899999999999999</v>
+        <v>0.3380798122756935</v>
       </c>
       <c r="N54">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="2:14">
@@ -10509,10 +10935,10 @@
         <v>182</v>
       </c>
       <c r="C55" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D55" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
@@ -10527,19 +10953,19 @@
         <v>186</v>
       </c>
       <c r="J55" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="K55" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L55">
-        <v>4.851944576116682</v>
+        <v>4.8624568965517234</v>
       </c>
       <c r="M55">
-        <v>0.35399999999999998</v>
+        <v>0.33565465890466423</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="2:14">
@@ -10547,10 +10973,10 @@
         <v>182</v>
       </c>
       <c r="C56" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -10565,16 +10991,16 @@
         <v>186</v>
       </c>
       <c r="J56" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="K56" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L56">
-        <v>4.9779003558185355</v>
+        <v>9.8449316059724268</v>
       </c>
       <c r="M56">
-        <v>0.35299999999999998</v>
+        <v>0.33226926477026636</v>
       </c>
       <c r="N56">
         <v>3</v>
@@ -10585,10 +11011,10 @@
         <v>182</v>
       </c>
       <c r="C57" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -10603,19 +11029,19 @@
         <v>186</v>
       </c>
       <c r="J57" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="K57" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L57">
-        <v>4.9455560929732627</v>
+        <v>9.6603381550950918</v>
       </c>
       <c r="M57">
-        <v>0.35199999999999998</v>
+        <v>0.33156823883970526</v>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="2:14">
@@ -10623,10 +11049,10 @@
         <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -10641,19 +11067,19 @@
         <v>186</v>
       </c>
       <c r="J58" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="K58" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L58">
-        <v>0.93356002702813012</v>
+        <v>9.8531956921453343</v>
       </c>
       <c r="M58">
-        <v>0.34599999999999997</v>
+        <v>0.33106249230449969</v>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="2:14">
@@ -10661,10 +11087,10 @@
         <v>182</v>
       </c>
       <c r="C59" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -10679,16 +11105,16 @@
         <v>186</v>
       </c>
       <c r="J59" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="K59" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L59">
-        <v>4.8624568965517234</v>
+        <v>9.7342520722063561</v>
       </c>
       <c r="M59">
-        <v>0.34499999999999997</v>
+        <v>0.33066551064847061</v>
       </c>
       <c r="N59">
         <v>4</v>
@@ -10699,10 +11125,10 @@
         <v>182</v>
       </c>
       <c r="C60" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -10717,19 +11143,19 @@
         <v>186</v>
       </c>
       <c r="J60" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="K60" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L60">
-        <v>4.9143760952594917</v>
+        <v>10.171034508796986</v>
       </c>
       <c r="M60">
-        <v>0.34399999999999997</v>
+        <v>0.32927477705262759</v>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:14">
@@ -10737,10 +11163,10 @@
         <v>182</v>
       </c>
       <c r="C61" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -10755,19 +11181,19 @@
         <v>186</v>
       </c>
       <c r="J61" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="K61" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L61">
-        <v>4.7878806570483601</v>
+        <v>5.8636933378977174</v>
       </c>
       <c r="M61">
-        <v>0.34399999999999997</v>
+        <v>0.3248909103796751</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:14">
@@ -10775,10 +11201,10 @@
         <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -10793,19 +11219,19 @@
         <v>186</v>
       </c>
       <c r="J62" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K62" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L62">
-        <v>4.8613650595423934</v>
+        <v>5.2073607071727208</v>
       </c>
       <c r="M62">
-        <v>0.33800000000000002</v>
+        <v>0.32233893827024601</v>
       </c>
       <c r="N62">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="2:14">
@@ -10813,10 +11239,10 @@
         <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -10831,19 +11257,19 @@
         <v>186</v>
       </c>
       <c r="J63" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="K63" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L63">
-        <v>4.0865774761939289</v>
+        <v>9.9178501900121336</v>
       </c>
       <c r="M63">
-        <v>0.33500000000000002</v>
+        <v>0.32228450210616966</v>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:14">
@@ -10851,10 +11277,10 @@
         <v>182</v>
       </c>
       <c r="C64" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -10869,19 +11295,19 @@
         <v>186</v>
       </c>
       <c r="J64" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="K64" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L64">
-        <v>4.9213123608204397</v>
+        <v>6.8389936670565934</v>
       </c>
       <c r="M64">
-        <v>0.33500000000000002</v>
+        <v>0.32000561918811904</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="2:14">
@@ -10889,10 +11315,10 @@
         <v>182</v>
       </c>
       <c r="C65" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -10907,19 +11333,19 @@
         <v>186</v>
       </c>
       <c r="J65" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="K65" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L65">
-        <v>4.9542152822842311</v>
+        <v>4.6341036452401667</v>
       </c>
       <c r="M65">
-        <v>0.33200000000000002</v>
+        <v>0.31646037881333522</v>
       </c>
       <c r="N65">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="2:14">
@@ -10927,10 +11353,10 @@
         <v>182</v>
       </c>
       <c r="C66" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D66" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -10945,19 +11371,19 @@
         <v>186</v>
       </c>
       <c r="J66" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="K66" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L66">
-        <v>4.8438766478279671</v>
+        <v>4.5300945728056137</v>
       </c>
       <c r="M66">
-        <v>0.32900000000000001</v>
+        <v>0.3136383423020469</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="2:14">
@@ -10965,10 +11391,10 @@
         <v>182</v>
       </c>
       <c r="C67" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="D67" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -10983,19 +11409,19 @@
         <v>186</v>
       </c>
       <c r="J67" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="K67" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L67">
-        <v>4.8096304762365536</v>
+        <v>9.4561009250765817</v>
       </c>
       <c r="M67">
-        <v>0.32900000000000001</v>
+        <v>0.31030223441492688</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="2:14">
@@ -11003,10 +11429,10 @@
         <v>182</v>
       </c>
       <c r="C68" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -11021,19 +11447,19 @@
         <v>186</v>
       </c>
       <c r="J68" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="K68" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L68">
-        <v>5.3252175859598845</v>
+        <v>9.7651890086484059</v>
       </c>
       <c r="M68">
-        <v>0.32700000000000001</v>
+        <v>0.30928005846085321</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:14">
@@ -11041,10 +11467,10 @@
         <v>182</v>
       </c>
       <c r="C69" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -11059,19 +11485,19 @@
         <v>186</v>
       </c>
       <c r="J69" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="K69" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L69">
-        <v>4.8907163236881939</v>
+        <v>5.1889235567804528</v>
       </c>
       <c r="M69">
-        <v>0.32700000000000001</v>
+        <v>0.30647247396222338</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="2:14">
@@ -11079,10 +11505,10 @@
         <v>182</v>
       </c>
       <c r="C70" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="D70" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -11097,19 +11523,19 @@
         <v>186</v>
       </c>
       <c r="J70" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="K70" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L70">
-        <v>10.947911509682086</v>
+        <v>4.5845280146163221</v>
       </c>
       <c r="M70">
-        <v>0.32357558385042384</v>
+        <v>0.30527266685973509</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="2:14">
@@ -11117,10 +11543,10 @@
         <v>182</v>
       </c>
       <c r="C71" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="D71" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
@@ -11135,16 +11561,16 @@
         <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="K71" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L71">
-        <v>15.156868040079724</v>
+        <v>9.7757411548018869</v>
       </c>
       <c r="M71">
-        <v>0.3226777076281595</v>
+        <v>0.30271365513090243</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -11155,10 +11581,10 @@
         <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="D72" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -11173,16 +11599,16 @@
         <v>186</v>
       </c>
       <c r="J72" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="K72" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L72">
-        <v>9.3788751439971421</v>
+        <v>8.7928204064541671</v>
       </c>
       <c r="M72">
-        <v>0.32000171858046994</v>
+        <v>0.30222147759349077</v>
       </c>
       <c r="N72">
         <v>3</v>
@@ -11193,10 +11619,10 @@
         <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="D73" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -11211,19 +11637,19 @@
         <v>186</v>
       </c>
       <c r="J73" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="K73" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L73">
-        <v>9.379403694701411</v>
+        <v>10.853822805485695</v>
       </c>
       <c r="M73">
-        <v>0.31900000000000001</v>
+        <v>0.30212238345838427</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="2:14">
@@ -11231,10 +11657,10 @@
         <v>182</v>
       </c>
       <c r="C74" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D74" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
@@ -11249,16 +11675,16 @@
         <v>186</v>
       </c>
       <c r="J74" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="K74" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L74">
-        <v>11.036952771537861</v>
+        <v>7.2570352571720447</v>
       </c>
       <c r="M74">
-        <v>0.31650975182315566</v>
+        <v>0.30123828002817632</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -11269,10 +11695,10 @@
         <v>182</v>
       </c>
       <c r="C75" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D75" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -11287,19 +11713,19 @@
         <v>186</v>
       </c>
       <c r="J75" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="K75" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L75">
-        <v>9.2537084879455112</v>
+        <v>4.2847170222576185</v>
       </c>
       <c r="M75">
-        <v>0.31301609570896388</v>
+        <v>0.2956005552279718</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="2:14">
@@ -11307,10 +11733,10 @@
         <v>182</v>
       </c>
       <c r="C76" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="D76" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
@@ -11325,19 +11751,19 @@
         <v>186</v>
       </c>
       <c r="J76" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="K76" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L76">
-        <v>10.57589864275476</v>
+        <v>9.3356103729736137</v>
       </c>
       <c r="M76">
-        <v>0.31244556074751012</v>
+        <v>0.29235708013785633</v>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="2:14">
@@ -11345,10 +11771,10 @@
         <v>182</v>
       </c>
       <c r="C77" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="D77" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -11363,19 +11789,19 @@
         <v>186</v>
       </c>
       <c r="J77" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="K77" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L77">
-        <v>4.5845280146163221</v>
+        <v>10.323603545198891</v>
       </c>
       <c r="M77">
-        <v>0.308</v>
+        <v>0.29127209469703913</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="2:14">
@@ -11383,10 +11809,10 @@
         <v>182</v>
       </c>
       <c r="C78" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="D78" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -11401,19 +11827,19 @@
         <v>186</v>
       </c>
       <c r="J78" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="K78" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L78">
-        <v>4.6545121707814463</v>
+        <v>10.389781968556326</v>
       </c>
       <c r="M78">
-        <v>0.30499999999999999</v>
+        <v>0.29059600086907184</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:14">
@@ -11421,10 +11847,10 @@
         <v>182</v>
       </c>
       <c r="C79" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="D79" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -11439,16 +11865,16 @@
         <v>186</v>
       </c>
       <c r="J79" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="K79" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L79">
-        <v>4.0542812473136758</v>
+        <v>4.349000942121001</v>
       </c>
       <c r="M79">
-        <v>0.30499999999999999</v>
+        <v>0.28641433365004793</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -11459,10 +11885,10 @@
         <v>182</v>
       </c>
       <c r="C80" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="D80" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -11477,19 +11903,19 @@
         <v>186</v>
       </c>
       <c r="J80" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="K80" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L80">
-        <v>5.1889235567804528</v>
+        <v>4.4041130325814537</v>
       </c>
       <c r="M80">
-        <v>0.30199999999999999</v>
+        <v>0.28531699904219149</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="2:14">
@@ -11497,10 +11923,10 @@
         <v>182</v>
       </c>
       <c r="C81" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D81" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -11515,19 +11941,19 @@
         <v>186</v>
       </c>
       <c r="J81" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="K81" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L81">
-        <v>8.883595826171728</v>
+        <v>14.037217310255906</v>
       </c>
       <c r="M81">
-        <v>0.30152164728516667</v>
+        <v>0.28196520200495223</v>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="2:14">
@@ -11535,10 +11961,10 @@
         <v>182</v>
       </c>
       <c r="C82" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D82" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -11553,19 +11979,19 @@
         <v>186</v>
       </c>
       <c r="J82" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="K82" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L82">
-        <v>9.1462487058296862</v>
+        <v>8.9607984660082689</v>
       </c>
       <c r="M82">
-        <v>0.3004950473117774</v>
+        <v>0.2808542360260754</v>
       </c>
       <c r="N82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="2:14">
@@ -11573,10 +11999,10 @@
         <v>182</v>
       </c>
       <c r="C83" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="D83" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -11591,19 +12017,19 @@
         <v>186</v>
       </c>
       <c r="J83" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="K83" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L83">
-        <v>5.2813291256599371</v>
+        <v>8.8076619859689522</v>
       </c>
       <c r="M83">
-        <v>0.29699999999999999</v>
+        <v>0.27999907827374398</v>
       </c>
       <c r="N83">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="2:14">
@@ -11611,10 +12037,10 @@
         <v>182</v>
       </c>
       <c r="C84" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D84" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -11629,19 +12055,19 @@
         <v>186</v>
       </c>
       <c r="J84" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="K84" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L84">
-        <v>5.9115072899602676</v>
+        <v>9.4899910812682915</v>
       </c>
       <c r="M84">
-        <v>0.29599999999999999</v>
+        <v>0.27934170908276346</v>
       </c>
       <c r="N84">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="2:14">
@@ -11649,10 +12075,10 @@
         <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D85" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -11667,19 +12093,19 @@
         <v>186</v>
       </c>
       <c r="J85" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="K85" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L85">
-        <v>8.7820183107080148</v>
+        <v>10.4340449150087</v>
       </c>
       <c r="M85">
-        <v>0.2919819966082256</v>
+        <v>0.27930358727980914</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="2:14">
@@ -11687,10 +12113,10 @@
         <v>182</v>
       </c>
       <c r="C86" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="D86" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -11705,19 +12131,19 @@
         <v>186</v>
       </c>
       <c r="J86" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="K86" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L86">
-        <v>8.7472121213954797</v>
+        <v>9.3956864382108716</v>
       </c>
       <c r="M86">
-        <v>0.29148660942592647</v>
+        <v>0.27318489220241343</v>
       </c>
       <c r="N86">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="2:14">
@@ -11725,10 +12151,10 @@
         <v>182</v>
       </c>
       <c r="C87" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="D87" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -11743,19 +12169,19 @@
         <v>186</v>
       </c>
       <c r="J87" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="K87" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L87">
-        <v>8.8559922267903239</v>
+        <v>11.393043209503709</v>
       </c>
       <c r="M87">
-        <v>0.2891569021304003</v>
+        <v>0.27142064905861385</v>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="2:14">
@@ -11763,10 +12189,10 @@
         <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D88" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -11781,19 +12207,19 @@
         <v>186</v>
       </c>
       <c r="J88" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="K88" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L88">
-        <v>5.4957336161516137</v>
+        <v>14.592800093292185</v>
       </c>
       <c r="M88">
-        <v>0.28799999999999998</v>
+        <v>0.2700610497913693</v>
       </c>
       <c r="N88">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="2:14">
@@ -11801,10 +12227,10 @@
         <v>182</v>
       </c>
       <c r="C89" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="D89" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -11819,19 +12245,19 @@
         <v>186</v>
       </c>
       <c r="J89" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="K89" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L89">
-        <v>4.5381100825646259</v>
+        <v>13.458204803075256</v>
       </c>
       <c r="M89">
-        <v>0.28599999999999998</v>
+        <v>0.26833205727454035</v>
       </c>
       <c r="N89">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="2:14">
@@ -11839,10 +12265,10 @@
         <v>182</v>
       </c>
       <c r="C90" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="D90" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -11857,16 +12283,16 @@
         <v>186</v>
       </c>
       <c r="J90" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="K90" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L90">
-        <v>6.8389936670565934</v>
+        <v>17.721809343695792</v>
       </c>
       <c r="M90">
-        <v>0.28399999999999997</v>
+        <v>0.26783763780350478</v>
       </c>
       <c r="N90">
         <v>3</v>
@@ -11877,10 +12303,10 @@
         <v>182</v>
       </c>
       <c r="C91" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="D91" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -11895,16 +12321,16 @@
         <v>186</v>
       </c>
       <c r="J91" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="K91" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L91">
-        <v>8.5542689256619457</v>
+        <v>9.7551758540067581</v>
       </c>
       <c r="M91">
-        <v>0.28349734078055322</v>
+        <v>0.26359071936102701</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -11915,10 +12341,10 @@
         <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="D92" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -11933,19 +12359,19 @@
         <v>186</v>
       </c>
       <c r="J92" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="K92" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L92">
-        <v>8.8196363168443597</v>
+        <v>4.5110170134884706</v>
       </c>
       <c r="M92">
-        <v>0.27900000000000003</v>
+        <v>0.26353984242186729</v>
       </c>
       <c r="N92">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="2:14">
@@ -11953,10 +12379,10 @@
         <v>182</v>
       </c>
       <c r="C93" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D93" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -11971,19 +12397,19 @@
         <v>186</v>
       </c>
       <c r="J93" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="K93" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L93">
-        <v>7.2570352571720447</v>
+        <v>13.410065064912054</v>
       </c>
       <c r="M93">
-        <v>0.27700000000000002</v>
+        <v>0.26102455301053762</v>
       </c>
       <c r="N93">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="2:14">
@@ -11991,10 +12417,10 @@
         <v>182</v>
       </c>
       <c r="C94" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="D94" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -12009,19 +12435,19 @@
         <v>186</v>
       </c>
       <c r="J94" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="K94" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L94">
-        <v>4.8405906082909169</v>
+        <v>6.1158273598366639</v>
       </c>
       <c r="M94">
-        <v>0.27600000000000002</v>
+        <v>0.26017150954454588</v>
       </c>
       <c r="N94">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="2:14">
@@ -12029,10 +12455,10 @@
         <v>182</v>
       </c>
       <c r="C95" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="D95" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -12047,19 +12473,19 @@
         <v>186</v>
       </c>
       <c r="J95" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="K95" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L95">
-        <v>9.3287996709345613</v>
+        <v>6.4809362742382701</v>
       </c>
       <c r="M95">
-        <v>0.27199999999999996</v>
+        <v>0.25624716754528271</v>
       </c>
       <c r="N95">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="2:14">
@@ -12067,10 +12493,10 @@
         <v>182</v>
       </c>
       <c r="C96" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="D96" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -12085,19 +12511,19 @@
         <v>186</v>
       </c>
       <c r="J96" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="K96" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L96">
-        <v>11.210608005261635</v>
+        <v>6.3534573390116744</v>
       </c>
       <c r="M96">
-        <v>0.27169029267377787</v>
+        <v>0.25437685697328188</v>
       </c>
       <c r="N96">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="2:14">
@@ -12105,10 +12531,10 @@
         <v>182</v>
       </c>
       <c r="C97" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="D97" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -12123,19 +12549,19 @@
         <v>186</v>
       </c>
       <c r="J97" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="K97" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L97">
-        <v>10.243936168565069</v>
+        <v>5.8074496044031649</v>
       </c>
       <c r="M97">
-        <v>0.26963893884660473</v>
+        <v>0.25033910336926979</v>
       </c>
       <c r="N97">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="2:14">
@@ -12143,10 +12569,10 @@
         <v>182</v>
       </c>
       <c r="C98" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D98" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -12161,19 +12587,19 @@
         <v>186</v>
       </c>
       <c r="J98" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="K98" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L98">
-        <v>5.8285641113784807</v>
+        <v>11.806050025341166</v>
       </c>
       <c r="M98">
-        <v>0.26800000000000002</v>
+        <v>0.25016362734905451</v>
       </c>
       <c r="N98">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="2:14">
@@ -12181,10 +12607,10 @@
         <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="D99" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -12199,19 +12625,19 @@
         <v>186</v>
       </c>
       <c r="J99" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="K99" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L99">
-        <v>11.80572716941902</v>
+        <v>11.507902266226953</v>
       </c>
       <c r="M99">
-        <v>0.26700000000000002</v>
+        <v>0.24989506692241467</v>
       </c>
       <c r="N99">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="2:14">
@@ -12219,10 +12645,10 @@
         <v>182</v>
       </c>
       <c r="C100" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D100" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -12237,19 +12663,19 @@
         <v>186</v>
       </c>
       <c r="J100" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="K100" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L100">
-        <v>10.300282496826917</v>
+        <v>5.796432202202026</v>
       </c>
       <c r="M100">
-        <v>0.26300000000000001</v>
+        <v>0.24866879062703021</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="2:14">
@@ -12257,10 +12683,10 @@
         <v>182</v>
       </c>
       <c r="C101" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="D101" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -12275,19 +12701,19 @@
         <v>186</v>
       </c>
       <c r="J101" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="K101" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L101">
-        <v>13.116020331258497</v>
+        <v>6.6541321768552892</v>
       </c>
       <c r="M101">
-        <v>0.26160113955177522</v>
+        <v>0.24453800228933562</v>
       </c>
       <c r="N101">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="2:14">
@@ -12295,10 +12721,10 @@
         <v>182</v>
       </c>
       <c r="C102" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="D102" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -12313,19 +12739,19 @@
         <v>186</v>
       </c>
       <c r="J102" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="K102" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L102">
-        <v>11.241985870961329</v>
+        <v>5.7512927167383499</v>
       </c>
       <c r="M102">
-        <v>0.2613580906125238</v>
+        <v>0.23431152599072719</v>
       </c>
       <c r="N102">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="2:14">
@@ -12333,10 +12759,10 @@
         <v>182</v>
       </c>
       <c r="C103" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="D103" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -12351,19 +12777,19 @@
         <v>186</v>
       </c>
       <c r="J103" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="K103" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L103">
-        <v>11.075096855096069</v>
+        <v>12.112476207127504</v>
       </c>
       <c r="M103">
-        <v>0.25970490363192827</v>
+        <v>0.23323129664541103</v>
       </c>
       <c r="N103">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="2:14">
@@ -12371,10 +12797,10 @@
         <v>182</v>
       </c>
       <c r="C104" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="D104" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -12389,19 +12815,19 @@
         <v>186</v>
       </c>
       <c r="J104" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="K104" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L104">
-        <v>5.6165998996393229</v>
+        <v>12.115358303482328</v>
       </c>
       <c r="M104">
-        <v>0.25800000000000001</v>
+        <v>0.23125192888807858</v>
       </c>
       <c r="N104">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="2:14">
@@ -12409,10 +12835,10 @@
         <v>182</v>
       </c>
       <c r="C105" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="D105" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -12427,19 +12853,19 @@
         <v>186</v>
       </c>
       <c r="J105" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="K105" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L105">
-        <v>4.5110170134884706</v>
+        <v>11.124836329529094</v>
       </c>
       <c r="M105">
-        <v>0.254</v>
+        <v>0.22754429512905205</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="2:14">
@@ -12447,10 +12873,10 @@
         <v>182</v>
       </c>
       <c r="C106" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D106" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -12465,19 +12891,19 @@
         <v>186</v>
       </c>
       <c r="J106" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="K106" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L106">
-        <v>5.7764433098643861</v>
+        <v>9.8733558921199158</v>
       </c>
       <c r="M106">
-        <v>0.252</v>
+        <v>0.22599723087133788</v>
       </c>
       <c r="N106">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="2:14">
@@ -12485,10 +12911,10 @@
         <v>182</v>
       </c>
       <c r="C107" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="D107" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -12503,19 +12929,19 @@
         <v>186</v>
       </c>
       <c r="J107" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="K107" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L107">
-        <v>5.5177612223893595</v>
+        <v>9.63317239541934</v>
       </c>
       <c r="M107">
-        <v>0.252</v>
+        <v>0.22245805250439696</v>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="2:14">
@@ -12523,10 +12949,10 @@
         <v>182</v>
       </c>
       <c r="C108" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="D108" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
@@ -12541,19 +12967,19 @@
         <v>186</v>
       </c>
       <c r="J108" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="K108" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L108">
-        <v>6.4809362742382701</v>
+        <v>5.2729080193969784</v>
       </c>
       <c r="M108">
-        <v>0.251</v>
+        <v>0.2213539932129876</v>
       </c>
       <c r="N108">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="2:14">
@@ -12561,10 +12987,10 @@
         <v>182</v>
       </c>
       <c r="C109" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="D109" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -12579,19 +13005,19 @@
         <v>186</v>
       </c>
       <c r="J109" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="K109" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L109">
-        <v>4.9162836926193423</v>
+        <v>10.175412746127334</v>
       </c>
       <c r="M109">
-        <v>0.245</v>
+        <v>0.21942069260339683</v>
       </c>
       <c r="N109">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="2:14">
@@ -12599,10 +13025,10 @@
         <v>182</v>
       </c>
       <c r="C110" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="D110" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
@@ -12617,16 +13043,16 @@
         <v>186</v>
       </c>
       <c r="J110" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="K110" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L110">
-        <v>12.461581781258454</v>
+        <v>10.637566675755002</v>
       </c>
       <c r="M110">
-        <v>0.24166985856757878</v>
+        <v>0.21869248962298557</v>
       </c>
       <c r="N110">
         <v>2</v>
@@ -12637,10 +13063,10 @@
         <v>182</v>
       </c>
       <c r="C111" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="D111" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -12655,19 +13081,19 @@
         <v>186</v>
       </c>
       <c r="J111" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="K111" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L111">
-        <v>8.5476117597164016</v>
+        <v>4.7802762696690877</v>
       </c>
       <c r="M111">
-        <v>0.23946785129309572</v>
+        <v>0.21709288081712197</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="2:14">
@@ -12675,10 +13101,10 @@
         <v>182</v>
       </c>
       <c r="C112" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="D112" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
@@ -12693,19 +13119,19 @@
         <v>186</v>
       </c>
       <c r="J112" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="K112" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L112">
-        <v>11.836128067739212</v>
+        <v>10.377164656431152</v>
       </c>
       <c r="M112">
-        <v>0.23551027631933105</v>
+        <v>0.21302425401867695</v>
       </c>
       <c r="N112">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="2:14">
@@ -12713,10 +13139,10 @@
         <v>182</v>
       </c>
       <c r="C113" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D113" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -12731,19 +13157,19 @@
         <v>186</v>
       </c>
       <c r="J113" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="K113" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L113">
-        <v>10.829302216902397</v>
+        <v>4.7565218753120782</v>
       </c>
       <c r="M113">
-        <v>0.23499999999999999</v>
+        <v>0.21070878780867561</v>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="2:14">
@@ -12751,10 +13177,10 @@
         <v>182</v>
       </c>
       <c r="C114" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="D114" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -12769,19 +13195,19 @@
         <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="K114" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L114">
-        <v>6.1020172586244481</v>
+        <v>5.1872871755483212</v>
       </c>
       <c r="M114">
-        <v>0.23499999999999999</v>
+        <v>0.20857782756184373</v>
       </c>
       <c r="N114">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="2:14">
@@ -12789,10 +13215,10 @@
         <v>182</v>
       </c>
       <c r="C115" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="D115" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -12807,19 +13233,19 @@
         <v>186</v>
       </c>
       <c r="J115" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="K115" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L115">
-        <v>5.5224316416039274</v>
+        <v>3.6695813919143436</v>
       </c>
       <c r="M115">
-        <v>0.23300000000000001</v>
+        <v>0.20722419775208162</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="2:14">
@@ -12827,10 +13253,10 @@
         <v>182</v>
       </c>
       <c r="C116" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D116" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -12845,19 +13271,19 @@
         <v>186</v>
       </c>
       <c r="J116" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="K116" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L116">
-        <v>6.7762483094915744</v>
+        <v>3.8839401768989066</v>
       </c>
       <c r="M116">
-        <v>0.22900000000000004</v>
+        <v>0.2069558113847936</v>
       </c>
       <c r="N116">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="2:14">
@@ -12865,10 +13291,10 @@
         <v>182</v>
       </c>
       <c r="C117" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="D117" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -12883,19 +13309,19 @@
         <v>186</v>
       </c>
       <c r="J117" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="K117" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L117">
-        <v>4.5677412696440225</v>
+        <v>5.4735607016044732</v>
       </c>
       <c r="M117">
-        <v>0.22800000000000001</v>
+        <v>0.20417104587625901</v>
       </c>
       <c r="N117">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="2:14">
@@ -12903,10 +13329,10 @@
         <v>182</v>
       </c>
       <c r="C118" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D118" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
@@ -12921,19 +13347,19 @@
         <v>186</v>
       </c>
       <c r="J118" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="K118" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L118">
-        <v>4.8943617948361116</v>
+        <v>4.8037288968289413</v>
       </c>
       <c r="M118">
-        <v>0.22600000000000001</v>
+        <v>0.20381315305750669</v>
       </c>
       <c r="N118">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="2:14">
@@ -12941,10 +13367,10 @@
         <v>182</v>
       </c>
       <c r="C119" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="D119" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
@@ -12959,19 +13385,19 @@
         <v>186</v>
       </c>
       <c r="J119" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="K119" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L119">
-        <v>14.484013970800403</v>
+        <v>3.9482250883014016</v>
       </c>
       <c r="M119">
-        <v>0.22285259743445196</v>
+        <v>0.19960804861015211</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="2:14">
@@ -12979,10 +13405,10 @@
         <v>182</v>
       </c>
       <c r="C120" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D120" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
@@ -12997,19 +13423,19 @@
         <v>186</v>
       </c>
       <c r="J120" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="K120" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L120">
-        <v>15.306904509089872</v>
+        <v>5.5462366170639088</v>
       </c>
       <c r="M120">
-        <v>0.22105977893047932</v>
+        <v>0.19874383548358607</v>
       </c>
       <c r="N120">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="2:14">
@@ -13017,10 +13443,10 @@
         <v>182</v>
       </c>
       <c r="C121" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="D121" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
@@ -13035,19 +13461,19 @@
         <v>186</v>
       </c>
       <c r="J121" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="K121" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L121">
-        <v>14.694629142996705</v>
+        <v>3.9990112146637284</v>
       </c>
       <c r="M121">
-        <v>0.22081668756048034</v>
+        <v>0.1954346092831527</v>
       </c>
       <c r="N121">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="2:14">
@@ -13055,10 +13481,10 @@
         <v>182</v>
       </c>
       <c r="C122" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="D122" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
@@ -13073,19 +13499,19 @@
         <v>186</v>
       </c>
       <c r="J122" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="K122" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L122">
-        <v>14.711329700109928</v>
+        <v>4.8943617948361116</v>
       </c>
       <c r="M122">
-        <v>0.21828144412580569</v>
+        <v>0.19307640154597469</v>
       </c>
       <c r="N122">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="2:14">
@@ -13093,10 +13519,10 @@
         <v>182</v>
       </c>
       <c r="C123" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="D123" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
@@ -13111,19 +13537,19 @@
         <v>186</v>
       </c>
       <c r="J123" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="K123" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L123">
-        <v>11.318997585164663</v>
+        <v>5.1668974571482398</v>
       </c>
       <c r="M123">
-        <v>0.21648357291892867</v>
+        <v>0.1920373552511174</v>
       </c>
       <c r="N123">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="2:14">
@@ -13131,10 +13557,10 @@
         <v>182</v>
       </c>
       <c r="C124" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="D124" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
@@ -13149,16 +13575,16 @@
         <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="K124" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L124">
-        <v>7.2158185827770955</v>
+        <v>4.5677412696440225</v>
       </c>
       <c r="M124">
-        <v>0.21299999999999999</v>
+        <v>0.1910895850265463</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -13169,10 +13595,10 @@
         <v>182</v>
       </c>
       <c r="C125" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D125" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="E125" t="s">
         <v>10</v>
@@ -13187,19 +13613,19 @@
         <v>186</v>
       </c>
       <c r="J125" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="K125" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L125">
-        <v>5.2729080193969784</v>
+        <v>3.9739696310223738</v>
       </c>
       <c r="M125">
-        <v>0.21199999999999999</v>
+        <v>0.18934356175103029</v>
       </c>
       <c r="N125">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="2:14">
@@ -13207,10 +13633,10 @@
         <v>182</v>
       </c>
       <c r="C126" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="D126" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
@@ -13225,16 +13651,16 @@
         <v>186</v>
       </c>
       <c r="J126" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="K126" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L126">
-        <v>5.1872871755483212</v>
+        <v>4.0227726982097192</v>
       </c>
       <c r="M126">
-        <v>0.21</v>
+        <v>0.18492326876860271</v>
       </c>
       <c r="N126">
         <v>3</v>
@@ -13245,10 +13671,10 @@
         <v>182</v>
       </c>
       <c r="C127" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="D127" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
@@ -13263,19 +13689,19 @@
         <v>186</v>
       </c>
       <c r="J127" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="K127" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L127">
-        <v>3.9739696310223738</v>
+        <v>7.3773404508868436</v>
       </c>
       <c r="M127">
-        <v>0.20699999999999999</v>
+        <v>0.18329917448629079</v>
       </c>
       <c r="N127">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="2:14">
@@ -13283,10 +13709,10 @@
         <v>182</v>
       </c>
       <c r="C128" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D128" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -13301,19 +13727,19 @@
         <v>186</v>
       </c>
       <c r="J128" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="K128" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L128">
-        <v>5.7512927167383499</v>
+        <v>7.5871443894149051</v>
       </c>
       <c r="M128">
-        <v>0.20699999999999999</v>
+        <v>0.18297409649828716</v>
       </c>
       <c r="N128">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="2:14">
@@ -13321,10 +13747,10 @@
         <v>182</v>
       </c>
       <c r="C129" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="D129" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
@@ -13339,19 +13765,19 @@
         <v>186</v>
       </c>
       <c r="J129" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="K129" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L129">
-        <v>12.232944913795405</v>
+        <v>4.5224792372855314</v>
       </c>
       <c r="M129">
-        <v>0.20254661476397157</v>
+        <v>0.1800625315270642</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="2:14">
@@ -13359,10 +13785,10 @@
         <v>182</v>
       </c>
       <c r="C130" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="D130" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
@@ -13377,19 +13803,19 @@
         <v>186</v>
       </c>
       <c r="J130" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="K130" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L130">
-        <v>12.427735791628271</v>
+        <v>4.8674343919848235</v>
       </c>
       <c r="M130">
-        <v>0.20130471055462157</v>
+        <v>0.17649544137809611</v>
       </c>
       <c r="N130">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="2:14">
@@ -13397,10 +13823,10 @@
         <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="D131" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
@@ -13415,19 +13841,19 @@
         <v>186</v>
       </c>
       <c r="J131" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="K131" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L131">
-        <v>9.1623368293883836</v>
+        <v>5.8454368835601898</v>
       </c>
       <c r="M131">
-        <v>0.19927632397200792</v>
+        <v>0.17322038910379561</v>
       </c>
       <c r="N131">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="2:14">
@@ -13435,10 +13861,10 @@
         <v>182</v>
       </c>
       <c r="C132" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D132" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
@@ -13453,19 +13879,19 @@
         <v>186</v>
       </c>
       <c r="J132" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="K132" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L132">
-        <v>9.0572714220328798</v>
+        <v>5.2141117410869811</v>
       </c>
       <c r="M132">
-        <v>0.19644414840968813</v>
+        <v>0.17119241346264749</v>
       </c>
       <c r="N132">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="2:14">
@@ -13473,10 +13899,10 @@
         <v>182</v>
       </c>
       <c r="C133" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="D133" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -13491,19 +13917,19 @@
         <v>186</v>
       </c>
       <c r="J133" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="K133" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L133">
-        <v>8.9663246965978445</v>
+        <v>5.0344987238231607</v>
       </c>
       <c r="M133">
-        <v>0.19554285725274165</v>
+        <v>0.1680996609254681</v>
       </c>
       <c r="N133">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="2:14">
@@ -13511,10 +13937,10 @@
         <v>182</v>
       </c>
       <c r="C134" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="D134" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -13529,19 +13955,19 @@
         <v>186</v>
       </c>
       <c r="J134" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="K134" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L134">
         <v>6.0178716042520675</v>
       </c>
       <c r="M134">
-        <v>0.19</v>
+        <v>0.16530815223310119</v>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="2:14">
@@ -13549,10 +13975,10 @@
         <v>182</v>
       </c>
       <c r="C135" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="D135" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -13567,19 +13993,19 @@
         <v>186</v>
       </c>
       <c r="J135" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="K135" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L135">
-        <v>4.2950214952425814</v>
+        <v>4.0988903046130218</v>
       </c>
       <c r="M135">
-        <v>0.19</v>
+        <v>0.1648640031148178</v>
       </c>
       <c r="N135">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="2:14">
@@ -13587,10 +14013,10 @@
         <v>182</v>
       </c>
       <c r="C136" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="D136" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -13605,19 +14031,19 @@
         <v>186</v>
       </c>
       <c r="J136" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="K136" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L136">
-        <v>4.5224792372855314</v>
+        <v>4.0988726922947114</v>
       </c>
       <c r="M136">
-        <v>0.189</v>
+        <v>0.1520135729443049</v>
       </c>
       <c r="N136">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="2:14">
@@ -13625,10 +14051,10 @@
         <v>182</v>
       </c>
       <c r="C137" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="D137" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -13643,19 +14069,19 @@
         <v>186</v>
       </c>
       <c r="J137" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="K137" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L137">
         <v>6.5715455615362517</v>
       </c>
       <c r="M137">
-        <v>0.185</v>
+        <v>0.151708166751155</v>
       </c>
       <c r="N137">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="2:14">
@@ -13663,10 +14089,10 @@
         <v>182</v>
       </c>
       <c r="C138" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D138" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -13681,19 +14107,19 @@
         <v>186</v>
       </c>
       <c r="J138" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="K138" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L138">
-        <v>7.252914863655616</v>
+        <v>5.7751350324233295</v>
       </c>
       <c r="M138">
-        <v>0.18351752774567745</v>
+        <v>0.15002509122581789</v>
       </c>
       <c r="N138">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="2:14">
@@ -13701,10 +14127,10 @@
         <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="D139" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -13719,19 +14145,19 @@
         <v>186</v>
       </c>
       <c r="J139" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="K139" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L139">
-        <v>9.8740077247180409</v>
+        <v>3.8163562619350917</v>
       </c>
       <c r="M139">
-        <v>0.18216976514368449</v>
+        <v>0.1486604569627136</v>
       </c>
       <c r="N139">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="2:14">
@@ -13739,10 +14165,10 @@
         <v>182</v>
       </c>
       <c r="C140" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D140" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -13757,19 +14183,19 @@
         <v>186</v>
       </c>
       <c r="J140" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="K140" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L140">
-        <v>0.82040396789140502</v>
+        <v>3.8459913153191176</v>
       </c>
       <c r="M140">
-        <v>0.17899999999999999</v>
+        <v>0.14069336661847687</v>
       </c>
       <c r="N140">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="2:14">
@@ -13777,10 +14203,10 @@
         <v>182</v>
       </c>
       <c r="C141" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="D141" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -13795,19 +14221,19 @@
         <v>186</v>
       </c>
       <c r="J141" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="K141" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L141">
-        <v>8.6591881426587864</v>
+        <v>3.4993301846775999</v>
       </c>
       <c r="M141">
-        <v>0.17755584851005002</v>
+        <v>0.1335690204311058</v>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="2:14">
@@ -13815,10 +14241,10 @@
         <v>182</v>
       </c>
       <c r="C142" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="D142" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -13833,19 +14259,19 @@
         <v>186</v>
       </c>
       <c r="J142" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="K142" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L142">
-        <v>2.2385167735403306</v>
+        <v>4.930205144235063</v>
       </c>
       <c r="M142">
-        <v>0.17599999999999999</v>
+        <v>0.118271462242377</v>
       </c>
       <c r="N142">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="2:14">
@@ -13853,10 +14279,10 @@
         <v>182</v>
       </c>
       <c r="C143" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="D143" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -13871,19 +14297,19 @@
         <v>186</v>
       </c>
       <c r="J143" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="K143" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L143">
-        <v>5.4261482771080383</v>
+        <v>4.8131968273396684</v>
       </c>
       <c r="M143">
-        <v>0.17299999999999999</v>
+        <v>0.11361008554715601</v>
       </c>
       <c r="N143">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="2:14">
@@ -13891,10 +14317,10 @@
         <v>182</v>
       </c>
       <c r="C144" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="D144" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -13909,19 +14335,19 @@
         <v>186</v>
       </c>
       <c r="J144" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="K144" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L144">
-        <v>1.4790050900062073</v>
+        <v>3.7535846789780156</v>
       </c>
       <c r="M144">
-        <v>0.16700000000000001</v>
+        <v>0.1106928942651814</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="2:14">
@@ -13929,10 +14355,10 @@
         <v>182</v>
       </c>
       <c r="C145" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="D145" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -13947,16 +14373,16 @@
         <v>186</v>
       </c>
       <c r="J145" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="K145" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L145">
-        <v>1.3949784753138748</v>
+        <v>4.2950214952425814</v>
       </c>
       <c r="M145">
-        <v>0.16400000000000001</v>
+        <v>0.1038043665341269</v>
       </c>
       <c r="N145">
         <v>1</v>
@@ -13967,10 +14393,10 @@
         <v>182</v>
       </c>
       <c r="C146" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="D146" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -13985,19 +14411,19 @@
         <v>186</v>
       </c>
       <c r="J146" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="K146" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L146">
-        <v>5.4637182537171771</v>
+        <v>5.4261482771080383</v>
       </c>
       <c r="M146">
-        <v>0.159</v>
+        <v>9.3457654798712805E-2</v>
       </c>
       <c r="N146">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="2:14">
@@ -14005,10 +14431,10 @@
         <v>182</v>
       </c>
       <c r="C147" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="D147" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -14023,19 +14449,19 @@
         <v>186</v>
       </c>
       <c r="J147" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="K147" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L147">
-        <v>4.8709592243217905</v>
+        <v>5.4637182537171771</v>
       </c>
       <c r="M147">
-        <v>0.155</v>
+        <v>8.6101260740745103E-2</v>
       </c>
       <c r="N147">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="2:14">
@@ -14043,10 +14469,10 @@
         <v>182</v>
       </c>
       <c r="C148" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D148" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -14061,19 +14487,19 @@
         <v>186</v>
       </c>
       <c r="J148" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="K148" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L148">
-        <v>0.82815675434685676</v>
+        <v>4.8709592243217905</v>
       </c>
       <c r="M148">
-        <v>0.151</v>
+        <v>7.03514394781561E-2</v>
       </c>
       <c r="N148">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="2:14">
@@ -14081,10 +14507,10 @@
         <v>182</v>
       </c>
       <c r="C149" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="D149" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -14099,18 +14525,208 @@
         <v>186</v>
       </c>
       <c r="J149" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="K149" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="L149">
-        <v>4.930205144235063</v>
+        <v>2.80276811983259</v>
       </c>
       <c r="M149">
-        <v>0.14899999999999999</v>
+        <v>5.1050580434309392E-2</v>
       </c>
       <c r="N149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:14">
+      <c r="B150" t="s">
+        <v>182</v>
+      </c>
+      <c r="C150" t="s">
+        <v>516</v>
+      </c>
+      <c r="D150" t="s">
+        <v>517</v>
+      </c>
+      <c r="E150" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" t="s">
+        <v>21</v>
+      </c>
+      <c r="G150" t="s">
+        <v>185</v>
+      </c>
+      <c r="H150" t="s">
+        <v>186</v>
+      </c>
+      <c r="J150" t="s">
+        <v>516</v>
+      </c>
+      <c r="K150" t="s">
+        <v>526</v>
+      </c>
+      <c r="L150">
+        <v>2.2385167735403306</v>
+      </c>
+      <c r="M150">
+        <v>5.0246123962461697E-2</v>
+      </c>
+      <c r="N150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="2:14">
+      <c r="B151" t="s">
+        <v>182</v>
+      </c>
+      <c r="C151" t="s">
+        <v>518</v>
+      </c>
+      <c r="D151" t="s">
+        <v>519</v>
+      </c>
+      <c r="E151" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" t="s">
+        <v>21</v>
+      </c>
+      <c r="G151" t="s">
+        <v>185</v>
+      </c>
+      <c r="H151" t="s">
+        <v>186</v>
+      </c>
+      <c r="J151" t="s">
+        <v>518</v>
+      </c>
+      <c r="K151" t="s">
+        <v>526</v>
+      </c>
+      <c r="L151">
+        <v>1.4790050900062073</v>
+      </c>
+      <c r="M151">
+        <v>2.8461322395155499E-2</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="2:14">
+      <c r="B152" t="s">
+        <v>182</v>
+      </c>
+      <c r="C152" t="s">
+        <v>520</v>
+      </c>
+      <c r="D152" t="s">
+        <v>521</v>
+      </c>
+      <c r="E152" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" t="s">
+        <v>21</v>
+      </c>
+      <c r="G152" t="s">
+        <v>185</v>
+      </c>
+      <c r="H152" t="s">
+        <v>186</v>
+      </c>
+      <c r="J152" t="s">
+        <v>520</v>
+      </c>
+      <c r="K152" t="s">
+        <v>526</v>
+      </c>
+      <c r="L152">
+        <v>1.3949784753138748</v>
+      </c>
+      <c r="M152">
+        <v>2.8014890642676902E-2</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="2:14">
+      <c r="B153" t="s">
+        <v>182</v>
+      </c>
+      <c r="C153" t="s">
+        <v>522</v>
+      </c>
+      <c r="D153" t="s">
+        <v>523</v>
+      </c>
+      <c r="E153" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153" t="s">
+        <v>21</v>
+      </c>
+      <c r="G153" t="s">
+        <v>185</v>
+      </c>
+      <c r="H153" t="s">
+        <v>186</v>
+      </c>
+      <c r="J153" t="s">
+        <v>522</v>
+      </c>
+      <c r="K153" t="s">
+        <v>526</v>
+      </c>
+      <c r="L153">
+        <v>0.82815675434685676</v>
+      </c>
+      <c r="M153">
+        <v>2.1418931566030801E-2</v>
+      </c>
+      <c r="N153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="2:14">
+      <c r="B154" t="s">
+        <v>182</v>
+      </c>
+      <c r="C154" t="s">
+        <v>524</v>
+      </c>
+      <c r="D154" t="s">
+        <v>525</v>
+      </c>
+      <c r="E154" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" t="s">
+        <v>21</v>
+      </c>
+      <c r="G154" t="s">
+        <v>185</v>
+      </c>
+      <c r="H154" t="s">
+        <v>186</v>
+      </c>
+      <c r="J154" t="s">
+        <v>524</v>
+      </c>
+      <c r="K154" t="s">
+        <v>526</v>
+      </c>
+      <c r="L154">
+        <v>0.82040396789140502</v>
+      </c>
+      <c r="M154">
+        <v>2.02272857010726E-2</v>
+      </c>
+      <c r="N154">
         <v>1</v>
       </c>
     </row>
@@ -14120,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EB3E35-2298-4C79-92A0-BCF2FBC49252}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1FE5DE-32CB-42D7-A81E-5353E2A0627D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14137,10 +14753,10 @@
         <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -14178,7 +14794,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -14202,7 +14818,7 @@
         <v>182</v>
       </c>
       <c r="K11" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -14211,15 +14827,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P11" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -14237,13 +14853,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="J12" t="s">
         <v>182</v>
       </c>
       <c r="K12" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -14252,15 +14868,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P12" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -14278,13 +14894,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="J13" t="s">
         <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -14293,15 +14909,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P13" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -14319,13 +14935,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="J14" t="s">
         <v>182</v>
       </c>
       <c r="K14" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -14334,15 +14950,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P14" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -14360,13 +14976,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="J15" t="s">
         <v>182</v>
       </c>
       <c r="K15" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -14375,15 +14991,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P15" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -14407,7 +15023,7 @@
         <v>182</v>
       </c>
       <c r="K16" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -14416,15 +15032,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P16" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -14442,13 +15058,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="J17" t="s">
         <v>182</v>
       </c>
       <c r="K17" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -14457,15 +15073,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P17" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -14483,13 +15099,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="J18" t="s">
         <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -14498,15 +15114,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P18" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -14524,13 +15140,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="J19" t="s">
         <v>182</v>
       </c>
       <c r="K19" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -14539,15 +15155,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P19" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -14565,13 +15181,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="J20" t="s">
         <v>182</v>
       </c>
       <c r="K20" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -14580,15 +15196,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P20" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -14612,7 +15228,7 @@
         <v>182</v>
       </c>
       <c r="K21" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -14621,15 +15237,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P21" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -14647,13 +15263,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="J22" t="s">
         <v>182</v>
       </c>
       <c r="K22" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -14662,15 +15278,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P22" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -14688,13 +15304,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="J23" t="s">
         <v>182</v>
       </c>
       <c r="K23" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -14703,15 +15319,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P23" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -14735,7 +15351,7 @@
         <v>182</v>
       </c>
       <c r="K24" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -14744,15 +15360,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P24" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -14770,13 +15386,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="J25" t="s">
         <v>182</v>
       </c>
       <c r="K25" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -14785,15 +15401,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P25" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -14811,13 +15427,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="J26" t="s">
         <v>182</v>
       </c>
       <c r="K26" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -14826,15 +15442,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P26" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -14858,7 +15474,7 @@
         <v>182</v>
       </c>
       <c r="K27" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -14867,15 +15483,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="P27" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -14893,12 +15509,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -14916,12 +15532,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -14944,7 +15560,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -14962,12 +15578,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -14985,12 +15601,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -15013,7 +15629,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -15031,12 +15647,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -15054,12 +15670,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -15077,12 +15693,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -15100,12 +15716,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -15128,7 +15744,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -15146,12 +15762,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -15169,12 +15785,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -15197,7 +15813,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -15215,12 +15831,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -15238,12 +15854,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -15266,7 +15882,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -15284,12 +15900,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -15307,12 +15923,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -15335,7 +15951,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -15353,12 +15969,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -15376,12 +15992,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -15404,7 +16020,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -15422,12 +16038,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -15445,12 +16061,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -15468,12 +16084,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -15491,12 +16107,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -15519,7 +16135,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -15537,12 +16153,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -15560,12 +16176,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -15588,7 +16204,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -15606,12 +16222,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -15629,12 +16245,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -15657,7 +16273,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -15675,12 +16291,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -15698,15 +16314,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="C64" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -15726,10 +16342,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="C65" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -15744,15 +16360,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="C66" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -15767,15 +16383,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="C67" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -15790,15 +16406,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="C68" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -15813,15 +16429,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C69" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -15841,10 +16457,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C70" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -15859,15 +16475,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C71" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -15882,15 +16498,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C72" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -15905,15 +16521,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C73" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -15928,7 +16544,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52486C56-C2AD-48C8-BC68-06B5C5DFFE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2834FF70-F0A9-4433-B508-ED8293A4509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6866,7 +6866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7314F02B-E03D-4979-8E2B-EE9344C32764}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C87FCBB-0CDA-4F98-8A31-58215B1DA76F}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7834,7 +7834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E74485-4207-4546-BC54-D0DEAA9D4472}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C055281-58B2-46AB-97F2-C6B64ABC1F41}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14736,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1FE5DE-32CB-42D7-A81E-5353E2A0627D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B4F9C7C-6206-42F3-A678-5C13ABF0B085}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2834FF70-F0A9-4433-B508-ED8293A4509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B7DABF7-B4FF-413C-A7FF-709160ECDB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6866,7 +6866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C87FCBB-0CDA-4F98-8A31-58215B1DA76F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EB2D6B-0ABD-4C3A-AD10-739512ADB08E}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7834,7 +7834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C055281-58B2-46AB-97F2-C6B64ABC1F41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4865EA13-E4D3-4648-95F1-BD77EF6AD29E}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14736,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B4F9C7C-6206-42F3-A678-5C13ABF0B085}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C3FCE1-F906-4899-8B4F-F7BB31F020E3}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B7DABF7-B4FF-413C-A7FF-709160ECDB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39B8FEF8-E347-4ACE-B032-86336CB9364B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6866,7 +6866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EB2D6B-0ABD-4C3A-AD10-739512ADB08E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810BAD24-9CA4-4ED4-9FEA-0AFD7B9F166D}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7290,7 +7290,7 @@
         <v>31.76985587454876</v>
       </c>
       <c r="M20">
-        <v>0.15245170977190434</v>
+        <v>0.15245170977190436</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -7442,7 +7442,7 @@
         <v>11.345704435831776</v>
       </c>
       <c r="M24">
-        <v>0.14643457270381485</v>
+        <v>0.14643457270381488</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -7518,7 +7518,7 @@
         <v>40.021838922783786</v>
       </c>
       <c r="M26">
-        <v>0.13854439301816671</v>
+        <v>0.13854439301816673</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -7556,7 +7556,7 @@
         <v>48.571657115533917</v>
       </c>
       <c r="M27">
-        <v>0.13802198772305829</v>
+        <v>0.13802198772305835</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -7594,7 +7594,7 @@
         <v>45.353475554365239</v>
       </c>
       <c r="M28">
-        <v>0.13702217040516357</v>
+        <v>0.1370221704051636</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -7670,7 +7670,7 @@
         <v>39.024506669608691</v>
       </c>
       <c r="M30">
-        <v>0.13376619369545326</v>
+        <v>0.13376619369545328</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -7746,7 +7746,7 @@
         <v>28.180219467472426</v>
       </c>
       <c r="M32">
-        <v>0.13338367781240143</v>
+        <v>0.13338367781240146</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -7834,7 +7834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4865EA13-E4D3-4648-95F1-BD77EF6AD29E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D186C2B-91D9-4D17-9D6D-2E01A00F0DC9}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7958,7 +7958,7 @@
         <v>7.6602564102564094E-3</v>
       </c>
       <c r="M11">
-        <v>0.60547369604706214</v>
+        <v>0.60547369459975697</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -8032,7 +8032,7 @@
         <v>8.8807957153787295E-2</v>
       </c>
       <c r="M12">
-        <v>0.57960586454463925</v>
+        <v>0.57960586277235726</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -8106,7 +8106,7 @@
         <v>0.1551219562401488</v>
       </c>
       <c r="M13">
-        <v>0.57320959241145331</v>
+        <v>0.57320959071863131</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -8180,7 +8180,7 @@
         <v>0.62654719309068485</v>
       </c>
       <c r="M14">
-        <v>0.57299534979618882</v>
+        <v>0.57299534824167275</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -8254,7 +8254,7 @@
         <v>0.14665964293128506</v>
       </c>
       <c r="M15">
-        <v>0.56455391735389493</v>
+        <v>0.5645539157425693</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -8290,7 +8290,7 @@
         <v>13.8675</v>
       </c>
       <c r="AA15">
-        <v>0.57256891372683982</v>
+        <v>0.57256891372683993</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -8328,7 +8328,7 @@
         <v>0.1374704812888238</v>
       </c>
       <c r="M16">
-        <v>0.55646086641743908</v>
+        <v>0.55646086427497155</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -8402,7 +8402,7 @@
         <v>0.30943732119635886</v>
       </c>
       <c r="M17">
-        <v>0.55571876678834353</v>
+        <v>0.55571876473693327</v>
       </c>
       <c r="N17">
         <v>3</v>
@@ -8476,7 +8476,7 @@
         <v>1.3855212742120202</v>
       </c>
       <c r="M18">
-        <v>0.55538842146607259</v>
+        <v>0.55538841965506003</v>
       </c>
       <c r="N18">
         <v>4</v>
@@ -8550,7 +8550,7 @@
         <v>0.58742454465550076</v>
       </c>
       <c r="M19">
-        <v>0.54362148490056739</v>
+        <v>0.54362148288577916</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -8624,7 +8624,7 @@
         <v>1.4212499999999999</v>
       </c>
       <c r="M20">
-        <v>0.51172011645728255</v>
+        <v>0.51172011461352251</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -8698,7 +8698,7 @@
         <v>1.3176292984869329</v>
       </c>
       <c r="M21">
-        <v>0.50785221851711282</v>
+        <v>0.50785221656308632</v>
       </c>
       <c r="N21">
         <v>2</v>
@@ -8772,7 +8772,7 @@
         <v>0.94391071885781108</v>
       </c>
       <c r="M22">
-        <v>0.50527134774735971</v>
+        <v>0.50527134581540512</v>
       </c>
       <c r="N22">
         <v>3</v>
@@ -8846,7 +8846,7 @@
         <v>0.52875913363466021</v>
       </c>
       <c r="M23">
-        <v>0.5000100636922703</v>
+        <v>0.50001006202105125</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -8920,7 +8920,7 @@
         <v>0.95119682831310748</v>
       </c>
       <c r="M24">
-        <v>0.47927323018315537</v>
+        <v>0.47927322850462512</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         <v>3.4628263818732856</v>
       </c>
       <c r="M25">
-        <v>0.47395544719054761</v>
+        <v>0.47395544524054306</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -9030,7 +9030,7 @@
         <v>13.8675</v>
       </c>
       <c r="AA25">
-        <v>0.51308140128455426</v>
+        <v>0.51308140128455437</v>
       </c>
       <c r="AB25">
         <v>2</v>
@@ -9068,7 +9068,7 @@
         <v>2.5383421781044189</v>
       </c>
       <c r="M26">
-        <v>0.4679272704745196</v>
+        <v>0.46792726807338542</v>
       </c>
       <c r="N26">
         <v>2</v>
@@ -9142,7 +9142,7 @@
         <v>0.93356002702813012</v>
       </c>
       <c r="M27">
-        <v>0.4617910666503538</v>
+        <v>0.4617910648584963</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -9216,7 +9216,7 @@
         <v>3.416737782360558</v>
       </c>
       <c r="M28">
-        <v>0.45911415041508086</v>
+        <v>0.45911414824251678</v>
       </c>
       <c r="N28">
         <v>1</v>
@@ -9290,7 +9290,7 @@
         <v>3.5420807364753699</v>
       </c>
       <c r="M29">
-        <v>0.45349251926597589</v>
+        <v>0.45349251767449378</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -9364,7 +9364,7 @@
         <v>4.5376647457138732</v>
       </c>
       <c r="M30">
-        <v>0.44728008221576948</v>
+        <v>0.44728008046218609</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -9438,7 +9438,7 @@
         <v>2.8129591489571522</v>
       </c>
       <c r="M31">
-        <v>0.43447773296025288</v>
+        <v>0.4344777299537888</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -9512,7 +9512,7 @@
         <v>4.0798187691058461</v>
       </c>
       <c r="M32">
-        <v>0.43159159220331572</v>
+        <v>0.43159158985285878</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -9586,7 +9586,7 @@
         <v>3.9527508633093529</v>
       </c>
       <c r="M33">
-        <v>0.41804908680458558</v>
+        <v>0.41804908528666901</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -9660,7 +9660,7 @@
         <v>4.884892809638619</v>
       </c>
       <c r="M34">
-        <v>0.41321055018703212</v>
+        <v>0.41321054817565978</v>
       </c>
       <c r="N34">
         <v>2</v>
@@ -9734,7 +9734,7 @@
         <v>4.8667662261345104</v>
       </c>
       <c r="M35">
-        <v>0.41233198565551887</v>
+        <v>0.41233198412011868</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -9770,7 +9770,7 @@
         <v>5.9212499999999997</v>
       </c>
       <c r="AA35">
-        <v>0.39574838482740898</v>
+        <v>0.39574838482740909</v>
       </c>
       <c r="AB35">
         <v>2</v>
@@ -9808,7 +9808,7 @@
         <v>3.8112316593784894</v>
       </c>
       <c r="M36">
-        <v>0.40294995999097311</v>
+        <v>0.40294995773628312</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -9882,7 +9882,7 @@
         <v>2.409816641133665</v>
       </c>
       <c r="M37">
-        <v>0.39697151968295202</v>
+        <v>0.39697151719775908</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -9956,7 +9956,7 @@
         <v>4.2242993630573249</v>
       </c>
       <c r="M38">
-        <v>0.39521220594388218</v>
+        <v>0.39521220456451511</v>
       </c>
       <c r="N38">
         <v>2</v>
@@ -9992,7 +9992,7 @@
         <v>1.0075000000000001</v>
       </c>
       <c r="AA38">
-        <v>0.33980836295119587</v>
+        <v>0.33980836295119599</v>
       </c>
       <c r="AB38">
         <v>1</v>
@@ -10030,7 +10030,7 @@
         <v>1.5770138627625505</v>
       </c>
       <c r="M39">
-        <v>0.39414986229971999</v>
+        <v>0.39414985830149268</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         <v>4.8593444496597042</v>
       </c>
       <c r="M40">
-        <v>0.38201746921684659</v>
+        <v>0.3820174674652832</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -10140,7 +10140,7 @@
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="AA40">
-        <v>0.31079819338694031</v>
+        <v>0.31079819338694042</v>
       </c>
       <c r="AB40">
         <v>1</v>
@@ -10178,7 +10178,7 @@
         <v>5.0095686646967783</v>
       </c>
       <c r="M41">
-        <v>0.37434168064361761</v>
+        <v>0.3743416786729723</v>
       </c>
       <c r="N41">
         <v>1</v>
@@ -10252,7 +10252,7 @@
         <v>4.8352011138905935</v>
       </c>
       <c r="M42">
-        <v>0.36917162151179039</v>
+        <v>0.36917161896226591</v>
       </c>
       <c r="N42">
         <v>2</v>
@@ -10326,7 +10326,7 @@
         <v>5.0859902905998453</v>
       </c>
       <c r="M43">
-        <v>0.36453803340134289</v>
+        <v>0.36453803091115888</v>
       </c>
       <c r="N43">
         <v>3</v>
@@ -10400,7 +10400,7 @@
         <v>5.2147718856773482</v>
       </c>
       <c r="M44">
-        <v>0.36281825576124332</v>
+        <v>0.3628182539284851</v>
       </c>
       <c r="N44">
         <v>2</v>
@@ -10474,7 +10474,7 @@
         <v>4.4937013078329349</v>
       </c>
       <c r="M45">
-        <v>0.36076949931521968</v>
+        <v>0.3607694973981791</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -10548,7 +10548,7 @@
         <v>4.864937090544406</v>
       </c>
       <c r="M46">
-        <v>0.3503211333347076</v>
+        <v>0.35032113092415978</v>
       </c>
       <c r="N46">
         <v>2</v>
@@ -10622,7 +10622,7 @@
         <v>4.9670647324483372</v>
       </c>
       <c r="M47">
-        <v>0.34982996232856922</v>
+        <v>0.3498299603350396</v>
       </c>
       <c r="N47">
         <v>4</v>
@@ -10696,7 +10696,7 @@
         <v>4.0865774761939289</v>
       </c>
       <c r="M48">
-        <v>0.3472447936452937</v>
+        <v>0.3472447912656928</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -10734,7 +10734,7 @@
         <v>5.0295832058946193</v>
       </c>
       <c r="M49">
-        <v>0.3460630650440007</v>
+        <v>0.34606306291633138</v>
       </c>
       <c r="N49">
         <v>3</v>
@@ -10772,7 +10772,7 @@
         <v>4.7590365600332367</v>
       </c>
       <c r="M50">
-        <v>0.34578516432535861</v>
+        <v>0.34578516228476841</v>
       </c>
       <c r="N50">
         <v>1</v>
@@ -10810,7 +10810,7 @@
         <v>9.2249743054143138</v>
       </c>
       <c r="M51">
-        <v>0.34285785438460714</v>
+        <v>0.3428578527197777</v>
       </c>
       <c r="N51">
         <v>3</v>
@@ -10848,7 +10848,7 @@
         <v>10.162442082612424</v>
       </c>
       <c r="M52">
-        <v>0.34279793123163405</v>
+        <v>0.34279792913455059</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -10886,7 +10886,7 @@
         <v>10.078696955477335</v>
       </c>
       <c r="M53">
-        <v>0.34158625076062854</v>
+        <v>0.34158624845681934</v>
       </c>
       <c r="N53">
         <v>2</v>
@@ -10924,7 +10924,7 @@
         <v>4.9779003558185355</v>
       </c>
       <c r="M54">
-        <v>0.3380798122756935</v>
+        <v>0.33807980994690412</v>
       </c>
       <c r="N54">
         <v>4</v>
@@ -10962,7 +10962,7 @@
         <v>4.8624568965517234</v>
       </c>
       <c r="M55">
-        <v>0.33565465890466423</v>
+        <v>0.33565465632149599</v>
       </c>
       <c r="N55">
         <v>5</v>
@@ -11000,7 +11000,7 @@
         <v>9.8449316059724268</v>
       </c>
       <c r="M56">
-        <v>0.33226926477026636</v>
+        <v>0.3322692638220992</v>
       </c>
       <c r="N56">
         <v>3</v>
@@ -11038,7 +11038,7 @@
         <v>9.6603381550950918</v>
       </c>
       <c r="M57">
-        <v>0.33156823883970526</v>
+        <v>0.33156823691170589</v>
       </c>
       <c r="N57">
         <v>5</v>
@@ -11076,7 +11076,7 @@
         <v>9.8531956921453343</v>
       </c>
       <c r="M58">
-        <v>0.33106249230449969</v>
+        <v>0.33106249057951342</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -11114,7 +11114,7 @@
         <v>9.7342520722063561</v>
       </c>
       <c r="M59">
-        <v>0.33066551064847061</v>
+        <v>0.3306655084920585</v>
       </c>
       <c r="N59">
         <v>4</v>
@@ -11152,7 +11152,7 @@
         <v>10.171034508796986</v>
       </c>
       <c r="M60">
-        <v>0.32927477705262759</v>
+        <v>0.32927477568116531</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -11190,7 +11190,7 @@
         <v>5.8636933378977174</v>
       </c>
       <c r="M61">
-        <v>0.3248909103796751</v>
+        <v>0.32489090867860138</v>
       </c>
       <c r="N61">
         <v>3</v>
@@ -11228,7 +11228,7 @@
         <v>5.2073607071727208</v>
       </c>
       <c r="M62">
-        <v>0.32233893827024601</v>
+        <v>0.32233893759448817</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -11266,7 +11266,7 @@
         <v>9.9178501900121336</v>
       </c>
       <c r="M63">
-        <v>0.32228450210616966</v>
+        <v>0.32228449992752656</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -11304,7 +11304,7 @@
         <v>6.8389936670565934</v>
       </c>
       <c r="M64">
-        <v>0.32000561918811904</v>
+        <v>0.3200056176289337</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -11342,7 +11342,7 @@
         <v>4.6341036452401667</v>
       </c>
       <c r="M65">
-        <v>0.31646037881333522</v>
+        <v>0.31646037649751307</v>
       </c>
       <c r="N65">
         <v>4</v>
@@ -11380,7 +11380,7 @@
         <v>4.5300945728056137</v>
       </c>
       <c r="M66">
-        <v>0.3136383423020469</v>
+        <v>0.31363834062700813</v>
       </c>
       <c r="N66">
         <v>3</v>
@@ -11418,7 +11418,7 @@
         <v>9.4561009250765817</v>
       </c>
       <c r="M67">
-        <v>0.31030223441492688</v>
+        <v>0.31030223374142674</v>
       </c>
       <c r="N67">
         <v>2</v>
@@ -11456,7 +11456,7 @@
         <v>9.7651890086484059</v>
       </c>
       <c r="M68">
-        <v>0.30928005846085321</v>
+        <v>0.30928005602540132</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -11494,7 +11494,7 @@
         <v>5.1889235567804528</v>
       </c>
       <c r="M69">
-        <v>0.30647247396222338</v>
+        <v>0.30647247188410048</v>
       </c>
       <c r="N69">
         <v>5</v>
@@ -11532,7 +11532,7 @@
         <v>4.5845280146163221</v>
       </c>
       <c r="M70">
-        <v>0.30527266685973509</v>
+        <v>0.30527266500478428</v>
       </c>
       <c r="N70">
         <v>4</v>
@@ -11570,7 +11570,7 @@
         <v>9.7757411548018869</v>
       </c>
       <c r="M71">
-        <v>0.30271365513090243</v>
+        <v>0.30271365302893394</v>
       </c>
       <c r="N71">
         <v>1</v>
@@ -11608,7 +11608,7 @@
         <v>8.7928204064541671</v>
       </c>
       <c r="M72">
-        <v>0.30222147759349077</v>
+        <v>0.30222147545214612</v>
       </c>
       <c r="N72">
         <v>3</v>
@@ -11646,7 +11646,7 @@
         <v>10.853822805485695</v>
       </c>
       <c r="M73">
-        <v>0.30212238345838427</v>
+        <v>0.30212238197226754</v>
       </c>
       <c r="N73">
         <v>2</v>
@@ -11684,7 +11684,7 @@
         <v>7.2570352571720447</v>
       </c>
       <c r="M74">
-        <v>0.30123828002817632</v>
+        <v>0.30123827799542469</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -11722,7 +11722,7 @@
         <v>4.2847170222576185</v>
       </c>
       <c r="M75">
-        <v>0.2956005552279718</v>
+        <v>0.29560055282886211</v>
       </c>
       <c r="N75">
         <v>4</v>
@@ -11760,7 +11760,7 @@
         <v>9.3356103729736137</v>
       </c>
       <c r="M76">
-        <v>0.29235708013785633</v>
+        <v>0.29235707902326624</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -11798,7 +11798,7 @@
         <v>10.323603545198891</v>
       </c>
       <c r="M77">
-        <v>0.29127209469703913</v>
+        <v>0.29127209234316404</v>
       </c>
       <c r="N77">
         <v>2</v>
@@ -11836,7 +11836,7 @@
         <v>10.389781968556326</v>
       </c>
       <c r="M78">
-        <v>0.29059600086907184</v>
+        <v>0.29059599914276357</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -11874,7 +11874,7 @@
         <v>4.349000942121001</v>
       </c>
       <c r="M79">
-        <v>0.28641433365004793</v>
+        <v>0.28641433173189279</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -11912,7 +11912,7 @@
         <v>4.4041130325814537</v>
       </c>
       <c r="M80">
-        <v>0.28531699904219149</v>
+        <v>0.28531699677131922</v>
       </c>
       <c r="N80">
         <v>4</v>
@@ -11950,7 +11950,7 @@
         <v>14.037217310255906</v>
       </c>
       <c r="M81">
-        <v>0.28196520200495223</v>
+        <v>0.28196520062342001</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -11988,7 +11988,7 @@
         <v>8.9607984660082689</v>
       </c>
       <c r="M82">
-        <v>0.2808542360260754</v>
+        <v>0.28085423423869033</v>
       </c>
       <c r="N82">
         <v>2</v>
@@ -12026,7 +12026,7 @@
         <v>8.8076619859689522</v>
       </c>
       <c r="M83">
-        <v>0.27999907827374398</v>
+        <v>0.27999907638959548</v>
       </c>
       <c r="N83">
         <v>3</v>
@@ -12064,7 +12064,7 @@
         <v>9.4899910812682915</v>
       </c>
       <c r="M84">
-        <v>0.27934170908276346</v>
+        <v>0.27934170743566378</v>
       </c>
       <c r="N84">
         <v>4</v>
@@ -12102,7 +12102,7 @@
         <v>10.4340449150087</v>
       </c>
       <c r="M85">
-        <v>0.27930358727980914</v>
+        <v>0.27930358575103875</v>
       </c>
       <c r="N85">
         <v>5</v>
@@ -12140,7 +12140,7 @@
         <v>9.3956864382108716</v>
       </c>
       <c r="M86">
-        <v>0.27318489220241343</v>
+        <v>0.27318488945394259</v>
       </c>
       <c r="N86">
         <v>4</v>
@@ -12178,7 +12178,7 @@
         <v>11.393043209503709</v>
       </c>
       <c r="M87">
-        <v>0.27142064905861385</v>
+        <v>0.27142064744404742</v>
       </c>
       <c r="N87">
         <v>5</v>
@@ -12216,7 +12216,7 @@
         <v>14.592800093292185</v>
       </c>
       <c r="M88">
-        <v>0.2700610497913693</v>
+        <v>0.27006104793515517</v>
       </c>
       <c r="N88">
         <v>2</v>
@@ -12254,7 +12254,7 @@
         <v>13.458204803075256</v>
       </c>
       <c r="M89">
-        <v>0.26833205727454035</v>
+        <v>0.26833205537859922</v>
       </c>
       <c r="N89">
         <v>1</v>
@@ -12292,7 +12292,7 @@
         <v>17.721809343695792</v>
       </c>
       <c r="M90">
-        <v>0.26783763780350478</v>
+        <v>0.26783763607733502</v>
       </c>
       <c r="N90">
         <v>3</v>
@@ -12330,7 +12330,7 @@
         <v>9.7551758540067581</v>
       </c>
       <c r="M91">
-        <v>0.26359071936102701</v>
+        <v>0.26359071765388276</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -12368,7 +12368,7 @@
         <v>4.5110170134884706</v>
       </c>
       <c r="M92">
-        <v>0.26353984242186729</v>
+        <v>0.26353984088771021</v>
       </c>
       <c r="N92">
         <v>4</v>
@@ -12406,7 +12406,7 @@
         <v>13.410065064912054</v>
       </c>
       <c r="M93">
-        <v>0.26102455301053762</v>
+        <v>0.26102455157877769</v>
       </c>
       <c r="N93">
         <v>2</v>
@@ -12444,7 +12444,7 @@
         <v>6.1158273598366639</v>
       </c>
       <c r="M94">
-        <v>0.26017150954454588</v>
+        <v>0.2601715080446072</v>
       </c>
       <c r="N94">
         <v>3</v>
@@ -12482,7 +12482,7 @@
         <v>6.4809362742382701</v>
       </c>
       <c r="M95">
-        <v>0.25624716754528271</v>
+        <v>0.25624716591748109</v>
       </c>
       <c r="N95">
         <v>5</v>
@@ -12520,7 +12520,7 @@
         <v>6.3534573390116744</v>
       </c>
       <c r="M96">
-        <v>0.25437685697328188</v>
+        <v>0.25437685520508968</v>
       </c>
       <c r="N96">
         <v>5</v>
@@ -12558,7 +12558,7 @@
         <v>5.8074496044031649</v>
       </c>
       <c r="M97">
-        <v>0.25033910336926979</v>
+        <v>0.2503391014152675</v>
       </c>
       <c r="N97">
         <v>3</v>
@@ -12596,7 +12596,7 @@
         <v>11.806050025341166</v>
       </c>
       <c r="M98">
-        <v>0.25016362734905451</v>
+        <v>0.25016362630439687</v>
       </c>
       <c r="N98">
         <v>2</v>
@@ -12634,7 +12634,7 @@
         <v>11.507902266226953</v>
       </c>
       <c r="M99">
-        <v>0.24989506692241467</v>
+        <v>0.24989506559932739</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -12672,7 +12672,7 @@
         <v>5.796432202202026</v>
       </c>
       <c r="M100">
-        <v>0.24866879062703021</v>
+        <v>0.24866878798213549</v>
       </c>
       <c r="N100">
         <v>4</v>
@@ -12710,7 +12710,7 @@
         <v>6.6541321768552892</v>
       </c>
       <c r="M101">
-        <v>0.24453800228933562</v>
+        <v>0.2445380008188954</v>
       </c>
       <c r="N101">
         <v>1</v>
@@ -12748,7 +12748,7 @@
         <v>5.7512927167383499</v>
       </c>
       <c r="M102">
-        <v>0.23431152599072719</v>
+        <v>0.23431152477005632</v>
       </c>
       <c r="N102">
         <v>5</v>
@@ -12786,7 +12786,7 @@
         <v>12.112476207127504</v>
       </c>
       <c r="M103">
-        <v>0.23323129664541103</v>
+        <v>0.23323129491640357</v>
       </c>
       <c r="N103">
         <v>2</v>
@@ -12824,7 +12824,7 @@
         <v>12.115358303482328</v>
       </c>
       <c r="M104">
-        <v>0.23125192888807858</v>
+        <v>0.23125192804070546</v>
       </c>
       <c r="N104">
         <v>4</v>
@@ -12862,7 +12862,7 @@
         <v>11.124836329529094</v>
       </c>
       <c r="M105">
-        <v>0.22754429512905205</v>
+        <v>0.22754429327977335</v>
       </c>
       <c r="N105">
         <v>3</v>
@@ -12900,7 +12900,7 @@
         <v>9.8733558921199158</v>
       </c>
       <c r="M106">
-        <v>0.22599723087133788</v>
+        <v>0.22599722912697404</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -12938,7 +12938,7 @@
         <v>9.63317239541934</v>
       </c>
       <c r="M107">
-        <v>0.22245805250439696</v>
+        <v>0.22245805157358056</v>
       </c>
       <c r="N107">
         <v>3</v>
@@ -12976,7 +12976,7 @@
         <v>5.2729080193969784</v>
       </c>
       <c r="M108">
-        <v>0.2213539932129876</v>
+        <v>0.22135399182254506</v>
       </c>
       <c r="N108">
         <v>4</v>
@@ -13014,7 +13014,7 @@
         <v>10.175412746127334</v>
       </c>
       <c r="M109">
-        <v>0.21942069260339683</v>
+        <v>0.21942069123135383</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -13052,7 +13052,7 @@
         <v>10.637566675755002</v>
       </c>
       <c r="M110">
-        <v>0.21869248962298557</v>
+        <v>0.21869248832667817</v>
       </c>
       <c r="N110">
         <v>2</v>
@@ -13090,7 +13090,7 @@
         <v>4.7802762696690877</v>
       </c>
       <c r="M111">
-        <v>0.21709288081712197</v>
+        <v>0.21709288020169659</v>
       </c>
       <c r="N111">
         <v>5</v>
@@ -13128,7 +13128,7 @@
         <v>10.377164656431152</v>
       </c>
       <c r="M112">
-        <v>0.21302425401867695</v>
+        <v>0.21302425314347539</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -13166,7 +13166,7 @@
         <v>4.7565218753120782</v>
       </c>
       <c r="M113">
-        <v>0.21070878780867561</v>
+        <v>0.21070878680571881</v>
       </c>
       <c r="N113">
         <v>2</v>
@@ -13204,7 +13204,7 @@
         <v>5.1872871755483212</v>
       </c>
       <c r="M114">
-        <v>0.20857782756184373</v>
+        <v>0.20857782644740502</v>
       </c>
       <c r="N114">
         <v>4</v>
@@ -13242,7 +13242,7 @@
         <v>3.6695813919143436</v>
       </c>
       <c r="M115">
-        <v>0.20722419775208162</v>
+        <v>0.20722419658298077</v>
       </c>
       <c r="N115">
         <v>3</v>
@@ -13280,7 +13280,7 @@
         <v>3.8839401768989066</v>
       </c>
       <c r="M116">
-        <v>0.2069558113847936</v>
+        <v>0.20695580998172039</v>
       </c>
       <c r="N116">
         <v>5</v>
@@ -13318,7 +13318,7 @@
         <v>5.4735607016044732</v>
       </c>
       <c r="M117">
-        <v>0.20417104587625901</v>
+        <v>0.20417104329275609</v>
       </c>
       <c r="N117">
         <v>3</v>
@@ -13356,7 +13356,7 @@
         <v>4.8037288968289413</v>
       </c>
       <c r="M118">
-        <v>0.20381315305750669</v>
+        <v>0.2038131517359813</v>
       </c>
       <c r="N118">
         <v>2</v>
@@ -13394,7 +13394,7 @@
         <v>3.9482250883014016</v>
       </c>
       <c r="M119">
-        <v>0.19960804861015211</v>
+        <v>0.1996080472645532</v>
       </c>
       <c r="N119">
         <v>5</v>
@@ -13432,7 +13432,7 @@
         <v>5.5462366170639088</v>
       </c>
       <c r="M120">
-        <v>0.19874383548358607</v>
+        <v>0.19874383283157659</v>
       </c>
       <c r="N120">
         <v>4</v>
@@ -13470,7 +13470,7 @@
         <v>3.9990112146637284</v>
       </c>
       <c r="M121">
-        <v>0.1954346092831527</v>
+        <v>0.1954346079657463</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -13508,7 +13508,7 @@
         <v>4.8943617948361116</v>
       </c>
       <c r="M122">
-        <v>0.19307640154597469</v>
+        <v>0.19307639960476289</v>
       </c>
       <c r="N122">
         <v>2</v>
@@ -13546,7 +13546,7 @@
         <v>5.1668974571482398</v>
       </c>
       <c r="M123">
-        <v>0.1920373552511174</v>
+        <v>0.1920373536724134</v>
       </c>
       <c r="N123">
         <v>3</v>
@@ -13584,7 +13584,7 @@
         <v>4.5677412696440225</v>
       </c>
       <c r="M124">
-        <v>0.1910895850265463</v>
+        <v>0.19108958362595779</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -13622,7 +13622,7 @@
         <v>3.9739696310223738</v>
       </c>
       <c r="M125">
-        <v>0.18934356175103029</v>
+        <v>0.18934356025093971</v>
       </c>
       <c r="N125">
         <v>4</v>
@@ -13660,7 +13660,7 @@
         <v>4.0227726982097192</v>
       </c>
       <c r="M126">
-        <v>0.18492326876860271</v>
+        <v>0.1849232672997457</v>
       </c>
       <c r="N126">
         <v>3</v>
@@ -13698,7 +13698,7 @@
         <v>7.3773404508868436</v>
       </c>
       <c r="M127">
-        <v>0.18329917448629079</v>
+        <v>0.1832991729814972</v>
       </c>
       <c r="N127">
         <v>2</v>
@@ -13736,7 +13736,7 @@
         <v>7.5871443894149051</v>
       </c>
       <c r="M128">
-        <v>0.18297409649828716</v>
+        <v>0.18297409424774005</v>
       </c>
       <c r="N128">
         <v>1</v>
@@ -13774,7 +13774,7 @@
         <v>4.5224792372855314</v>
       </c>
       <c r="M129">
-        <v>0.1800625315270642</v>
+        <v>0.18006252950116119</v>
       </c>
       <c r="N129">
         <v>5</v>
@@ -13812,7 +13812,7 @@
         <v>4.8674343919848235</v>
       </c>
       <c r="M130">
-        <v>0.17649544137809611</v>
+        <v>0.17649544036905179</v>
       </c>
       <c r="N130">
         <v>4</v>
@@ -13850,7 +13850,7 @@
         <v>5.8454368835601898</v>
       </c>
       <c r="M131">
-        <v>0.17322038910379561</v>
+        <v>0.1732203879093798</v>
       </c>
       <c r="N131">
         <v>1</v>
@@ -13888,7 +13888,7 @@
         <v>5.2141117410869811</v>
       </c>
       <c r="M132">
-        <v>0.17119241346264749</v>
+        <v>0.1711924124503765</v>
       </c>
       <c r="N132">
         <v>2</v>
@@ -13926,7 +13926,7 @@
         <v>5.0344987238231607</v>
       </c>
       <c r="M133">
-        <v>0.1680996609254681</v>
+        <v>0.1680996603074745</v>
       </c>
       <c r="N133">
         <v>3</v>
@@ -13964,7 +13964,7 @@
         <v>6.0178716042520675</v>
       </c>
       <c r="M134">
-        <v>0.16530815223310119</v>
+        <v>0.16530815008516789</v>
       </c>
       <c r="N134">
         <v>4</v>
@@ -14002,7 +14002,7 @@
         <v>4.0988903046130218</v>
       </c>
       <c r="M135">
-        <v>0.1648640031148178</v>
+        <v>0.16486400117690181</v>
       </c>
       <c r="N135">
         <v>1</v>
@@ -14040,7 +14040,7 @@
         <v>4.0988726922947114</v>
       </c>
       <c r="M136">
-        <v>0.1520135729443049</v>
+        <v>0.15201357141239591</v>
       </c>
       <c r="N136">
         <v>4</v>
@@ -14078,7 +14078,7 @@
         <v>6.5715455615362517</v>
       </c>
       <c r="M137">
-        <v>0.151708166751155</v>
+        <v>0.1517081658239964</v>
       </c>
       <c r="N137">
         <v>3</v>
@@ -14116,7 +14116,7 @@
         <v>5.7751350324233295</v>
       </c>
       <c r="M138">
-        <v>0.15002509122581789</v>
+        <v>0.15002509036097891</v>
       </c>
       <c r="N138">
         <v>2</v>
@@ -14154,7 +14154,7 @@
         <v>3.8163562619350917</v>
       </c>
       <c r="M139">
-        <v>0.1486604569627136</v>
+        <v>0.14866045625091809</v>
       </c>
       <c r="N139">
         <v>1</v>
@@ -14192,7 +14192,7 @@
         <v>3.8459913153191176</v>
       </c>
       <c r="M140">
-        <v>0.14069336661847687</v>
+        <v>0.14069336577841449</v>
       </c>
       <c r="N140">
         <v>1</v>
@@ -14230,7 +14230,7 @@
         <v>3.4993301846775999</v>
       </c>
       <c r="M141">
-        <v>0.1335690204311058</v>
+        <v>0.1335690195898907</v>
       </c>
       <c r="N141">
         <v>1</v>
@@ -14268,7 +14268,7 @@
         <v>4.930205144235063</v>
       </c>
       <c r="M142">
-        <v>0.118271462242377</v>
+        <v>0.1182714616616439</v>
       </c>
       <c r="N142">
         <v>1</v>
@@ -14306,7 +14306,7 @@
         <v>4.8131968273396684</v>
       </c>
       <c r="M143">
-        <v>0.11361008554715601</v>
+        <v>0.11361008427809871</v>
       </c>
       <c r="N143">
         <v>2</v>
@@ -14344,7 +14344,7 @@
         <v>3.7535846789780156</v>
       </c>
       <c r="M144">
-        <v>0.1106928942651814</v>
+        <v>0.1106928936770296</v>
       </c>
       <c r="N144">
         <v>1</v>
@@ -14382,7 +14382,7 @@
         <v>4.2950214952425814</v>
       </c>
       <c r="M145">
-        <v>0.1038043665341269</v>
+        <v>0.1038043651041048</v>
       </c>
       <c r="N145">
         <v>1</v>
@@ -14420,7 +14420,7 @@
         <v>5.4261482771080383</v>
       </c>
       <c r="M146">
-        <v>9.3457654798712805E-2</v>
+        <v>9.3457654188586106E-2</v>
       </c>
       <c r="N146">
         <v>1</v>
@@ -14458,7 +14458,7 @@
         <v>5.4637182537171771</v>
       </c>
       <c r="M147">
-        <v>8.6101260740745103E-2</v>
+        <v>8.6101260350866501E-2</v>
       </c>
       <c r="N147">
         <v>2</v>
@@ -14496,7 +14496,7 @@
         <v>4.8709592243217905</v>
       </c>
       <c r="M148">
-        <v>7.03514394781561E-2</v>
+        <v>7.0351438964671095E-2</v>
       </c>
       <c r="N148">
         <v>1</v>
@@ -14534,7 +14534,7 @@
         <v>2.80276811983259</v>
       </c>
       <c r="M149">
-        <v>5.1050580434309392E-2</v>
+        <v>5.1050579825946095E-2</v>
       </c>
       <c r="N149">
         <v>1</v>
@@ -14572,7 +14572,7 @@
         <v>2.2385167735403306</v>
       </c>
       <c r="M150">
-        <v>5.0246123962461697E-2</v>
+        <v>5.0246123305733699E-2</v>
       </c>
       <c r="N150">
         <v>2</v>
@@ -14610,7 +14610,7 @@
         <v>1.4790050900062073</v>
       </c>
       <c r="M151">
-        <v>2.8461322395155499E-2</v>
+        <v>2.8461321578447496E-2</v>
       </c>
       <c r="N151">
         <v>1</v>
@@ -14648,7 +14648,7 @@
         <v>1.3949784753138748</v>
       </c>
       <c r="M152">
-        <v>2.8014890642676902E-2</v>
+        <v>2.80148902511233E-2</v>
       </c>
       <c r="N152">
         <v>2</v>
@@ -14686,7 +14686,7 @@
         <v>0.82815675434685676</v>
       </c>
       <c r="M153">
-        <v>2.1418931566030801E-2</v>
+        <v>2.1418931160766399E-2</v>
       </c>
       <c r="N153">
         <v>2</v>
@@ -14724,7 +14724,7 @@
         <v>0.82040396789140502</v>
       </c>
       <c r="M154">
-        <v>2.02272857010726E-2</v>
+        <v>2.0227285386603198E-2</v>
       </c>
       <c r="N154">
         <v>1</v>
@@ -14736,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C3FCE1-F906-4899-8B4F-F7BB31F020E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59145DE1-FF7D-4905-B298-2E1D9086176D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39B8FEF8-E347-4ACE-B032-86336CB9364B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8ADEE71-DE88-41B3-BF21-0CA19B0D086C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6866,7 +6866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810BAD24-9CA4-4ED4-9FEA-0AFD7B9F166D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85F9C99-1AC8-431E-AF33-9AD5F12631D1}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7834,7 +7834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D186C2B-91D9-4D17-9D6D-2E01A00F0DC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BCA6FF-C15C-4D0B-BCEF-68B9E3899070}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14736,7 +14736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59145DE1-FF7D-4905-B298-2E1D9086176D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D518A5-CD1D-4E69-A410-144D5B317A76}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8ADEE71-DE88-41B3-BF21-0CA19B0D086C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A852FD-C322-497A-975B-83EC6D939064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="627">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -3548,7 +3548,9 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
@@ -3584,7 +3586,9 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
@@ -6866,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85F9C99-1AC8-431E-AF33-9AD5F12631D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB8BC63-2AF8-49CD-8497-3720EC1DC224}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7834,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BCA6FF-C15C-4D0B-BCEF-68B9E3899070}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F873EBB2-581A-4E7A-ADD2-0E2E9693D571}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14736,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D518A5-CD1D-4E69-A410-144D5B317A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D18FE2-B9FA-4B08-82A0-BB839B987C5D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A852FD-C322-497A-975B-83EC6D939064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB9CE892-D6CB-45D5-B4C3-F794E4783D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6870,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB8BC63-2AF8-49CD-8497-3720EC1DC224}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BCDA2C-378A-497F-8655-1D6780CFEC81}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7838,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F873EBB2-581A-4E7A-ADD2-0E2E9693D571}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA2FCBD-F06F-4F04-A280-D369F617192A}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14740,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D18FE2-B9FA-4B08-82A0-BB839B987C5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407D55C7-B3C4-4B35-8446-9C46A3D6AAB9}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB9CE892-D6CB-45D5-B4C3-F794E4783D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16CE2550-A8D8-4C0C-A780-81C081B7B31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6870,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BCDA2C-378A-497F-8655-1D6780CFEC81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F601B599-0212-43B5-9463-6CB7FCC927A3}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7838,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA2FCBD-F06F-4F04-A280-D369F617192A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CFCEF70-2C7A-4BCF-A551-EAE833894953}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14740,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407D55C7-B3C4-4B35-8446-9C46A3D6AAB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C2FE76-4228-43BC-B24E-449586C0E33E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16CE2550-A8D8-4C0C-A780-81C081B7B31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{995A8853-7C57-45D4-95FB-B64DB31A34A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6870,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F601B599-0212-43B5-9463-6CB7FCC927A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABA850B-2276-49A3-99C2-C36210D13E31}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7838,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CFCEF70-2C7A-4BCF-A551-EAE833894953}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67B224F-19F9-4706-91FB-3E51117914DA}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14740,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C2FE76-4228-43BC-B24E-449586C0E33E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{073D65B1-BBDD-455E-8C64-6070E3D8E00E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{995A8853-7C57-45D4-95FB-B64DB31A34A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C10F4E5-FF03-4D81-A118-0248B478FA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6870,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABA850B-2276-49A3-99C2-C36210D13E31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A30E62-FFC4-488D-A311-12D5AB0AC9D3}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7838,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67B224F-19F9-4706-91FB-3E51117914DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C81906-CB01-4C85-B6EE-263BBC4A3D38}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14740,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{073D65B1-BBDD-455E-8C64-6070E3D8E00E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03772941-7DA5-47C5-B97F-8179BF68A682}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C10F4E5-FF03-4D81-A118-0248B478FA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3904CD-D950-4894-9E3B-335DC105E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6870,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A30E62-FFC4-488D-A311-12D5AB0AC9D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809C680D-4511-49FB-B80C-6ADB2FD0EEF6}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7838,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C81906-CB01-4C85-B6EE-263BBC4A3D38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F51E90F-FB2E-495E-A3BA-539416544EBB}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14740,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03772941-7DA5-47C5-B97F-8179BF68A682}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A435E7-6347-4C93-9199-4E6E00D412CB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3904CD-D950-4894-9E3B-335DC105E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FBC971A-D795-4D94-ACC6-AA55A4DCF589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6870,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809C680D-4511-49FB-B80C-6ADB2FD0EEF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E929A3-A83E-4753-8254-B5CFA66A6C41}">
   <dimension ref="B9:N34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7838,7 +7838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F51E90F-FB2E-495E-A3BA-539416544EBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BBCA2A3-316F-4A43-ACEF-60E25E43FE9D}">
   <dimension ref="B9:AB154"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14740,7 +14740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A435E7-6347-4C93-9199-4E6E00D412CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C288B21D-C07A-4141-BCFE-FD737B71EE8E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF7401F4-9793-4586-A737-D6D3536CCA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB179735-E1DB-4149-A875-481421EAAD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
-    <sheet name="hydro" sheetId="6" r:id="rId2"/>
-    <sheet name="ELC_Storage" sheetId="9" r:id="rId3"/>
-    <sheet name="EV Battery" sheetId="10" r:id="rId4"/>
-    <sheet name="H2 prod" sheetId="11" r:id="rId5"/>
-    <sheet name="solar" sheetId="12" r:id="rId6"/>
-    <sheet name="wind" sheetId="13" r:id="rId7"/>
-    <sheet name="conventional" sheetId="14" r:id="rId8"/>
+    <sheet name="ELC_Storage" sheetId="9" r:id="rId2"/>
+    <sheet name="EV Battery" sheetId="10" r:id="rId3"/>
+    <sheet name="H2 prod" sheetId="11" r:id="rId4"/>
+    <sheet name="solar" sheetId="12" r:id="rId5"/>
+    <sheet name="wind" sheetId="13" r:id="rId6"/>
+    <sheet name="conventional" sheetId="14" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="368">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -622,205 +621,175 @@
     <t>~fi_process</t>
   </si>
   <si>
+    <t>set</t>
+  </si>
+  <si>
     <t>process</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
+    <t>capacity_unit</t>
+  </si>
+  <si>
+    <t>activity_unit</t>
+  </si>
+  <si>
     <t>timeslicelevel</t>
   </si>
   <si>
-    <t>EN_Hydro_DEU-1</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - Germany - Step 1</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>EN_Hydro_DEU-2</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - Germany - Step 2</t>
-  </si>
-  <si>
-    <t>EN_Hydro_DEU-3</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - Germany - Step 3</t>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>ele</t>
+  </si>
+  <si>
+    <t>e_spv_001</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 1</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>e_spv_002</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 2</t>
+  </si>
+  <si>
+    <t>e_spv_003</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 3</t>
+  </si>
+  <si>
+    <t>e_spv_004</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 4</t>
+  </si>
+  <si>
+    <t>e_spv_005</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 5</t>
+  </si>
+  <si>
+    <t>e_spv_006</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 6</t>
+  </si>
+  <si>
+    <t>e_spv_007</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 7</t>
+  </si>
+  <si>
+    <t>e_spv_008</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 8</t>
+  </si>
+  <si>
+    <t>e_spv_009</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 9</t>
+  </si>
+  <si>
+    <t>e_spv_010</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 10</t>
+  </si>
+  <si>
+    <t>e_spv_011</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 11</t>
+  </si>
+  <si>
+    <t>e_spv_012</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 12</t>
+  </si>
+  <si>
+    <t>e_spv_013</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 13</t>
+  </si>
+  <si>
+    <t>e_spv_014</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 14</t>
+  </si>
+  <si>
+    <t>e_spv_015</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 15</t>
+  </si>
+  <si>
+    <t>e_spv_016</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 16</t>
+  </si>
+  <si>
+    <t>e_spv_017</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 17</t>
+  </si>
+  <si>
+    <t>e_spv_018</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 18</t>
+  </si>
+  <si>
+    <t>e_spv_019</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 19</t>
+  </si>
+  <si>
+    <t>e_spv_020</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 20</t>
+  </si>
+  <si>
+    <t>e_spv_021</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 21</t>
+  </si>
+  <si>
+    <t>e_spv_022</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 22</t>
+  </si>
+  <si>
+    <t>e_spv_023</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 23</t>
   </si>
   <si>
     <t>~fi_t</t>
-  </si>
-  <si>
-    <t>CAP_BND</t>
-  </si>
-  <si>
-    <t>INVCOST~USD21_alt</t>
-  </si>
-  <si>
-    <t>AF~FX</t>
-  </si>
-  <si>
-    <t>set</t>
-  </si>
-  <si>
-    <t>capacity_unit</t>
-  </si>
-  <si>
-    <t>activity_unit</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>ele</t>
-  </si>
-  <si>
-    <t>e_spv_001</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 1</t>
-  </si>
-  <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>e_spv_002</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 2</t>
-  </si>
-  <si>
-    <t>e_spv_003</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 3</t>
-  </si>
-  <si>
-    <t>e_spv_004</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 4</t>
-  </si>
-  <si>
-    <t>e_spv_005</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 5</t>
-  </si>
-  <si>
-    <t>e_spv_006</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 6</t>
-  </si>
-  <si>
-    <t>e_spv_007</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 7</t>
-  </si>
-  <si>
-    <t>e_spv_008</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 8</t>
-  </si>
-  <si>
-    <t>e_spv_009</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 9</t>
-  </si>
-  <si>
-    <t>e_spv_010</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 10</t>
-  </si>
-  <si>
-    <t>e_spv_011</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 11</t>
-  </si>
-  <si>
-    <t>e_spv_012</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 12</t>
-  </si>
-  <si>
-    <t>e_spv_013</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 13</t>
-  </si>
-  <si>
-    <t>e_spv_014</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 14</t>
-  </si>
-  <si>
-    <t>e_spv_015</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 15</t>
-  </si>
-  <si>
-    <t>e_spv_016</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 16</t>
-  </si>
-  <si>
-    <t>e_spv_017</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 17</t>
-  </si>
-  <si>
-    <t>e_spv_018</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 18</t>
-  </si>
-  <si>
-    <t>e_spv_019</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 19</t>
-  </si>
-  <si>
-    <t>e_spv_020</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 20</t>
-  </si>
-  <si>
-    <t>e_spv_021</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 21</t>
-  </si>
-  <si>
-    <t>e_spv_022</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 22</t>
-  </si>
-  <si>
-    <t>e_spv_023</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 23</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -3178,158 +3147,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5417F31-D792-47CD-82F2-E942FCB1F74A}">
-  <dimension ref="B9:N13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:14">
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="I10" t="s">
-        <v>164</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>175</v>
-      </c>
-      <c r="M10" t="s">
-        <v>176</v>
-      </c>
-      <c r="N10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11">
-        <v>1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13">
-        <v>4.45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD6D8AA-F8A9-4BBE-94C7-C767CA3BCC03}">
   <dimension ref="B2:W61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
@@ -4565,7 +4382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12EA90E-43F0-4F26-A089-D51219939B11}">
   <dimension ref="B3:Y8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -4836,7 +4653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A64BB3-8019-4461-A511-24783E2ADCDE}">
   <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -6122,8 +5939,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1093034E-1B56-4A97-A5B0-19E5C8650769}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D78C946-2547-4B68-A212-E89548D88D34}">
   <dimension ref="B9:M33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6132,53 +5949,53 @@
         <v>163</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" t="s">
         <v>165</v>
       </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>164</v>
-      </c>
       <c r="K10" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="L10" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="M10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6187,16 +6004,16 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="L11">
         <v>13.938003670888978</v>
@@ -6207,13 +6024,13 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6222,16 +6039,16 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K12" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="L12">
         <v>18.31863654586293</v>
@@ -6242,13 +6059,13 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6257,16 +6074,16 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H13" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="K13" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="L13">
         <v>30.238043484360141</v>
@@ -6277,13 +6094,13 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D14" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6292,16 +6109,16 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="K14" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="L14">
         <v>45.351574205977535</v>
@@ -6312,13 +6129,13 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
         <v>182</v>
       </c>
-      <c r="C15" t="s">
-        <v>193</v>
-      </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6327,16 +6144,16 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="K15" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="L15">
         <v>34.531914591504368</v>
@@ -6347,13 +6164,13 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6362,16 +6179,16 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="K16" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L16">
         <v>38.190379780391297</v>
@@ -6382,13 +6199,13 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6397,16 +6214,16 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" t="s">
         <v>186</v>
       </c>
-      <c r="J17" t="s">
-        <v>197</v>
-      </c>
       <c r="K17" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L17">
         <v>13.44361680351453</v>
@@ -6417,13 +6234,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6432,16 +6249,16 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H18" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="K18" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="L18">
         <v>15.833691242733796</v>
@@ -6452,13 +6269,13 @@
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6467,16 +6284,16 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="K19" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="L19">
         <v>11.346394535605524</v>
@@ -6487,13 +6304,13 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6502,16 +6319,16 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H20" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="K20" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L20">
         <v>32.21637396151899</v>
@@ -6522,13 +6339,13 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6537,16 +6354,16 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="K21" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="L21">
         <v>30.007867954603132</v>
@@ -6557,13 +6374,13 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -6572,33 +6389,33 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H22" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="K22" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="L22">
-        <v>15.545485308406519</v>
+        <v>38.24309918267349</v>
       </c>
       <c r="M22">
-        <v>0.13249412957220019</v>
+        <v>0.13439514464711891</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -6607,33 +6424,33 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H23" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="K23" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="L23">
-        <v>22.697613874266967</v>
+        <v>0.95743993217852441</v>
       </c>
       <c r="M23">
-        <v>0.1356971406226391</v>
+        <v>0.1497995747391499</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -6642,33 +6459,33 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="K24" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L24">
-        <v>0.95743993217852441</v>
+        <v>15.746380528104394</v>
       </c>
       <c r="M24">
-        <v>0.1497995747391499</v>
+        <v>0.1361753774721691</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -6677,33 +6494,33 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H25" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="K25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="L25">
-        <v>15.746380528104394</v>
+        <v>32.685256480874017</v>
       </c>
       <c r="M25">
-        <v>0.1361753774721691</v>
+        <v>0.13680478137029231</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -6712,33 +6529,33 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="K26" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="L26">
-        <v>32.685256480874017</v>
+        <v>13.348518217290337</v>
       </c>
       <c r="M26">
-        <v>0.13680478137029231</v>
+        <v>0.14595055475480129</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -6747,33 +6564,33 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H27" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K27" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="L27">
-        <v>13.348518217290337</v>
+        <v>19.75277137741244</v>
       </c>
       <c r="M27">
-        <v>0.14595055475480129</v>
+        <v>0.13638324455665041</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -6782,33 +6599,33 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="K28" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L28">
-        <v>19.75277137741244</v>
+        <v>23.3954191787236</v>
       </c>
       <c r="M28">
-        <v>0.13638324455665041</v>
+        <v>0.14124198799860169</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D29" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -6817,33 +6634,33 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H29" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K29" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="L29">
-        <v>23.3954191787236</v>
+        <v>20.01197763203729</v>
       </c>
       <c r="M29">
-        <v>0.14124198799860169</v>
+        <v>0.13366475380241499</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D30" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -6852,33 +6669,33 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="K30" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="L30">
-        <v>23.28078369016097</v>
+        <v>23.591873553963495</v>
       </c>
       <c r="M30">
-        <v>0.1336296330519684</v>
+        <v>0.13360401365368399</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -6887,33 +6704,33 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H31" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J31" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="K31" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L31">
-        <v>25.352521767431195</v>
+        <v>21.653826323424543</v>
       </c>
       <c r="M31">
-        <v>0.13287551119482599</v>
+        <v>0.1321576257262759</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D32" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -6922,33 +6739,33 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H32" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J32" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="K32" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L32">
-        <v>21.007370293639131</v>
+        <v>12.637613221312568</v>
       </c>
       <c r="M32">
-        <v>0.1339595723409856</v>
+        <v>0.13378598692581661</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -6957,22 +6774,1214 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H33" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="K33" t="s">
+        <v>246</v>
+      </c>
+      <c r="L33">
+        <v>23.28078369016097</v>
+      </c>
+      <c r="M33">
+        <v>0.1336296330519684</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F878B0-9BDE-46EE-A189-F5E3722AEB38}">
+  <dimension ref="B9:Z32"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="9" spans="2:26">
+      <c r="B9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J9" t="s">
+        <v>220</v>
+      </c>
+      <c r="O9" t="s">
+        <v>163</v>
+      </c>
+      <c r="W9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26">
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" t="s">
+        <v>165</v>
+      </c>
+      <c r="K10" t="s">
+        <v>221</v>
+      </c>
+      <c r="L10" t="s">
+        <v>222</v>
+      </c>
+      <c r="M10" t="s">
+        <v>223</v>
+      </c>
+      <c r="O10" t="s">
+        <v>164</v>
+      </c>
+      <c r="P10" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>166</v>
+      </c>
+      <c r="R10" t="s">
+        <v>167</v>
+      </c>
+      <c r="S10" t="s">
+        <v>168</v>
+      </c>
+      <c r="T10" t="s">
+        <v>169</v>
+      </c>
+      <c r="U10" t="s">
+        <v>170</v>
+      </c>
+      <c r="W10" t="s">
+        <v>165</v>
+      </c>
+      <c r="X10" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26">
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
+        <v>247</v>
+      </c>
+      <c r="K11" t="s">
+        <v>291</v>
+      </c>
+      <c r="L11">
+        <v>79.362778177778793</v>
+      </c>
+      <c r="M11">
+        <v>0.32113557799809911</v>
+      </c>
+      <c r="O11" t="s">
+        <v>171</v>
+      </c>
+      <c r="P11" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>314</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>174</v>
+      </c>
+      <c r="U11" t="s">
+        <v>175</v>
+      </c>
+      <c r="W11" t="s">
+        <v>313</v>
+      </c>
+      <c r="X11" t="s">
+        <v>333</v>
+      </c>
+      <c r="Y11">
+        <v>108.8275</v>
+      </c>
+      <c r="Z11">
+        <v>0.5723991316469299</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="B12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J12" t="s">
+        <v>249</v>
+      </c>
+      <c r="K12" t="s">
+        <v>292</v>
+      </c>
+      <c r="L12">
+        <v>50.354564381123943</v>
+      </c>
+      <c r="M12">
+        <v>0.26229547814325971</v>
+      </c>
+      <c r="O12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>316</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>174</v>
+      </c>
+      <c r="U12" t="s">
+        <v>175</v>
+      </c>
+      <c r="W12" t="s">
+        <v>315</v>
+      </c>
+      <c r="X12" t="s">
+        <v>334</v>
+      </c>
+      <c r="Y12">
+        <v>54.292499999999997</v>
+      </c>
+      <c r="Z12">
+        <v>0.54240024081939597</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26">
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" t="s">
+        <v>251</v>
+      </c>
+      <c r="K13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L13">
+        <v>57.005439523831519</v>
+      </c>
+      <c r="M13">
+        <v>0.27008680004560909</v>
+      </c>
+      <c r="O13" t="s">
+        <v>171</v>
+      </c>
+      <c r="P13" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>318</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>174</v>
+      </c>
+      <c r="U13" t="s">
+        <v>175</v>
+      </c>
+      <c r="W13" t="s">
+        <v>317</v>
+      </c>
+      <c r="X13" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y13">
+        <v>50.356250000000003</v>
+      </c>
+      <c r="Z13">
+        <v>0.53901340841870993</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" t="s">
+        <v>175</v>
+      </c>
+      <c r="J14" t="s">
+        <v>253</v>
+      </c>
+      <c r="K14" t="s">
+        <v>294</v>
+      </c>
+      <c r="L14">
+        <v>19.895723562817633</v>
+      </c>
+      <c r="M14">
+        <v>0.41998320074620132</v>
+      </c>
+      <c r="O14" t="s">
+        <v>171</v>
+      </c>
+      <c r="P14" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>320</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>174</v>
+      </c>
+      <c r="U14" t="s">
+        <v>175</v>
+      </c>
+      <c r="W14" t="s">
+        <v>319</v>
+      </c>
+      <c r="X14" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y14">
+        <v>9.5987500000000008</v>
+      </c>
+      <c r="Z14">
+        <v>0.44411317641629539</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26">
+      <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D15" t="s">
         <v>256</v>
       </c>
-      <c r="L33">
-        <v>31.535398669667572</v>
-      </c>
-      <c r="M33">
-        <v>0.13307113397189341</v>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" t="s">
+        <v>255</v>
+      </c>
+      <c r="K15" t="s">
+        <v>295</v>
+      </c>
+      <c r="L15">
+        <v>9.5699994650614961</v>
+      </c>
+      <c r="M15">
+        <v>0.44653362265814228</v>
+      </c>
+      <c r="O15" t="s">
+        <v>171</v>
+      </c>
+      <c r="P15" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>322</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>174</v>
+      </c>
+      <c r="U15" t="s">
+        <v>175</v>
+      </c>
+      <c r="W15" t="s">
+        <v>321</v>
+      </c>
+      <c r="X15" t="s">
+        <v>337</v>
+      </c>
+      <c r="Y15">
+        <v>50.66</v>
+      </c>
+      <c r="Z15">
+        <v>0.47592028835921918</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" t="s">
+        <v>257</v>
+      </c>
+      <c r="D16" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" t="s">
+        <v>296</v>
+      </c>
+      <c r="L16">
+        <v>44.760252416795389</v>
+      </c>
+      <c r="M16">
+        <v>0.42821243398456738</v>
+      </c>
+      <c r="O16" t="s">
+        <v>171</v>
+      </c>
+      <c r="P16" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>324</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>174</v>
+      </c>
+      <c r="U16" t="s">
+        <v>175</v>
+      </c>
+      <c r="W16" t="s">
+        <v>323</v>
+      </c>
+      <c r="X16" t="s">
+        <v>338</v>
+      </c>
+      <c r="Y16">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Z16">
+        <v>0.25312783580877751</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26">
+      <c r="B17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" t="s">
+        <v>259</v>
+      </c>
+      <c r="K17" t="s">
+        <v>297</v>
+      </c>
+      <c r="L17">
+        <v>40.59880776523103</v>
+      </c>
+      <c r="M17">
+        <v>0.34199104865897728</v>
+      </c>
+      <c r="O17" t="s">
+        <v>171</v>
+      </c>
+      <c r="P17" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>326</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>174</v>
+      </c>
+      <c r="U17" t="s">
+        <v>175</v>
+      </c>
+      <c r="W17" t="s">
+        <v>325</v>
+      </c>
+      <c r="X17" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y17">
+        <v>0.92625000000000002</v>
+      </c>
+      <c r="Z17">
+        <v>0.28470851865910418</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26">
+      <c r="B18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" t="s">
+        <v>175</v>
+      </c>
+      <c r="J18" t="s">
+        <v>261</v>
+      </c>
+      <c r="K18" t="s">
+        <v>298</v>
+      </c>
+      <c r="L18">
+        <v>71.045385513132985</v>
+      </c>
+      <c r="M18">
+        <v>0.30696999602332747</v>
+      </c>
+      <c r="O18" t="s">
+        <v>171</v>
+      </c>
+      <c r="P18" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>328</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>174</v>
+      </c>
+      <c r="U18" t="s">
+        <v>175</v>
+      </c>
+      <c r="W18" t="s">
+        <v>327</v>
+      </c>
+      <c r="X18" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y18">
+        <v>7.5287499999999996</v>
+      </c>
+      <c r="Z18">
+        <v>0.38304656398167958</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26">
+      <c r="B19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" t="s">
+        <v>263</v>
+      </c>
+      <c r="K19" t="s">
+        <v>299</v>
+      </c>
+      <c r="L19">
+        <v>63.055598832310729</v>
+      </c>
+      <c r="M19">
+        <v>0.3285833519844587</v>
+      </c>
+      <c r="O19" t="s">
+        <v>171</v>
+      </c>
+      <c r="P19" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>330</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>174</v>
+      </c>
+      <c r="U19" t="s">
+        <v>175</v>
+      </c>
+      <c r="W19" t="s">
+        <v>329</v>
+      </c>
+      <c r="X19" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y19">
+        <v>14.6</v>
+      </c>
+      <c r="Z19">
+        <v>0.39107677526530671</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26">
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" t="s">
+        <v>265</v>
+      </c>
+      <c r="K20" t="s">
+        <v>300</v>
+      </c>
+      <c r="L20">
+        <v>43.89469200396065</v>
+      </c>
+      <c r="M20">
+        <v>0.2838221752225063</v>
+      </c>
+      <c r="O20" t="s">
+        <v>171</v>
+      </c>
+      <c r="P20" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>332</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>174</v>
+      </c>
+      <c r="U20" t="s">
+        <v>175</v>
+      </c>
+      <c r="W20" t="s">
+        <v>331</v>
+      </c>
+      <c r="X20" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y20">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="Z20">
+        <v>0.2928857430245369</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26">
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" t="s">
+        <v>268</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" t="s">
+        <v>267</v>
+      </c>
+      <c r="K21" t="s">
+        <v>301</v>
+      </c>
+      <c r="L21">
+        <v>11.547936358898198</v>
+      </c>
+      <c r="M21">
+        <v>0.11506291599579389</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26">
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" t="s">
+        <v>269</v>
+      </c>
+      <c r="K22" t="s">
+        <v>302</v>
+      </c>
+      <c r="L22">
+        <v>31.481356456094364</v>
+      </c>
+      <c r="M22">
+        <v>0.2069371408679247</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26">
+      <c r="B23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D23" t="s">
+        <v>272</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" t="s">
+        <v>271</v>
+      </c>
+      <c r="K23" t="s">
+        <v>303</v>
+      </c>
+      <c r="L23">
+        <v>15.708789779919334</v>
+      </c>
+      <c r="M23">
+        <v>0.17539476044040481</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26">
+      <c r="B24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>174</v>
+      </c>
+      <c r="H24" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K24" t="s">
+        <v>304</v>
+      </c>
+      <c r="L24">
+        <v>20.814752751471318</v>
+      </c>
+      <c r="M24">
+        <v>0.15125980855062521</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26">
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" t="s">
+        <v>275</v>
+      </c>
+      <c r="K25" t="s">
+        <v>305</v>
+      </c>
+      <c r="L25">
+        <v>50.266717026070005</v>
+      </c>
+      <c r="M25">
+        <v>0.24965463444905531</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26">
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D26" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" t="s">
+        <v>277</v>
+      </c>
+      <c r="K26" t="s">
+        <v>306</v>
+      </c>
+      <c r="L26">
+        <v>56.728889145623882</v>
+      </c>
+      <c r="M26">
+        <v>0.22062927657380671</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26">
+      <c r="B27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" t="s">
+        <v>279</v>
+      </c>
+      <c r="K27" t="s">
+        <v>307</v>
+      </c>
+      <c r="L27">
+        <v>70.602917671125681</v>
+      </c>
+      <c r="M27">
+        <v>0.25064149863403667</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26">
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" t="s">
+        <v>282</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" t="s">
+        <v>281</v>
+      </c>
+      <c r="K28" t="s">
+        <v>308</v>
+      </c>
+      <c r="L28">
+        <v>7.8153674765988201</v>
+      </c>
+      <c r="M28">
+        <v>0.172594117441394</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26">
+      <c r="B29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>174</v>
+      </c>
+      <c r="H29" t="s">
+        <v>175</v>
+      </c>
+      <c r="J29" t="s">
+        <v>283</v>
+      </c>
+      <c r="K29" t="s">
+        <v>309</v>
+      </c>
+      <c r="L29">
+        <v>26.861604762024118</v>
+      </c>
+      <c r="M29">
+        <v>0.19566496141896261</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26">
+      <c r="B30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" t="s">
+        <v>285</v>
+      </c>
+      <c r="K30" t="s">
+        <v>310</v>
+      </c>
+      <c r="L30">
+        <v>10.889866530825216</v>
+      </c>
+      <c r="M30">
+        <v>8.9766767511609002E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26">
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
+        <v>287</v>
+      </c>
+      <c r="D31" t="s">
+        <v>288</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" t="s">
+        <v>287</v>
+      </c>
+      <c r="K31" t="s">
+        <v>311</v>
+      </c>
+      <c r="L31">
+        <v>9.0084683548455349</v>
+      </c>
+      <c r="M31">
+        <v>0.1774711327814161</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26">
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="s">
+        <v>289</v>
+      </c>
+      <c r="D32" t="s">
+        <v>290</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" t="s">
+        <v>289</v>
+      </c>
+      <c r="K32" t="s">
+        <v>312</v>
+      </c>
+      <c r="L32">
+        <v>35.009005865752776</v>
+      </c>
+      <c r="M32">
+        <v>0.1603815287130477</v>
       </c>
     </row>
   </sheetData>
@@ -6981,1205 +7990,13 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B66B24A-BD61-445B-BD8C-5F6B2178E6FB}">
-  <dimension ref="B9:Z32"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:26">
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J9" t="s">
-        <v>174</v>
-      </c>
-      <c r="O9" t="s">
-        <v>163</v>
-      </c>
-      <c r="W9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:26">
-      <c r="B10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K10" t="s">
-        <v>231</v>
-      </c>
-      <c r="L10" t="s">
-        <v>232</v>
-      </c>
-      <c r="M10" t="s">
-        <v>233</v>
-      </c>
-      <c r="O10" t="s">
-        <v>178</v>
-      </c>
-      <c r="P10" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>165</v>
-      </c>
-      <c r="R10" t="s">
-        <v>179</v>
-      </c>
-      <c r="S10" t="s">
-        <v>180</v>
-      </c>
-      <c r="T10" t="s">
-        <v>166</v>
-      </c>
-      <c r="U10" t="s">
-        <v>181</v>
-      </c>
-      <c r="W10" t="s">
-        <v>164</v>
-      </c>
-      <c r="X10" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="11" spans="2:26">
-      <c r="B11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D11" t="s">
-        <v>258</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H11" t="s">
-        <v>186</v>
-      </c>
-      <c r="J11" t="s">
-        <v>257</v>
-      </c>
-      <c r="K11" t="s">
-        <v>301</v>
-      </c>
-      <c r="L11">
-        <v>79.362778177778793</v>
-      </c>
-      <c r="M11">
-        <v>0.32113557799809911</v>
-      </c>
-      <c r="O11" t="s">
-        <v>182</v>
-      </c>
-      <c r="P11" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>324</v>
-      </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T11" t="s">
-        <v>185</v>
-      </c>
-      <c r="U11" t="s">
-        <v>186</v>
-      </c>
-      <c r="W11" t="s">
-        <v>323</v>
-      </c>
-      <c r="X11" t="s">
-        <v>343</v>
-      </c>
-      <c r="Y11">
-        <v>108.8275</v>
-      </c>
-      <c r="Z11">
-        <v>0.5723991316469299</v>
-      </c>
-    </row>
-    <row r="12" spans="2:26">
-      <c r="B12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" t="s">
-        <v>186</v>
-      </c>
-      <c r="J12" t="s">
-        <v>259</v>
-      </c>
-      <c r="K12" t="s">
-        <v>302</v>
-      </c>
-      <c r="L12">
-        <v>50.354564381123943</v>
-      </c>
-      <c r="M12">
-        <v>0.26229547814325971</v>
-      </c>
-      <c r="O12" t="s">
-        <v>182</v>
-      </c>
-      <c r="P12" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>326</v>
-      </c>
-      <c r="R12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s">
-        <v>185</v>
-      </c>
-      <c r="U12" t="s">
-        <v>186</v>
-      </c>
-      <c r="W12" t="s">
-        <v>325</v>
-      </c>
-      <c r="X12" t="s">
-        <v>344</v>
-      </c>
-      <c r="Y12">
-        <v>54.292499999999997</v>
-      </c>
-      <c r="Z12">
-        <v>0.54240024081939597</v>
-      </c>
-    </row>
-    <row r="13" spans="2:26">
-      <c r="B13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" t="s">
-        <v>261</v>
-      </c>
-      <c r="K13" t="s">
-        <v>303</v>
-      </c>
-      <c r="L13">
-        <v>57.005439523831519</v>
-      </c>
-      <c r="M13">
-        <v>0.27008680004560909</v>
-      </c>
-      <c r="O13" t="s">
-        <v>182</v>
-      </c>
-      <c r="P13" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>328</v>
-      </c>
-      <c r="R13" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s">
-        <v>185</v>
-      </c>
-      <c r="U13" t="s">
-        <v>186</v>
-      </c>
-      <c r="W13" t="s">
-        <v>327</v>
-      </c>
-      <c r="X13" t="s">
-        <v>345</v>
-      </c>
-      <c r="Y13">
-        <v>50.356250000000003</v>
-      </c>
-      <c r="Z13">
-        <v>0.53901340841870993</v>
-      </c>
-    </row>
-    <row r="14" spans="2:26">
-      <c r="B14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" t="s">
-        <v>263</v>
-      </c>
-      <c r="D14" t="s">
-        <v>264</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H14" t="s">
-        <v>186</v>
-      </c>
-      <c r="J14" t="s">
-        <v>263</v>
-      </c>
-      <c r="K14" t="s">
-        <v>304</v>
-      </c>
-      <c r="L14">
-        <v>19.895723562817633</v>
-      </c>
-      <c r="M14">
-        <v>0.41998320074620132</v>
-      </c>
-      <c r="O14" t="s">
-        <v>182</v>
-      </c>
-      <c r="P14" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>330</v>
-      </c>
-      <c r="R14" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U14" t="s">
-        <v>186</v>
-      </c>
-      <c r="W14" t="s">
-        <v>329</v>
-      </c>
-      <c r="X14" t="s">
-        <v>346</v>
-      </c>
-      <c r="Y14">
-        <v>9.5987500000000008</v>
-      </c>
-      <c r="Z14">
-        <v>0.44411317641629539</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26">
-      <c r="B15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>185</v>
-      </c>
-      <c r="H15" t="s">
-        <v>186</v>
-      </c>
-      <c r="J15" t="s">
-        <v>265</v>
-      </c>
-      <c r="K15" t="s">
-        <v>305</v>
-      </c>
-      <c r="L15">
-        <v>9.5699994650614961</v>
-      </c>
-      <c r="M15">
-        <v>0.44653362265814228</v>
-      </c>
-      <c r="O15" t="s">
-        <v>182</v>
-      </c>
-      <c r="P15" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>332</v>
-      </c>
-      <c r="R15" t="s">
-        <v>10</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>185</v>
-      </c>
-      <c r="U15" t="s">
-        <v>186</v>
-      </c>
-      <c r="W15" t="s">
-        <v>331</v>
-      </c>
-      <c r="X15" t="s">
-        <v>347</v>
-      </c>
-      <c r="Y15">
-        <v>50.66</v>
-      </c>
-      <c r="Z15">
-        <v>0.47592028835921918</v>
-      </c>
-    </row>
-    <row r="16" spans="2:26">
-      <c r="B16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" t="s">
-        <v>267</v>
-      </c>
-      <c r="D16" t="s">
-        <v>268</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>185</v>
-      </c>
-      <c r="H16" t="s">
-        <v>186</v>
-      </c>
-      <c r="J16" t="s">
-        <v>267</v>
-      </c>
-      <c r="K16" t="s">
-        <v>306</v>
-      </c>
-      <c r="L16">
-        <v>44.760252416795389</v>
-      </c>
-      <c r="M16">
-        <v>0.42821243398456738</v>
-      </c>
-      <c r="O16" t="s">
-        <v>182</v>
-      </c>
-      <c r="P16" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>334</v>
-      </c>
-      <c r="R16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>185</v>
-      </c>
-      <c r="U16" t="s">
-        <v>186</v>
-      </c>
-      <c r="W16" t="s">
-        <v>333</v>
-      </c>
-      <c r="X16" t="s">
-        <v>348</v>
-      </c>
-      <c r="Y16">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Z16">
-        <v>0.25312783580877751</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26">
-      <c r="B17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>269</v>
-      </c>
-      <c r="D17" t="s">
-        <v>270</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>185</v>
-      </c>
-      <c r="H17" t="s">
-        <v>186</v>
-      </c>
-      <c r="J17" t="s">
-        <v>269</v>
-      </c>
-      <c r="K17" t="s">
-        <v>307</v>
-      </c>
-      <c r="L17">
-        <v>40.59880776523103</v>
-      </c>
-      <c r="M17">
-        <v>0.34199104865897728</v>
-      </c>
-      <c r="O17" t="s">
-        <v>182</v>
-      </c>
-      <c r="P17" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>336</v>
-      </c>
-      <c r="R17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>185</v>
-      </c>
-      <c r="U17" t="s">
-        <v>186</v>
-      </c>
-      <c r="W17" t="s">
-        <v>335</v>
-      </c>
-      <c r="X17" t="s">
-        <v>349</v>
-      </c>
-      <c r="Y17">
-        <v>0.92625000000000002</v>
-      </c>
-      <c r="Z17">
-        <v>0.28470851865910418</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26">
-      <c r="B18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" t="s">
-        <v>271</v>
-      </c>
-      <c r="D18" t="s">
-        <v>272</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" t="s">
-        <v>186</v>
-      </c>
-      <c r="J18" t="s">
-        <v>271</v>
-      </c>
-      <c r="K18" t="s">
-        <v>308</v>
-      </c>
-      <c r="L18">
-        <v>71.045385513132985</v>
-      </c>
-      <c r="M18">
-        <v>0.30696999602332747</v>
-      </c>
-      <c r="O18" t="s">
-        <v>182</v>
-      </c>
-      <c r="P18" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>338</v>
-      </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>185</v>
-      </c>
-      <c r="U18" t="s">
-        <v>186</v>
-      </c>
-      <c r="W18" t="s">
-        <v>337</v>
-      </c>
-      <c r="X18" t="s">
-        <v>350</v>
-      </c>
-      <c r="Y18">
-        <v>7.5287499999999996</v>
-      </c>
-      <c r="Z18">
-        <v>0.38304656398167958</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26">
-      <c r="B19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" t="s">
-        <v>273</v>
-      </c>
-      <c r="D19" t="s">
-        <v>274</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>185</v>
-      </c>
-      <c r="H19" t="s">
-        <v>186</v>
-      </c>
-      <c r="J19" t="s">
-        <v>273</v>
-      </c>
-      <c r="K19" t="s">
-        <v>309</v>
-      </c>
-      <c r="L19">
-        <v>63.055598832310729</v>
-      </c>
-      <c r="M19">
-        <v>0.3285833519844587</v>
-      </c>
-      <c r="O19" t="s">
-        <v>182</v>
-      </c>
-      <c r="P19" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>340</v>
-      </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>185</v>
-      </c>
-      <c r="U19" t="s">
-        <v>186</v>
-      </c>
-      <c r="W19" t="s">
-        <v>339</v>
-      </c>
-      <c r="X19" t="s">
-        <v>351</v>
-      </c>
-      <c r="Y19">
-        <v>14.6</v>
-      </c>
-      <c r="Z19">
-        <v>0.39107677526530671</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26">
-      <c r="B20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" t="s">
-        <v>275</v>
-      </c>
-      <c r="D20" t="s">
-        <v>276</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" t="s">
-        <v>186</v>
-      </c>
-      <c r="J20" t="s">
-        <v>275</v>
-      </c>
-      <c r="K20" t="s">
-        <v>310</v>
-      </c>
-      <c r="L20">
-        <v>43.89469200396065</v>
-      </c>
-      <c r="M20">
-        <v>0.2838221752225063</v>
-      </c>
-      <c r="O20" t="s">
-        <v>182</v>
-      </c>
-      <c r="P20" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>342</v>
-      </c>
-      <c r="R20" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" t="s">
-        <v>21</v>
-      </c>
-      <c r="T20" t="s">
-        <v>185</v>
-      </c>
-      <c r="U20" t="s">
-        <v>186</v>
-      </c>
-      <c r="W20" t="s">
-        <v>341</v>
-      </c>
-      <c r="X20" t="s">
-        <v>352</v>
-      </c>
-      <c r="Y20">
-        <v>0.24374999999999999</v>
-      </c>
-      <c r="Z20">
-        <v>0.2928857430245369</v>
-      </c>
-    </row>
-    <row r="21" spans="2:26">
-      <c r="B21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" t="s">
-        <v>277</v>
-      </c>
-      <c r="D21" t="s">
-        <v>278</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" t="s">
-        <v>277</v>
-      </c>
-      <c r="K21" t="s">
-        <v>311</v>
-      </c>
-      <c r="L21">
-        <v>11.547936358898198</v>
-      </c>
-      <c r="M21">
-        <v>0.11506291599579389</v>
-      </c>
-    </row>
-    <row r="22" spans="2:26">
-      <c r="B22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" t="s">
-        <v>279</v>
-      </c>
-      <c r="D22" t="s">
-        <v>280</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" t="s">
-        <v>279</v>
-      </c>
-      <c r="K22" t="s">
-        <v>312</v>
-      </c>
-      <c r="L22">
-        <v>31.481356456094364</v>
-      </c>
-      <c r="M22">
-        <v>0.2069371408679247</v>
-      </c>
-    </row>
-    <row r="23" spans="2:26">
-      <c r="B23" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" t="s">
-        <v>281</v>
-      </c>
-      <c r="D23" t="s">
-        <v>282</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>185</v>
-      </c>
-      <c r="H23" t="s">
-        <v>186</v>
-      </c>
-      <c r="J23" t="s">
-        <v>281</v>
-      </c>
-      <c r="K23" t="s">
-        <v>313</v>
-      </c>
-      <c r="L23">
-        <v>15.708789779919334</v>
-      </c>
-      <c r="M23">
-        <v>0.17539476044040481</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26">
-      <c r="B24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C24" t="s">
-        <v>283</v>
-      </c>
-      <c r="D24" t="s">
-        <v>284</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>185</v>
-      </c>
-      <c r="H24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24" t="s">
-        <v>283</v>
-      </c>
-      <c r="K24" t="s">
-        <v>314</v>
-      </c>
-      <c r="L24">
-        <v>20.814752751471318</v>
-      </c>
-      <c r="M24">
-        <v>0.15125980855062521</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26">
-      <c r="B25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" t="s">
-        <v>285</v>
-      </c>
-      <c r="D25" t="s">
-        <v>286</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>185</v>
-      </c>
-      <c r="H25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" t="s">
-        <v>285</v>
-      </c>
-      <c r="K25" t="s">
-        <v>315</v>
-      </c>
-      <c r="L25">
-        <v>50.266717026070005</v>
-      </c>
-      <c r="M25">
-        <v>0.24965463444905531</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26">
-      <c r="B26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" t="s">
-        <v>287</v>
-      </c>
-      <c r="D26" t="s">
-        <v>288</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>185</v>
-      </c>
-      <c r="H26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J26" t="s">
-        <v>287</v>
-      </c>
-      <c r="K26" t="s">
-        <v>316</v>
-      </c>
-      <c r="L26">
-        <v>56.728889145623882</v>
-      </c>
-      <c r="M26">
-        <v>0.22062927657380671</v>
-      </c>
-    </row>
-    <row r="27" spans="2:26">
-      <c r="B27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" t="s">
-        <v>290</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>185</v>
-      </c>
-      <c r="H27" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" t="s">
-        <v>289</v>
-      </c>
-      <c r="K27" t="s">
-        <v>317</v>
-      </c>
-      <c r="L27">
-        <v>70.602917671125681</v>
-      </c>
-      <c r="M27">
-        <v>0.25064149863403667</v>
-      </c>
-    </row>
-    <row r="28" spans="2:26">
-      <c r="B28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" t="s">
-        <v>291</v>
-      </c>
-      <c r="D28" t="s">
-        <v>292</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" t="s">
-        <v>186</v>
-      </c>
-      <c r="J28" t="s">
-        <v>291</v>
-      </c>
-      <c r="K28" t="s">
-        <v>318</v>
-      </c>
-      <c r="L28">
-        <v>7.8153674765988201</v>
-      </c>
-      <c r="M28">
-        <v>0.172594117441394</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26">
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" t="s">
-        <v>293</v>
-      </c>
-      <c r="D29" t="s">
-        <v>294</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H29" t="s">
-        <v>186</v>
-      </c>
-      <c r="J29" t="s">
-        <v>293</v>
-      </c>
-      <c r="K29" t="s">
-        <v>319</v>
-      </c>
-      <c r="L29">
-        <v>26.861604762024118</v>
-      </c>
-      <c r="M29">
-        <v>0.19566496141896261</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26">
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" t="s">
-        <v>186</v>
-      </c>
-      <c r="J30" t="s">
-        <v>295</v>
-      </c>
-      <c r="K30" t="s">
-        <v>320</v>
-      </c>
-      <c r="L30">
-        <v>10.889866530825216</v>
-      </c>
-      <c r="M30">
-        <v>8.9766767511609002E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:26">
-      <c r="B31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" t="s">
-        <v>297</v>
-      </c>
-      <c r="D31" t="s">
-        <v>298</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" t="s">
-        <v>297</v>
-      </c>
-      <c r="K31" t="s">
-        <v>321</v>
-      </c>
-      <c r="L31">
-        <v>9.0084683548455349</v>
-      </c>
-      <c r="M31">
-        <v>0.1774711327814161</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26">
-      <c r="B32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" t="s">
-        <v>299</v>
-      </c>
-      <c r="D32" t="s">
-        <v>300</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>185</v>
-      </c>
-      <c r="H32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J32" t="s">
-        <v>299</v>
-      </c>
-      <c r="K32" t="s">
-        <v>322</v>
-      </c>
-      <c r="L32">
-        <v>35.009005865752776</v>
-      </c>
-      <c r="M32">
-        <v>0.1603815287130477</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BA0C58-0091-4431-9832-98088E7542D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0803C16-B7DF-4A4D-9F7D-9B177146B221}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="J9" t="s">
         <v>163</v>
@@ -8187,13 +8004,13 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -8208,30 +8025,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M10" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="N10" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="O10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -8252,10 +8069,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -8264,15 +8081,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P11" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -8290,13 +8107,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="J12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -8305,15 +8122,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P12" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -8331,13 +8148,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -8346,15 +8163,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P13" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -8372,13 +8189,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="J14" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K14" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -8387,15 +8204,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P14" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -8413,13 +8230,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -8428,15 +8245,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P15" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -8457,10 +8274,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K16" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -8469,15 +8286,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P16" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -8495,13 +8312,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="J17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -8510,15 +8327,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P17" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -8536,13 +8353,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="J18" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K18" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -8551,15 +8368,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P18" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -8577,13 +8394,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="J19" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K19" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -8592,15 +8409,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P19" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -8618,13 +8435,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="J20" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K20" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -8633,15 +8450,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P20" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -8662,10 +8479,10 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -8674,15 +8491,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P21" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -8700,13 +8517,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="J22" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -8715,15 +8532,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P22" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -8741,13 +8558,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="J23" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -8756,15 +8573,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P23" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -8785,10 +8602,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -8797,15 +8614,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P24" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -8823,13 +8640,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="J25" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -8838,15 +8655,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P25" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -8864,13 +8681,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="J26" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K26" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -8879,15 +8696,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P26" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -8908,10 +8725,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -8920,15 +8737,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P27" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -8946,12 +8763,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -8969,12 +8786,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -8997,7 +8814,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -9015,12 +8832,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -9038,12 +8855,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -9066,7 +8883,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -9084,12 +8901,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -9107,12 +8924,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -9130,12 +8947,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -9153,12 +8970,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -9181,7 +8998,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -9199,12 +9016,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -9222,12 +9039,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -9250,7 +9067,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -9268,12 +9085,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -9291,12 +9108,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -9319,7 +9136,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -9337,12 +9154,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -9360,12 +9177,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -9388,7 +9205,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -9406,12 +9223,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -9429,12 +9246,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -9457,7 +9274,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -9475,12 +9292,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -9498,12 +9315,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -9521,12 +9338,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -9544,12 +9361,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -9572,7 +9389,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -9590,12 +9407,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -9613,12 +9430,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -9641,7 +9458,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -9659,12 +9476,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -9682,12 +9499,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -9710,7 +9527,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -9728,12 +9545,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -9751,15 +9568,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C64" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -9779,10 +9596,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C65" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -9797,15 +9614,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C66" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -9820,15 +9637,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C67" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -9843,15 +9660,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C68" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -9866,15 +9683,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C69" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -9894,10 +9711,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C70" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -9912,15 +9729,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C71" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -9935,15 +9752,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C72" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -9958,15 +9775,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C73" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -9981,7 +9798,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB179735-E1DB-4149-A875-481421EAAD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B15C9FF3-D9CD-4783-AC71-B4C50E1F56A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5940,7 +5940,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D78C946-2547-4B68-A212-E89548D88D34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586B7EDC-F203-444E-9FE9-9CEF8406FDDE}">
   <dimension ref="B9:M33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6798,7 +6798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F878B0-9BDE-46EE-A189-F5E3722AEB38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9230B4A9-D703-431F-868F-9ACB56499E9A}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7990,7 +7990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0803C16-B7DF-4A4D-9F7D-9B177146B221}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB87F11-810E-4B5F-AE58-A386EB80C1E1}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B15C9FF3-D9CD-4783-AC71-B4C50E1F56A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF96098A-BAFC-4F66-A277-F4AA60A4B8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="368">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1245,7 +1245,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1393,8 +1393,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1486,6 +1493,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1700,7 +1712,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1720,8 +1732,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2113,6 +2126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2132,8 +2146,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -2526,423 +2541,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -2950,32 +2638,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -2983,37 +2671,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -3025,120 +2713,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1000</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
+        <v>Trd_electricity export</v>
+      </c>
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>1000</v>
+      </c>
+      <c r="S28">
+        <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
         <v>19</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>1000</v>
-      </c>
-      <c r="S18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1000</v>
-      </c>
-      <c r="S19">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4684,25 +4707,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -4748,7 +4771,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -4793,7 +4816,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -4835,7 +4858,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -5940,7 +5963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586B7EDC-F203-444E-9FE9-9CEF8406FDDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFE63CA-8333-4676-B1D1-2E22E36AA8F4}">
   <dimension ref="B9:M33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6798,7 +6821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9230B4A9-D703-431F-868F-9ACB56499E9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF16C26-3322-4C07-9407-08FCC9B13B83}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7990,7 +8013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB87F11-810E-4B5F-AE58-A386EB80C1E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7EECA8-DDEF-461B-BE98-FA221DB124DA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF96098A-BAFC-4F66-A277-F4AA60A4B8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78B8234A-0D4B-4F4A-9D54-939A35AF21C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="370">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -618,6 +618,9 @@
     <t>wnid offshore potential</t>
   </si>
   <si>
+    <t>ELC_BatIn</t>
+  </si>
+  <si>
     <t>~fi_process</t>
   </si>
   <si>
@@ -1231,6 +1234,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>e_DE62-380,e_w170123812-400,e_w59026005-380,e_w952346322-380</t>
   </si>
 </sst>
 </file>
@@ -3124,7 +3130,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_DE62-380,e_w170123812-400,e_w59026005-380,e_w952346322-380</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3146,7 +3152,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_DE62-380,e_w170123812-400,e_w59026005-380,e_w952346322-380</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3161,7 +3167,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -4638,9 +4644,8 @@
     <row r="8" spans="2:25" ht="17.649999999999999">
       <c r="B8" s="20"/>
       <c r="E8" s="26"/>
-      <c r="F8" t="str">
-        <f>C5</f>
-        <v>ELC</v>
+      <c r="F8" t="s">
+        <v>163</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
@@ -5963,62 +5968,62 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFE63CA-8333-4676-B1D1-2E22E36AA8F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649865C8-F8BF-49DB-831B-5C407E3D9476}">
   <dimension ref="B9:M33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10" t="s">
-        <v>170</v>
-      </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
       <c r="K10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6027,16 +6032,16 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L11">
         <v>13.938003670888978</v>
@@ -6047,13 +6052,13 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6062,16 +6067,16 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L12">
         <v>18.31863654586293</v>
@@ -6082,13 +6087,13 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6097,16 +6102,16 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L13">
         <v>30.238043484360141</v>
@@ -6117,13 +6122,13 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6132,16 +6137,16 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L14">
         <v>45.351574205977535</v>
@@ -6152,13 +6157,13 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6167,16 +6172,16 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L15">
         <v>34.531914591504368</v>
@@ -6187,13 +6192,13 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6202,16 +6207,16 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L16">
         <v>38.190379780391297</v>
@@ -6222,13 +6227,13 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6237,16 +6242,16 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L17">
         <v>13.44361680351453</v>
@@ -6257,13 +6262,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6272,16 +6277,16 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L18">
         <v>15.833691242733796</v>
@@ -6292,13 +6297,13 @@
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6307,16 +6312,16 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L19">
         <v>11.346394535605524</v>
@@ -6327,13 +6332,13 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6342,16 +6347,16 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L20">
         <v>32.21637396151899</v>
@@ -6362,13 +6367,13 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6377,16 +6382,16 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L21">
         <v>30.007867954603132</v>
@@ -6397,13 +6402,13 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -6412,16 +6417,16 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L22">
         <v>38.24309918267349</v>
@@ -6432,13 +6437,13 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -6447,16 +6452,16 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23">
         <v>0.95743993217852441</v>
@@ -6467,13 +6472,13 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -6482,16 +6487,16 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L24">
         <v>15.746380528104394</v>
@@ -6502,13 +6507,13 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -6517,16 +6522,16 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L25">
         <v>32.685256480874017</v>
@@ -6537,13 +6542,13 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -6552,16 +6557,16 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L26">
         <v>13.348518217290337</v>
@@ -6572,13 +6577,13 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -6587,16 +6592,16 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L27">
         <v>19.75277137741244</v>
@@ -6607,13 +6612,13 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -6622,16 +6627,16 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L28">
         <v>23.3954191787236</v>
@@ -6642,13 +6647,13 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -6657,16 +6662,16 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L29">
         <v>20.01197763203729</v>
@@ -6677,13 +6682,13 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D30" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -6692,16 +6697,16 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L30">
         <v>23.591873553963495</v>
@@ -6712,13 +6717,13 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -6727,16 +6732,16 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L31">
         <v>21.653826323424543</v>
@@ -6747,13 +6752,13 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -6762,16 +6767,16 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L32">
         <v>12.637613221312568</v>
@@ -6782,13 +6787,13 @@
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -6797,16 +6802,16 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L33">
         <v>23.28078369016097</v>
@@ -6821,101 +6826,101 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF16C26-3322-4C07-9407-08FCC9B13B83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367102E2-9D51-4C63-98B2-4FFE82EE758D}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" t="s">
+        <v>222</v>
+      </c>
+      <c r="L10" t="s">
+        <v>223</v>
+      </c>
+      <c r="M10" t="s">
+        <v>224</v>
+      </c>
+      <c r="O10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="P10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>167</v>
       </c>
-      <c r="F10" t="s">
+      <c r="R10" t="s">
         <v>168</v>
       </c>
-      <c r="G10" t="s">
+      <c r="S10" t="s">
         <v>169</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
         <v>170</v>
       </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
-      <c r="K10" t="s">
-        <v>221</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="U10" t="s">
+        <v>171</v>
+      </c>
+      <c r="W10" t="s">
+        <v>166</v>
+      </c>
+      <c r="X10" t="s">
         <v>222</v>
       </c>
-      <c r="M10" t="s">
+      <c r="Y10" t="s">
         <v>223</v>
       </c>
-      <c r="O10" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>166</v>
-      </c>
-      <c r="R10" t="s">
-        <v>167</v>
-      </c>
-      <c r="S10" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" t="s">
-        <v>169</v>
-      </c>
-      <c r="U10" t="s">
-        <v>170</v>
-      </c>
-      <c r="W10" t="s">
-        <v>165</v>
-      </c>
-      <c r="X10" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>222</v>
-      </c>
       <c r="Z10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6924,16 +6929,16 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L11">
         <v>79.362778177778793</v>
@@ -6942,13 +6947,13 @@
         <v>0.32113557799809911</v>
       </c>
       <c r="O11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -6957,16 +6962,16 @@
         <v>21</v>
       </c>
       <c r="T11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Y11">
         <v>108.8275</v>
@@ -6977,13 +6982,13 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6992,16 +6997,16 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L12">
         <v>50.354564381123943</v>
@@ -7010,13 +7015,13 @@
         <v>0.26229547814325971</v>
       </c>
       <c r="O12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -7025,16 +7030,16 @@
         <v>21</v>
       </c>
       <c r="T12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Y12">
         <v>54.292499999999997</v>
@@ -7045,13 +7050,13 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -7060,16 +7065,16 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L13">
         <v>57.005439523831519</v>
@@ -7078,13 +7083,13 @@
         <v>0.27008680004560909</v>
       </c>
       <c r="O13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -7093,16 +7098,16 @@
         <v>21</v>
       </c>
       <c r="T13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Y13">
         <v>50.356250000000003</v>
@@ -7113,13 +7118,13 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -7128,16 +7133,16 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L14">
         <v>19.895723562817633</v>
@@ -7146,13 +7151,13 @@
         <v>0.41998320074620132</v>
       </c>
       <c r="O14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -7161,16 +7166,16 @@
         <v>21</v>
       </c>
       <c r="T14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Y14">
         <v>9.5987500000000008</v>
@@ -7181,13 +7186,13 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -7196,16 +7201,16 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L15">
         <v>9.5699994650614961</v>
@@ -7214,13 +7219,13 @@
         <v>0.44653362265814228</v>
       </c>
       <c r="O15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -7229,16 +7234,16 @@
         <v>21</v>
       </c>
       <c r="T15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="X15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Y15">
         <v>50.66</v>
@@ -7249,13 +7254,13 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -7264,16 +7269,16 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L16">
         <v>44.760252416795389</v>
@@ -7282,13 +7287,13 @@
         <v>0.42821243398456738</v>
       </c>
       <c r="O16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -7297,16 +7302,16 @@
         <v>21</v>
       </c>
       <c r="T16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="X16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Y16">
         <v>5.0000000000000001E-3</v>
@@ -7317,13 +7322,13 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7332,16 +7337,16 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L17">
         <v>40.59880776523103</v>
@@ -7350,13 +7355,13 @@
         <v>0.34199104865897728</v>
       </c>
       <c r="O17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -7365,16 +7370,16 @@
         <v>21</v>
       </c>
       <c r="T17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="X17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Y17">
         <v>0.92625000000000002</v>
@@ -7385,13 +7390,13 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -7400,16 +7405,16 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L18">
         <v>71.045385513132985</v>
@@ -7418,13 +7423,13 @@
         <v>0.30696999602332747</v>
       </c>
       <c r="O18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -7433,16 +7438,16 @@
         <v>21</v>
       </c>
       <c r="T18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Y18">
         <v>7.5287499999999996</v>
@@ -7453,13 +7458,13 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -7468,16 +7473,16 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L19">
         <v>63.055598832310729</v>
@@ -7486,13 +7491,13 @@
         <v>0.3285833519844587</v>
       </c>
       <c r="O19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -7501,16 +7506,16 @@
         <v>21</v>
       </c>
       <c r="T19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Y19">
         <v>14.6</v>
@@ -7521,13 +7526,13 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -7536,16 +7541,16 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L20">
         <v>43.89469200396065</v>
@@ -7554,13 +7559,13 @@
         <v>0.2838221752225063</v>
       </c>
       <c r="O20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -7569,16 +7574,16 @@
         <v>21</v>
       </c>
       <c r="T20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Y20">
         <v>0.24374999999999999</v>
@@ -7589,13 +7594,13 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -7604,16 +7609,16 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K21" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L21">
         <v>11.547936358898198</v>
@@ -7624,13 +7629,13 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -7639,16 +7644,16 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K22" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L22">
         <v>31.481356456094364</v>
@@ -7659,13 +7664,13 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -7674,16 +7679,16 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L23">
         <v>15.708789779919334</v>
@@ -7694,13 +7699,13 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -7709,16 +7714,16 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L24">
         <v>20.814752751471318</v>
@@ -7729,13 +7734,13 @@
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -7744,16 +7749,16 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L25">
         <v>50.266717026070005</v>
@@ -7764,13 +7769,13 @@
     </row>
     <row r="26" spans="2:26">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -7779,16 +7784,16 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L26">
         <v>56.728889145623882</v>
@@ -7799,13 +7804,13 @@
     </row>
     <row r="27" spans="2:26">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -7814,16 +7819,16 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L27">
         <v>70.602917671125681</v>
@@ -7834,13 +7839,13 @@
     </row>
     <row r="28" spans="2:26">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -7849,16 +7854,16 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K28" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L28">
         <v>7.8153674765988201</v>
@@ -7869,13 +7874,13 @@
     </row>
     <row r="29" spans="2:26">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -7884,16 +7889,16 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K29" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L29">
         <v>26.861604762024118</v>
@@ -7904,13 +7909,13 @@
     </row>
     <row r="30" spans="2:26">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -7919,16 +7924,16 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L30">
         <v>10.889866530825216</v>
@@ -7939,13 +7944,13 @@
     </row>
     <row r="31" spans="2:26">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -7954,16 +7959,16 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K31" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L31">
         <v>9.0084683548455349</v>
@@ -7974,13 +7979,13 @@
     </row>
     <row r="32" spans="2:26">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -7989,16 +7994,16 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L32">
         <v>35.009005865752776</v>
@@ -8013,27 +8018,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7EECA8-DDEF-461B-BE98-FA221DB124DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72517389-39D8-45BF-BB64-2955DEEA03F5}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -8048,30 +8053,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -8092,10 +8097,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -8104,15 +8109,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -8130,13 +8135,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -8145,15 +8150,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -8171,13 +8176,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -8186,15 +8191,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -8212,13 +8217,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -8227,15 +8232,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -8253,13 +8258,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -8268,15 +8273,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -8297,10 +8302,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -8309,15 +8314,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -8335,13 +8340,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -8350,15 +8355,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -8376,13 +8381,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -8391,15 +8396,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -8417,13 +8422,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -8432,15 +8437,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -8458,13 +8463,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -8473,15 +8478,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -8502,10 +8507,10 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -8514,15 +8519,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P21" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -8540,13 +8545,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -8555,15 +8560,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P22" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -8581,13 +8586,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -8596,15 +8601,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P23" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -8625,10 +8630,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -8637,15 +8642,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P24" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -8663,13 +8668,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -8678,15 +8683,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P25" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -8704,13 +8709,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -8719,15 +8724,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P26" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -8748,10 +8753,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -8760,15 +8765,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P27" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -8786,12 +8791,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -8809,12 +8814,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -8837,7 +8842,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -8855,12 +8860,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -8878,12 +8883,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -8906,7 +8911,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -8924,12 +8929,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -8947,12 +8952,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -8970,12 +8975,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -8993,12 +8998,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -9021,7 +9026,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -9039,12 +9044,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -9062,12 +9067,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -9090,7 +9095,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -9108,12 +9113,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -9131,12 +9136,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -9159,7 +9164,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -9177,12 +9182,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -9200,12 +9205,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -9228,7 +9233,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -9246,12 +9251,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -9269,12 +9274,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -9297,7 +9302,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -9315,12 +9320,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -9338,12 +9343,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -9361,12 +9366,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -9384,12 +9389,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -9412,7 +9417,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -9430,12 +9435,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -9453,12 +9458,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -9481,7 +9486,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -9499,12 +9504,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -9522,12 +9527,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -9550,7 +9555,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -9568,12 +9573,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -9591,15 +9596,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C64" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -9619,10 +9624,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C65" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -9637,15 +9642,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -9660,15 +9665,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C67" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -9683,15 +9688,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C68" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -9706,15 +9711,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
+        <v>366</v>
+      </c>
+      <c r="C69" t="s">
         <v>365</v>
-      </c>
-      <c r="C69" t="s">
-        <v>364</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -9734,10 +9739,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
+        <v>366</v>
+      </c>
+      <c r="C70" t="s">
         <v>365</v>
-      </c>
-      <c r="C70" t="s">
-        <v>364</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -9752,15 +9757,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
+        <v>366</v>
+      </c>
+      <c r="C71" t="s">
         <v>365</v>
-      </c>
-      <c r="C71" t="s">
-        <v>364</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -9775,15 +9780,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
+        <v>366</v>
+      </c>
+      <c r="C72" t="s">
         <v>365</v>
-      </c>
-      <c r="C72" t="s">
-        <v>364</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -9798,15 +9803,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
+        <v>366</v>
+      </c>
+      <c r="C73" t="s">
         <v>365</v>
-      </c>
-      <c r="C73" t="s">
-        <v>364</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -9821,7 +9826,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78B8234A-0D4B-4F4A-9D54-939A35AF21C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F04EAA67-405A-4CA3-A871-DBF9F31662A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5968,7 +5968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649865C8-F8BF-49DB-831B-5C407E3D9476}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446257EC-88C4-4692-B573-238A2AC055B1}">
   <dimension ref="B9:M33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6826,7 +6826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367102E2-9D51-4C63-98B2-4FFE82EE758D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E33203C-464F-4769-8E89-FC85B1B64F3F}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8018,7 +8018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72517389-39D8-45BF-BB64-2955DEEA03F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8335C02-94C5-4A09-AA03-D3E81F945F89}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
